--- a/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
+++ b/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
@@ -5044,7 +5044,7 @@
         <v>46181</v>
       </c>
       <c r="B543" t="n">
-        <v>1076477.485714286</v>
+        <v>1076590.042857143</v>
       </c>
     </row>
     <row r="544">
@@ -5108,7 +5108,7 @@
         <v>46237</v>
       </c>
       <c r="B551" t="n">
-        <v>1128658.185714286</v>
+        <v>1128562.957142857</v>
       </c>
     </row>
     <row r="552">
@@ -5156,7 +5156,7 @@
         <v>46279</v>
       </c>
       <c r="B557" t="n">
-        <v>1070109.275</v>
+        <v>1079041.18</v>
       </c>
     </row>
   </sheetData>
@@ -5171,7 +5171,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3886"/>
+  <dimension ref="A1:F3887"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78701,7 +78701,7 @@
         <v>8209.6</v>
       </c>
       <c r="F3684" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3685">
@@ -80789,19 +80789,19 @@
         <v>46185</v>
       </c>
       <c r="B3789" t="n">
-        <v>1112357.4</v>
+        <v>1113145.3</v>
       </c>
       <c r="C3789" t="n">
-        <v>1040259.9</v>
+        <v>1041042.5</v>
       </c>
       <c r="D3789" t="n">
-        <v>61451.2</v>
+        <v>61456.5</v>
       </c>
       <c r="E3789" t="n">
         <v>10646.3</v>
       </c>
       <c r="F3789" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3790">
@@ -81909,19 +81909,19 @@
         <v>46241</v>
       </c>
       <c r="B3845" t="n">
-        <v>1164391.1</v>
+        <v>1163724.5</v>
       </c>
       <c r="C3845" t="n">
-        <v>1080265</v>
+        <v>1079621.2</v>
       </c>
       <c r="D3845" t="n">
-        <v>69670.10000000001</v>
+        <v>69741</v>
       </c>
       <c r="E3845" t="n">
-        <v>14456</v>
+        <v>14362.4</v>
       </c>
       <c r="F3845" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3846">
@@ -82741,6 +82741,26 @@
         <v>13013.9</v>
       </c>
       <c r="F3886" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3887">
+      <c r="A3887" s="4" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B3887" t="n">
+        <v>1114768.8</v>
+      </c>
+      <c r="C3887" t="n">
+        <v>1042133.2</v>
+      </c>
+      <c r="D3887" t="n">
+        <v>59201.1</v>
+      </c>
+      <c r="E3887" t="n">
+        <v>13434.5</v>
+      </c>
+      <c r="F3887" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
+++ b/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
@@ -155,7 +155,8 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Mexico national electricity demand (weekly average) (to Sep/26)</a:t>
+              <a:rPr sz="1200" b="1"/>
+              <a:t>Mexico national electricity demand (weekly average) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -191,12 +192,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$557</f>
+              <f>'Chart'!$A$2:$A$561</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$557</f>
+              <f>'Chart'!$B$2:$B$561</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -693,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B557"/>
+  <dimension ref="A1:B561"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -716,7 +717,7 @@
         <v>42394</v>
       </c>
       <c r="B2" t="n">
-        <v>637597.2333333333</v>
+        <v>637597.2333333334</v>
       </c>
     </row>
     <row r="3">
@@ -772,7 +773,7 @@
         <v>42443</v>
       </c>
       <c r="B9" t="n">
-        <v>719467.9571428571</v>
+        <v>719467.957142857</v>
       </c>
     </row>
     <row r="10">
@@ -812,7 +813,7 @@
         <v>42478</v>
       </c>
       <c r="B14" t="n">
-        <v>763918.0428571429</v>
+        <v>763918.0428571427</v>
       </c>
     </row>
     <row r="15">
@@ -844,7 +845,7 @@
         <v>42506</v>
       </c>
       <c r="B18" t="n">
-        <v>820175.0428571429</v>
+        <v>820175.042857143</v>
       </c>
     </row>
     <row r="19">
@@ -860,7 +861,7 @@
         <v>42520</v>
       </c>
       <c r="B20" t="n">
-        <v>826086.2857142857</v>
+        <v>826086.2857142856</v>
       </c>
     </row>
     <row r="21">
@@ -892,7 +893,7 @@
         <v>42548</v>
       </c>
       <c r="B24" t="n">
-        <v>845643.4714285714</v>
+        <v>845643.4714285715</v>
       </c>
     </row>
     <row r="25">
@@ -924,7 +925,7 @@
         <v>42576</v>
       </c>
       <c r="B28" t="n">
-        <v>841450.0428571429</v>
+        <v>841450.042857143</v>
       </c>
     </row>
     <row r="29">
@@ -940,7 +941,7 @@
         <v>42590</v>
       </c>
       <c r="B30" t="n">
-        <v>852447.9571428571</v>
+        <v>852447.957142857</v>
       </c>
     </row>
     <row r="31">
@@ -964,7 +965,7 @@
         <v>42611</v>
       </c>
       <c r="B33" t="n">
-        <v>824421.4857142858</v>
+        <v>824421.4857142856</v>
       </c>
     </row>
     <row r="34">
@@ -1012,7 +1013,7 @@
         <v>42653</v>
       </c>
       <c r="B39" t="n">
-        <v>790232.5</v>
+        <v>790232.4999999999</v>
       </c>
     </row>
     <row r="40">
@@ -1044,7 +1045,7 @@
         <v>42681</v>
       </c>
       <c r="B43" t="n">
-        <v>725267.6714285715</v>
+        <v>725267.6714285713</v>
       </c>
     </row>
     <row r="44">
@@ -1060,7 +1061,7 @@
         <v>42695</v>
       </c>
       <c r="B45" t="n">
-        <v>692896.5285714286</v>
+        <v>692896.5285714287</v>
       </c>
     </row>
     <row r="46">
@@ -1100,7 +1101,7 @@
         <v>42730</v>
       </c>
       <c r="B50" t="n">
-        <v>643192.0142857142</v>
+        <v>643192.0142857144</v>
       </c>
     </row>
     <row r="51">
@@ -1148,7 +1149,7 @@
         <v>42772</v>
       </c>
       <c r="B56" t="n">
-        <v>725554.2714285714</v>
+        <v>725554.2714285713</v>
       </c>
     </row>
     <row r="57">
@@ -1156,7 +1157,7 @@
         <v>42779</v>
       </c>
       <c r="B57" t="n">
-        <v>740189.6571428571</v>
+        <v>740189.6571428572</v>
       </c>
     </row>
     <row r="58">
@@ -1164,7 +1165,7 @@
         <v>42786</v>
       </c>
       <c r="B58" t="n">
-        <v>739628.6571428571</v>
+        <v>739628.6571428572</v>
       </c>
     </row>
     <row r="59">
@@ -1180,7 +1181,7 @@
         <v>42800</v>
       </c>
       <c r="B60" t="n">
-        <v>753894.7428571429</v>
+        <v>753894.7428571427</v>
       </c>
     </row>
     <row r="61">
@@ -1220,7 +1221,7 @@
         <v>42835</v>
       </c>
       <c r="B65" t="n">
-        <v>739737.2857142857</v>
+        <v>739737.2857142858</v>
       </c>
     </row>
     <row r="66">
@@ -1228,7 +1229,7 @@
         <v>42842</v>
       </c>
       <c r="B66" t="n">
-        <v>804400.8428571429</v>
+        <v>804400.8428571428</v>
       </c>
     </row>
     <row r="67">
@@ -1244,7 +1245,7 @@
         <v>42856</v>
       </c>
       <c r="B68" t="n">
-        <v>812377.2999999999</v>
+        <v>812377.3</v>
       </c>
     </row>
     <row r="69">
@@ -1276,7 +1277,7 @@
         <v>42884</v>
       </c>
       <c r="B72" t="n">
-        <v>853894.4142857144</v>
+        <v>853894.4142857142</v>
       </c>
     </row>
     <row r="73">
@@ -1300,7 +1301,7 @@
         <v>42905</v>
       </c>
       <c r="B75" t="n">
-        <v>920334.5428571429</v>
+        <v>920334.5428571427</v>
       </c>
     </row>
     <row r="76">
@@ -1340,7 +1341,7 @@
         <v>42940</v>
       </c>
       <c r="B80" t="n">
-        <v>878227.8857142858</v>
+        <v>878227.8857142857</v>
       </c>
     </row>
     <row r="81">
@@ -1356,7 +1357,7 @@
         <v>42954</v>
       </c>
       <c r="B82" t="n">
-        <v>895012.7000000001</v>
+        <v>895012.7</v>
       </c>
     </row>
     <row r="83">
@@ -1364,7 +1365,7 @@
         <v>42961</v>
       </c>
       <c r="B83" t="n">
-        <v>897114.3142857143</v>
+        <v>897114.3142857142</v>
       </c>
     </row>
     <row r="84">
@@ -1372,7 +1373,7 @@
         <v>42968</v>
       </c>
       <c r="B84" t="n">
-        <v>903244.8714285714</v>
+        <v>903244.8714285715</v>
       </c>
     </row>
     <row r="85">
@@ -1412,7 +1413,7 @@
         <v>43003</v>
       </c>
       <c r="B89" t="n">
-        <v>817748.4142857142</v>
+        <v>817748.4142857144</v>
       </c>
     </row>
     <row r="90">
@@ -1436,7 +1437,7 @@
         <v>43024</v>
       </c>
       <c r="B92" t="n">
-        <v>811530.5571428572</v>
+        <v>811530.5571428571</v>
       </c>
     </row>
     <row r="93">
@@ -1452,7 +1453,7 @@
         <v>43038</v>
       </c>
       <c r="B94" t="n">
-        <v>772156.8285714285</v>
+        <v>772156.8285714284</v>
       </c>
     </row>
     <row r="95">
@@ -1460,7 +1461,7 @@
         <v>43045</v>
       </c>
       <c r="B95" t="n">
-        <v>785297.2428571429</v>
+        <v>785297.2428571427</v>
       </c>
     </row>
     <row r="96">
@@ -1484,7 +1485,7 @@
         <v>43066</v>
       </c>
       <c r="B98" t="n">
-        <v>745501.3428571429</v>
+        <v>745501.3428571428</v>
       </c>
     </row>
     <row r="99">
@@ -1500,7 +1501,7 @@
         <v>43080</v>
       </c>
       <c r="B100" t="n">
-        <v>735489.0142857142</v>
+        <v>735489.0142857144</v>
       </c>
     </row>
     <row r="101">
@@ -1524,7 +1525,7 @@
         <v>43101</v>
       </c>
       <c r="B103" t="n">
-        <v>702457.9857142858</v>
+        <v>702457.9857142856</v>
       </c>
     </row>
     <row r="104">
@@ -1548,7 +1549,7 @@
         <v>43122</v>
       </c>
       <c r="B106" t="n">
-        <v>747958.0857142856</v>
+        <v>747958.0857142858</v>
       </c>
     </row>
     <row r="107">
@@ -1564,7 +1565,7 @@
         <v>43136</v>
       </c>
       <c r="B108" t="n">
-        <v>737696.4714285714</v>
+        <v>737696.4714285715</v>
       </c>
     </row>
     <row r="109">
@@ -1588,7 +1589,7 @@
         <v>43157</v>
       </c>
       <c r="B111" t="n">
-        <v>785075.4</v>
+        <v>785075.4000000001</v>
       </c>
     </row>
     <row r="112">
@@ -1612,7 +1613,7 @@
         <v>43178</v>
       </c>
       <c r="B114" t="n">
-        <v>803386.8714285714</v>
+        <v>803386.8714285715</v>
       </c>
     </row>
     <row r="115">
@@ -1620,7 +1621,7 @@
         <v>43185</v>
       </c>
       <c r="B115" t="n">
-        <v>758408.4571428571</v>
+        <v>758408.4571428573</v>
       </c>
     </row>
     <row r="116">
@@ -1668,7 +1669,7 @@
         <v>43227</v>
       </c>
       <c r="B121" t="n">
-        <v>864833.8428571429</v>
+        <v>864833.8428571428</v>
       </c>
     </row>
     <row r="122">
@@ -1676,7 +1677,7 @@
         <v>43234</v>
       </c>
       <c r="B122" t="n">
-        <v>905814.3285714285</v>
+        <v>905814.3285714284</v>
       </c>
     </row>
     <row r="123">
@@ -1684,7 +1685,7 @@
         <v>43241</v>
       </c>
       <c r="B123" t="n">
-        <v>911148.7999999999</v>
+        <v>911148.8</v>
       </c>
     </row>
     <row r="124">
@@ -1700,7 +1701,7 @@
         <v>43255</v>
       </c>
       <c r="B125" t="n">
-        <v>964718.1285714286</v>
+        <v>964718.1285714285</v>
       </c>
     </row>
     <row r="126">
@@ -1708,7 +1709,7 @@
         <v>43262</v>
       </c>
       <c r="B126" t="n">
-        <v>917517.7714285714</v>
+        <v>917517.7714285713</v>
       </c>
     </row>
     <row r="127">
@@ -1716,7 +1717,7 @@
         <v>43269</v>
       </c>
       <c r="B127" t="n">
-        <v>909142.2142857143</v>
+        <v>909142.2142857144</v>
       </c>
     </row>
     <row r="128">
@@ -1796,7 +1797,7 @@
         <v>43339</v>
       </c>
       <c r="B137" t="n">
-        <v>937349.2428571429</v>
+        <v>937349.2428571427</v>
       </c>
     </row>
     <row r="138">
@@ -1812,7 +1813,7 @@
         <v>43353</v>
       </c>
       <c r="B139" t="n">
-        <v>885197.2142857143</v>
+        <v>885197.2142857142</v>
       </c>
     </row>
     <row r="140">
@@ -1844,7 +1845,7 @@
         <v>43381</v>
       </c>
       <c r="B143" t="n">
-        <v>847064.1428571428</v>
+        <v>847064.142857143</v>
       </c>
     </row>
     <row r="144">
@@ -1852,7 +1853,7 @@
         <v>43388</v>
       </c>
       <c r="B144" t="n">
-        <v>796261.8857142858</v>
+        <v>796261.8857142857</v>
       </c>
     </row>
     <row r="145">
@@ -1868,7 +1869,7 @@
         <v>43402</v>
       </c>
       <c r="B146" t="n">
-        <v>776671.9142857144</v>
+        <v>776671.9142857142</v>
       </c>
     </row>
     <row r="147">
@@ -1876,7 +1877,7 @@
         <v>43409</v>
       </c>
       <c r="B147" t="n">
-        <v>797205.0285714286</v>
+        <v>797205.0285714285</v>
       </c>
     </row>
     <row r="148">
@@ -1900,7 +1901,7 @@
         <v>43430</v>
       </c>
       <c r="B150" t="n">
-        <v>757518.7285714286</v>
+        <v>757518.7285714287</v>
       </c>
     </row>
     <row r="151">
@@ -1908,7 +1909,7 @@
         <v>43437</v>
       </c>
       <c r="B151" t="n">
-        <v>775416.4571428571</v>
+        <v>775416.457142857</v>
       </c>
     </row>
     <row r="152">
@@ -1956,7 +1957,7 @@
         <v>43479</v>
       </c>
       <c r="B157" t="n">
-        <v>760121.6285714286</v>
+        <v>760121.6285714285</v>
       </c>
     </row>
     <row r="158">
@@ -1972,7 +1973,7 @@
         <v>43493</v>
       </c>
       <c r="B159" t="n">
-        <v>758608.6</v>
+        <v>758608.5999999999</v>
       </c>
     </row>
     <row r="160">
@@ -1980,7 +1981,7 @@
         <v>43500</v>
       </c>
       <c r="B160" t="n">
-        <v>771074.1571428571</v>
+        <v>771074.1571428572</v>
       </c>
     </row>
     <row r="161">
@@ -2020,7 +2021,7 @@
         <v>43535</v>
       </c>
       <c r="B165" t="n">
-        <v>824491.7999999999</v>
+        <v>824491.8</v>
       </c>
     </row>
     <row r="166">
@@ -2044,7 +2045,7 @@
         <v>43556</v>
       </c>
       <c r="B168" t="n">
-        <v>826844.3285714285</v>
+        <v>826844.3285714284</v>
       </c>
     </row>
     <row r="169">
@@ -2068,7 +2069,7 @@
         <v>43577</v>
       </c>
       <c r="B171" t="n">
-        <v>862165.4571428571</v>
+        <v>862165.457142857</v>
       </c>
     </row>
     <row r="172">
@@ -2092,7 +2093,7 @@
         <v>43598</v>
       </c>
       <c r="B174" t="n">
-        <v>906348.6142857142</v>
+        <v>906348.6142857143</v>
       </c>
     </row>
     <row r="175">
@@ -2100,7 +2101,7 @@
         <v>43605</v>
       </c>
       <c r="B175" t="n">
-        <v>931077.3285714285</v>
+        <v>931077.3285714284</v>
       </c>
     </row>
     <row r="176">
@@ -2108,7 +2109,7 @@
         <v>43612</v>
       </c>
       <c r="B176" t="n">
-        <v>930521.0571428572</v>
+        <v>930521.0571428571</v>
       </c>
     </row>
     <row r="177">
@@ -2156,7 +2157,7 @@
         <v>43654</v>
       </c>
       <c r="B182" t="n">
-        <v>970532.6285714286</v>
+        <v>970532.6285714284</v>
       </c>
     </row>
     <row r="183">
@@ -2212,7 +2213,7 @@
         <v>43703</v>
       </c>
       <c r="B189" t="n">
-        <v>971080.9428571428</v>
+        <v>971080.9428571429</v>
       </c>
     </row>
     <row r="190">
@@ -2252,7 +2253,7 @@
         <v>43738</v>
       </c>
       <c r="B194" t="n">
-        <v>869541.3714285714</v>
+        <v>869541.3714285715</v>
       </c>
     </row>
     <row r="195">
@@ -2260,7 +2261,7 @@
         <v>43745</v>
       </c>
       <c r="B195" t="n">
-        <v>862967.1428571428</v>
+        <v>862967.142857143</v>
       </c>
     </row>
     <row r="196">
@@ -2356,7 +2357,7 @@
         <v>43829</v>
       </c>
       <c r="B207" t="n">
-        <v>677102.3428571429</v>
+        <v>677102.3428571428</v>
       </c>
     </row>
     <row r="208">
@@ -2364,7 +2365,7 @@
         <v>43836</v>
       </c>
       <c r="B208" t="n">
-        <v>759224.9857142858</v>
+        <v>759224.9857142856</v>
       </c>
     </row>
     <row r="209">
@@ -2372,7 +2373,7 @@
         <v>43843</v>
       </c>
       <c r="B209" t="n">
-        <v>784824.1142857142</v>
+        <v>784824.1142857143</v>
       </c>
     </row>
     <row r="210">
@@ -2388,7 +2389,7 @@
         <v>43857</v>
       </c>
       <c r="B211" t="n">
-        <v>764850.4428571428</v>
+        <v>764850.4428571429</v>
       </c>
     </row>
     <row r="212">
@@ -2468,7 +2469,7 @@
         <v>43927</v>
       </c>
       <c r="B221" t="n">
-        <v>735634.6571428571</v>
+        <v>735634.6571428572</v>
       </c>
     </row>
     <row r="222">
@@ -2476,7 +2477,7 @@
         <v>43934</v>
       </c>
       <c r="B222" t="n">
-        <v>746119.4142857144</v>
+        <v>746119.4142857142</v>
       </c>
     </row>
     <row r="223">
@@ -2532,7 +2533,7 @@
         <v>43983</v>
       </c>
       <c r="B229" t="n">
-        <v>863511.7000000001</v>
+        <v>863511.7</v>
       </c>
     </row>
     <row r="230">
@@ -2548,7 +2549,7 @@
         <v>43997</v>
       </c>
       <c r="B231" t="n">
-        <v>901776.8857142858</v>
+        <v>901776.8857142857</v>
       </c>
     </row>
     <row r="232">
@@ -2588,7 +2589,7 @@
         <v>44032</v>
       </c>
       <c r="B236" t="n">
-        <v>923270.8285714285</v>
+        <v>923270.8285714284</v>
       </c>
     </row>
     <row r="237">
@@ -2596,7 +2597,7 @@
         <v>44039</v>
       </c>
       <c r="B237" t="n">
-        <v>896321.0571428572</v>
+        <v>896321.0571428571</v>
       </c>
     </row>
     <row r="238">
@@ -2604,7 +2605,7 @@
         <v>44046</v>
       </c>
       <c r="B238" t="n">
-        <v>937819.9142857144</v>
+        <v>937819.9142857142</v>
       </c>
     </row>
     <row r="239">
@@ -2612,7 +2613,7 @@
         <v>44053</v>
       </c>
       <c r="B239" t="n">
-        <v>957281.1571428571</v>
+        <v>957281.1571428572</v>
       </c>
     </row>
     <row r="240">
@@ -2644,7 +2645,7 @@
         <v>44081</v>
       </c>
       <c r="B243" t="n">
-        <v>885653.5857142856</v>
+        <v>885653.5857142858</v>
       </c>
     </row>
     <row r="244">
@@ -2652,7 +2653,7 @@
         <v>44088</v>
       </c>
       <c r="B244" t="n">
-        <v>864477.8428571429</v>
+        <v>864477.8428571428</v>
       </c>
     </row>
     <row r="245">
@@ -2660,7 +2661,7 @@
         <v>44095</v>
       </c>
       <c r="B245" t="n">
-        <v>904455.9714285714</v>
+        <v>904455.9714285715</v>
       </c>
     </row>
     <row r="246">
@@ -2676,7 +2677,7 @@
         <v>44109</v>
       </c>
       <c r="B247" t="n">
-        <v>876939.2999999999</v>
+        <v>876939.3</v>
       </c>
     </row>
     <row r="248">
@@ -2684,7 +2685,7 @@
         <v>44116</v>
       </c>
       <c r="B248" t="n">
-        <v>889487.4</v>
+        <v>889487.4000000001</v>
       </c>
     </row>
     <row r="249">
@@ -2716,7 +2717,7 @@
         <v>44144</v>
       </c>
       <c r="B252" t="n">
-        <v>812168.7428571429</v>
+        <v>812168.7428571427</v>
       </c>
     </row>
     <row r="253">
@@ -2724,7 +2725,7 @@
         <v>44151</v>
       </c>
       <c r="B253" t="n">
-        <v>787586.2857142857</v>
+        <v>787586.2857142856</v>
       </c>
     </row>
     <row r="254">
@@ -2732,7 +2733,7 @@
         <v>44158</v>
       </c>
       <c r="B254" t="n">
-        <v>804438.4285714285</v>
+        <v>804438.4285714288</v>
       </c>
     </row>
     <row r="255">
@@ -2772,7 +2773,7 @@
         <v>44193</v>
       </c>
       <c r="B259" t="n">
-        <v>673228.8571428572</v>
+        <v>673228.8571428573</v>
       </c>
     </row>
     <row r="260">
@@ -2788,7 +2789,7 @@
         <v>44207</v>
       </c>
       <c r="B261" t="n">
-        <v>781788.0285714286</v>
+        <v>781788.0285714285</v>
       </c>
     </row>
     <row r="262">
@@ -2844,7 +2845,7 @@
         <v>44256</v>
       </c>
       <c r="B268" t="n">
-        <v>804754.5571428572</v>
+        <v>804754.5571428571</v>
       </c>
     </row>
     <row r="269">
@@ -2860,7 +2861,7 @@
         <v>44270</v>
       </c>
       <c r="B270" t="n">
-        <v>813604.5142857142</v>
+        <v>813604.5142857144</v>
       </c>
     </row>
     <row r="271">
@@ -2868,7 +2869,7 @@
         <v>44277</v>
       </c>
       <c r="B271" t="n">
-        <v>841831.2428571429</v>
+        <v>841831.2428571427</v>
       </c>
     </row>
     <row r="272">
@@ -2884,7 +2885,7 @@
         <v>44291</v>
       </c>
       <c r="B273" t="n">
-        <v>883353.2999999999</v>
+        <v>883353.3</v>
       </c>
     </row>
     <row r="274">
@@ -2892,7 +2893,7 @@
         <v>44298</v>
       </c>
       <c r="B274" t="n">
-        <v>908989.6571428571</v>
+        <v>908989.6571428572</v>
       </c>
     </row>
     <row r="275">
@@ -2908,7 +2909,7 @@
         <v>44312</v>
       </c>
       <c r="B276" t="n">
-        <v>898290.6714285715</v>
+        <v>898290.6714285713</v>
       </c>
     </row>
     <row r="277">
@@ -2932,7 +2933,7 @@
         <v>44333</v>
       </c>
       <c r="B279" t="n">
-        <v>924578.4</v>
+        <v>924578.4000000001</v>
       </c>
     </row>
     <row r="280">
@@ -2940,7 +2941,7 @@
         <v>44340</v>
       </c>
       <c r="B280" t="n">
-        <v>957157.6714285715</v>
+        <v>957157.6714285713</v>
       </c>
     </row>
     <row r="281">
@@ -2972,7 +2973,7 @@
         <v>44368</v>
       </c>
       <c r="B284" t="n">
-        <v>970744.2999999999</v>
+        <v>970744.3</v>
       </c>
     </row>
     <row r="285">
@@ -3004,7 +3005,7 @@
         <v>44396</v>
       </c>
       <c r="B288" t="n">
-        <v>962700.1285714286</v>
+        <v>962700.1285714285</v>
       </c>
     </row>
     <row r="289">
@@ -3020,7 +3021,7 @@
         <v>44410</v>
       </c>
       <c r="B290" t="n">
-        <v>957023.8571428572</v>
+        <v>957023.857142857</v>
       </c>
     </row>
     <row r="291">
@@ -3036,7 +3037,7 @@
         <v>44424</v>
       </c>
       <c r="B292" t="n">
-        <v>961760.7285714286</v>
+        <v>961760.7285714288</v>
       </c>
     </row>
     <row r="293">
@@ -3044,7 +3045,7 @@
         <v>44431</v>
       </c>
       <c r="B293" t="n">
-        <v>964140.8857142858</v>
+        <v>964140.8857142857</v>
       </c>
     </row>
     <row r="294">
@@ -3060,7 +3061,7 @@
         <v>44445</v>
       </c>
       <c r="B295" t="n">
-        <v>936611.7428571429</v>
+        <v>936611.7428571427</v>
       </c>
     </row>
     <row r="296">
@@ -3116,7 +3117,7 @@
         <v>44494</v>
       </c>
       <c r="B302" t="n">
-        <v>851351.8857142858</v>
+        <v>851351.8857142857</v>
       </c>
     </row>
     <row r="303">
@@ -3140,7 +3141,7 @@
         <v>44515</v>
       </c>
       <c r="B305" t="n">
-        <v>782332.8571428572</v>
+        <v>782332.857142857</v>
       </c>
     </row>
     <row r="306">
@@ -3156,7 +3157,7 @@
         <v>44529</v>
       </c>
       <c r="B307" t="n">
-        <v>797911.7285714286</v>
+        <v>797911.7285714287</v>
       </c>
     </row>
     <row r="308">
@@ -3196,7 +3197,7 @@
         <v>44564</v>
       </c>
       <c r="B312" t="n">
-        <v>781054.8</v>
+        <v>781054.7999999999</v>
       </c>
     </row>
     <row r="313">
@@ -3204,7 +3205,7 @@
         <v>44571</v>
       </c>
       <c r="B313" t="n">
-        <v>789021.0571428572</v>
+        <v>789021.0571428571</v>
       </c>
     </row>
     <row r="314">
@@ -3228,7 +3229,7 @@
         <v>44592</v>
       </c>
       <c r="B316" t="n">
-        <v>804333.5571428572</v>
+        <v>804333.5571428571</v>
       </c>
     </row>
     <row r="317">
@@ -3236,7 +3237,7 @@
         <v>44599</v>
       </c>
       <c r="B317" t="n">
-        <v>783251.7000000001</v>
+        <v>783251.7</v>
       </c>
     </row>
     <row r="318">
@@ -3244,7 +3245,7 @@
         <v>44606</v>
       </c>
       <c r="B318" t="n">
-        <v>800562.4714285714</v>
+        <v>800562.4714285715</v>
       </c>
     </row>
     <row r="319">
@@ -3260,7 +3261,7 @@
         <v>44620</v>
       </c>
       <c r="B320" t="n">
-        <v>818555.5857142856</v>
+        <v>818555.5857142858</v>
       </c>
     </row>
     <row r="321">
@@ -3268,7 +3269,7 @@
         <v>44627</v>
       </c>
       <c r="B321" t="n">
-        <v>834167.7857142857</v>
+        <v>834167.7857142856</v>
       </c>
     </row>
     <row r="322">
@@ -3308,7 +3309,7 @@
         <v>44662</v>
       </c>
       <c r="B326" t="n">
-        <v>863537.0142857142</v>
+        <v>863537.0142857144</v>
       </c>
     </row>
     <row r="327">
@@ -3332,7 +3333,7 @@
         <v>44683</v>
       </c>
       <c r="B329" t="n">
-        <v>971875.7714285714</v>
+        <v>971875.7714285713</v>
       </c>
     </row>
     <row r="330">
@@ -3356,7 +3357,7 @@
         <v>44704</v>
       </c>
       <c r="B332" t="n">
-        <v>987922.2714285714</v>
+        <v>987922.2714285713</v>
       </c>
     </row>
     <row r="333">
@@ -3428,7 +3429,7 @@
         <v>44767</v>
       </c>
       <c r="B341" t="n">
-        <v>988050.2142857143</v>
+        <v>988050.2142857144</v>
       </c>
     </row>
     <row r="342">
@@ -3452,7 +3453,7 @@
         <v>44788</v>
       </c>
       <c r="B344" t="n">
-        <v>974169.5857142856</v>
+        <v>974169.5857142858</v>
       </c>
     </row>
     <row r="345">
@@ -3484,7 +3485,7 @@
         <v>44816</v>
       </c>
       <c r="B348" t="n">
-        <v>907053.2285714286</v>
+        <v>907053.2285714287</v>
       </c>
     </row>
     <row r="349">
@@ -3500,7 +3501,7 @@
         <v>44830</v>
       </c>
       <c r="B350" t="n">
-        <v>924424.8428571429</v>
+        <v>924424.8428571428</v>
       </c>
     </row>
     <row r="351">
@@ -3516,7 +3517,7 @@
         <v>44844</v>
       </c>
       <c r="B352" t="n">
-        <v>899133.8142857143</v>
+        <v>899133.8142857142</v>
       </c>
     </row>
     <row r="353">
@@ -3532,7 +3533,7 @@
         <v>44858</v>
       </c>
       <c r="B354" t="n">
-        <v>861914.3714285714</v>
+        <v>861914.3714285715</v>
       </c>
     </row>
     <row r="355">
@@ -3540,7 +3541,7 @@
         <v>44865</v>
       </c>
       <c r="B355" t="n">
-        <v>830321.7000000001</v>
+        <v>830321.7</v>
       </c>
     </row>
     <row r="356">
@@ -3548,7 +3549,7 @@
         <v>44872</v>
       </c>
       <c r="B356" t="n">
-        <v>846317.8714285714</v>
+        <v>846317.8714285715</v>
       </c>
     </row>
     <row r="357">
@@ -3564,7 +3565,7 @@
         <v>44886</v>
       </c>
       <c r="B358" t="n">
-        <v>808607.7714285714</v>
+        <v>808607.7714285713</v>
       </c>
     </row>
     <row r="359">
@@ -3644,7 +3645,7 @@
         <v>44956</v>
       </c>
       <c r="B368" t="n">
-        <v>831313.9</v>
+        <v>831313.8999999998</v>
       </c>
     </row>
     <row r="369">
@@ -3660,7 +3661,7 @@
         <v>44970</v>
       </c>
       <c r="B370" t="n">
-        <v>830163.2285714286</v>
+        <v>830163.2285714287</v>
       </c>
     </row>
     <row r="371">
@@ -3708,7 +3709,7 @@
         <v>45012</v>
       </c>
       <c r="B376" t="n">
-        <v>898901.7857142857</v>
+        <v>898901.7857142858</v>
       </c>
     </row>
     <row r="377">
@@ -3716,7 +3717,7 @@
         <v>45019</v>
       </c>
       <c r="B377" t="n">
-        <v>839030.1571428571</v>
+        <v>839030.1571428572</v>
       </c>
     </row>
     <row r="378">
@@ -3764,7 +3765,7 @@
         <v>45061</v>
       </c>
       <c r="B383" t="n">
-        <v>955621.5714285715</v>
+        <v>955621.5714285712</v>
       </c>
     </row>
     <row r="384">
@@ -3772,7 +3773,7 @@
         <v>45068</v>
       </c>
       <c r="B384" t="n">
-        <v>985343.6285714286</v>
+        <v>985343.6285714285</v>
       </c>
     </row>
     <row r="385">
@@ -3956,7 +3957,7 @@
         <v>45229</v>
       </c>
       <c r="B407" t="n">
-        <v>823392.3571428572</v>
+        <v>823392.3571428573</v>
       </c>
     </row>
     <row r="408">
@@ -3964,7 +3965,7 @@
         <v>45236</v>
       </c>
       <c r="B408" t="n">
-        <v>865530.2428571429</v>
+        <v>865530.2428571427</v>
       </c>
     </row>
     <row r="409">
@@ -3988,7 +3989,7 @@
         <v>45257</v>
       </c>
       <c r="B411" t="n">
-        <v>829123.9285714285</v>
+        <v>829123.9285714288</v>
       </c>
     </row>
     <row r="412">
@@ -4012,7 +4013,7 @@
         <v>45278</v>
       </c>
       <c r="B414" t="n">
-        <v>774327.8857142858</v>
+        <v>774327.8857142857</v>
       </c>
     </row>
     <row r="415">
@@ -4020,7 +4021,7 @@
         <v>45285</v>
       </c>
       <c r="B415" t="n">
-        <v>700220.7857142857</v>
+        <v>700220.7857142856</v>
       </c>
     </row>
     <row r="416">
@@ -4036,7 +4037,7 @@
         <v>45299</v>
       </c>
       <c r="B417" t="n">
-        <v>827502.2999999999</v>
+        <v>827502.3</v>
       </c>
     </row>
     <row r="418">
@@ -4124,7 +4125,7 @@
         <v>45376</v>
       </c>
       <c r="B428" t="n">
-        <v>820048.6571428571</v>
+        <v>820048.6571428572</v>
       </c>
     </row>
     <row r="429">
@@ -4132,7 +4133,7 @@
         <v>45383</v>
       </c>
       <c r="B429" t="n">
-        <v>899013.2714285713</v>
+        <v>899013.2714285714</v>
       </c>
     </row>
     <row r="430">
@@ -4140,7 +4141,7 @@
         <v>45390</v>
       </c>
       <c r="B430" t="n">
-        <v>929206.4571428571</v>
+        <v>929206.457142857</v>
       </c>
     </row>
     <row r="431">
@@ -4156,7 +4157,7 @@
         <v>45404</v>
       </c>
       <c r="B432" t="n">
-        <v>964496.9714285714</v>
+        <v>964496.9714285715</v>
       </c>
     </row>
     <row r="433">
@@ -4292,7 +4293,7 @@
         <v>45523</v>
       </c>
       <c r="B449" t="n">
-        <v>1079905.028571428</v>
+        <v>1079905.028571429</v>
       </c>
     </row>
     <row r="450">
@@ -4324,7 +4325,7 @@
         <v>45551</v>
       </c>
       <c r="B453" t="n">
-        <v>1002259.871428572</v>
+        <v>1002259.871428571</v>
       </c>
     </row>
     <row r="454">
@@ -4356,7 +4357,7 @@
         <v>45579</v>
       </c>
       <c r="B457" t="n">
-        <v>928195.4714285714</v>
+        <v>928195.4714285715</v>
       </c>
     </row>
     <row r="458">
@@ -4364,7 +4365,7 @@
         <v>45586</v>
       </c>
       <c r="B458" t="n">
-        <v>923168.2428571429</v>
+        <v>923168.2428571427</v>
       </c>
     </row>
     <row r="459">
@@ -4372,7 +4373,7 @@
         <v>45593</v>
       </c>
       <c r="B459" t="n">
-        <v>898314.9</v>
+        <v>898314.9000000001</v>
       </c>
     </row>
     <row r="460">
@@ -4388,7 +4389,7 @@
         <v>45607</v>
       </c>
       <c r="B461" t="n">
-        <v>878816.1</v>
+        <v>878816.0999999999</v>
       </c>
     </row>
     <row r="462">
@@ -4404,7 +4405,7 @@
         <v>45621</v>
       </c>
       <c r="B463" t="n">
-        <v>836330.8428571429</v>
+        <v>836330.8428571428</v>
       </c>
     </row>
     <row r="464">
@@ -4420,7 +4421,7 @@
         <v>45635</v>
       </c>
       <c r="B465" t="n">
-        <v>818561.3857142858</v>
+        <v>818561.3857142857</v>
       </c>
     </row>
     <row r="466">
@@ -4436,7 +4437,7 @@
         <v>45649</v>
       </c>
       <c r="B467" t="n">
-        <v>709094.0571428572</v>
+        <v>709094.0571428571</v>
       </c>
     </row>
     <row r="468">
@@ -4476,7 +4477,7 @@
         <v>45684</v>
       </c>
       <c r="B472" t="n">
-        <v>836760.7857142857</v>
+        <v>836760.7857142856</v>
       </c>
     </row>
     <row r="473">
@@ -4508,7 +4509,7 @@
         <v>45712</v>
       </c>
       <c r="B476" t="n">
-        <v>848332.2142857143</v>
+        <v>848332.2142857142</v>
       </c>
     </row>
     <row r="477">
@@ -4548,7 +4549,7 @@
         <v>45747</v>
       </c>
       <c r="B481" t="n">
-        <v>955471.2285714286</v>
+        <v>955471.2285714287</v>
       </c>
     </row>
     <row r="482">
@@ -4652,7 +4653,7 @@
         <v>45838</v>
       </c>
       <c r="B494" t="n">
-        <v>1020714.428571429</v>
+        <v>1020714.428571428</v>
       </c>
     </row>
     <row r="495">
@@ -4756,7 +4757,7 @@
         <v>45929</v>
       </c>
       <c r="B507" t="n">
-        <v>984447.3428571429</v>
+        <v>984447.3428571428</v>
       </c>
     </row>
     <row r="508">
@@ -4772,7 +4773,7 @@
         <v>45943</v>
       </c>
       <c r="B509" t="n">
-        <v>945904.7285714286</v>
+        <v>945904.7285714287</v>
       </c>
     </row>
     <row r="510">
@@ -4796,7 +4797,7 @@
         <v>45964</v>
       </c>
       <c r="B512" t="n">
-        <v>885104.5428571429</v>
+        <v>885104.542857143</v>
       </c>
     </row>
     <row r="513">
@@ -4820,7 +4821,7 @@
         <v>45985</v>
       </c>
       <c r="B515" t="n">
-        <v>867899.7142857143</v>
+        <v>867899.7142857142</v>
       </c>
     </row>
     <row r="516">
@@ -4852,7 +4853,7 @@
         <v>46013</v>
       </c>
       <c r="B519" t="n">
-        <v>750876.6142857142</v>
+        <v>750876.6142857143</v>
       </c>
     </row>
     <row r="520">
@@ -4876,7 +4877,7 @@
         <v>46034</v>
       </c>
       <c r="B522" t="n">
-        <v>846389.4428571428</v>
+        <v>846389.4428571429</v>
       </c>
     </row>
     <row r="523">
@@ -4884,7 +4885,7 @@
         <v>46041</v>
       </c>
       <c r="B523" t="n">
-        <v>852954.4428571428</v>
+        <v>852954.4428571427</v>
       </c>
     </row>
     <row r="524">
@@ -4924,7 +4925,7 @@
         <v>46076</v>
       </c>
       <c r="B528" t="n">
-        <v>874484.6285714286</v>
+        <v>874484.5571428571</v>
       </c>
     </row>
     <row r="529">
@@ -4932,7 +4933,7 @@
         <v>46083</v>
       </c>
       <c r="B529" t="n">
-        <v>921059.1142857142</v>
+        <v>921057.5999999999</v>
       </c>
     </row>
     <row r="530">
@@ -4940,7 +4941,7 @@
         <v>46090</v>
       </c>
       <c r="B530" t="n">
-        <v>923212.7714285714</v>
+        <v>923212.2</v>
       </c>
     </row>
     <row r="531">
@@ -4948,7 +4949,7 @@
         <v>46097</v>
       </c>
       <c r="B531" t="n">
-        <v>887406.7285714286</v>
+        <v>887406.1714285713</v>
       </c>
     </row>
     <row r="532">
@@ -4956,7 +4957,7 @@
         <v>46104</v>
       </c>
       <c r="B532" t="n">
-        <v>953600.5142857142</v>
+        <v>953600.3285714285</v>
       </c>
     </row>
     <row r="533">
@@ -4964,7 +4965,7 @@
         <v>46111</v>
       </c>
       <c r="B533" t="n">
-        <v>890255.0714285715</v>
+        <v>890255.0714285716</v>
       </c>
     </row>
     <row r="534">
@@ -5044,7 +5045,7 @@
         <v>46181</v>
       </c>
       <c r="B543" t="n">
-        <v>1076590.042857143</v>
+        <v>1076567.114285714</v>
       </c>
     </row>
     <row r="544">
@@ -5052,7 +5053,7 @@
         <v>46188</v>
       </c>
       <c r="B544" t="n">
-        <v>1094591.857142857</v>
+        <v>1094444.685714286</v>
       </c>
     </row>
     <row r="545">
@@ -5060,7 +5061,7 @@
         <v>46195</v>
       </c>
       <c r="B545" t="n">
-        <v>1116005.714285714</v>
+        <v>1116059.585714286</v>
       </c>
     </row>
     <row r="546">
@@ -5068,7 +5069,7 @@
         <v>46202</v>
       </c>
       <c r="B546" t="n">
-        <v>1104721.371428571</v>
+        <v>1104543.157142857</v>
       </c>
     </row>
     <row r="547">
@@ -5076,7 +5077,7 @@
         <v>46209</v>
       </c>
       <c r="B547" t="n">
-        <v>1095245.942857143</v>
+        <v>1095172.785714286</v>
       </c>
     </row>
     <row r="548">
@@ -5108,7 +5109,7 @@
         <v>46237</v>
       </c>
       <c r="B551" t="n">
-        <v>1128562.957142857</v>
+        <v>1128605.014285714</v>
       </c>
     </row>
     <row r="552">
@@ -5116,7 +5117,7 @@
         <v>46244</v>
       </c>
       <c r="B552" t="n">
-        <v>1133514.5</v>
+        <v>1133936.185714286</v>
       </c>
     </row>
     <row r="553">
@@ -5124,7 +5125,7 @@
         <v>46251</v>
       </c>
       <c r="B553" t="n">
-        <v>1150060.328571429</v>
+        <v>1149800.914285715</v>
       </c>
     </row>
     <row r="554">
@@ -5132,7 +5133,7 @@
         <v>46258</v>
       </c>
       <c r="B554" t="n">
-        <v>1159741.614285714</v>
+        <v>1159026.271428572</v>
       </c>
     </row>
     <row r="555">
@@ -5140,7 +5141,7 @@
         <v>46265</v>
       </c>
       <c r="B555" t="n">
-        <v>1131145.3</v>
+        <v>1131045.314285714</v>
       </c>
     </row>
     <row r="556">
@@ -5156,7 +5157,39 @@
         <v>46279</v>
       </c>
       <c r="B557" t="n">
-        <v>1079041.18</v>
+        <v>1062828.185714286</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="3" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B558" t="n">
+        <v>1077434.414285714</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="3" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B559" t="n">
+        <v>1039934.528571429</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="3" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B560" t="n">
+        <v>1015648.385714286</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="3" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B561" t="n">
+        <v>1034647.85</v>
       </c>
     </row>
   </sheetData>
@@ -5171,7 +5204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3887"/>
+  <dimension ref="A1:F3912"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78721,7 +78754,7 @@
         <v>8108.7</v>
       </c>
       <c r="F3685" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3686">
@@ -78729,19 +78762,19 @@
         <v>46082</v>
       </c>
       <c r="B3686" t="n">
-        <v>808808.3</v>
+        <v>808807.8</v>
       </c>
       <c r="C3686" t="n">
-        <v>763279.9</v>
+        <v>763283.5</v>
       </c>
       <c r="D3686" t="n">
-        <v>37606.9</v>
+        <v>37602.8</v>
       </c>
       <c r="E3686" t="n">
         <v>7921.5</v>
       </c>
       <c r="F3686" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3687">
@@ -78749,19 +78782,19 @@
         <v>46083</v>
       </c>
       <c r="B3687" t="n">
-        <v>910973.1</v>
+        <v>910970.6</v>
       </c>
       <c r="C3687" t="n">
-        <v>861056.2</v>
+        <v>861059.6</v>
       </c>
       <c r="D3687" t="n">
-        <v>41476.2</v>
+        <v>41472.2</v>
       </c>
       <c r="E3687" t="n">
-        <v>8440.799999999999</v>
+        <v>8438.799999999999</v>
       </c>
       <c r="F3687" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3688">
@@ -78769,19 +78802,19 @@
         <v>46084</v>
       </c>
       <c r="B3688" t="n">
-        <v>944997.5</v>
+        <v>944995.2</v>
       </c>
       <c r="C3688" t="n">
-        <v>894744.5</v>
+        <v>894748.2</v>
       </c>
       <c r="D3688" t="n">
-        <v>41786.1</v>
+        <v>41781.9</v>
       </c>
       <c r="E3688" t="n">
-        <v>8467</v>
+        <v>8465.1</v>
       </c>
       <c r="F3688" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3689">
@@ -78789,19 +78822,19 @@
         <v>46085</v>
       </c>
       <c r="B3689" t="n">
-        <v>955439.2</v>
+        <v>955436.8</v>
       </c>
       <c r="C3689" t="n">
-        <v>904891.6</v>
+        <v>904895</v>
       </c>
       <c r="D3689" t="n">
-        <v>42044.1</v>
+        <v>42040.2</v>
       </c>
       <c r="E3689" t="n">
-        <v>8503.4</v>
+        <v>8501.6</v>
       </c>
       <c r="F3689" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3690">
@@ -78809,19 +78842,19 @@
         <v>46086</v>
       </c>
       <c r="B3690" t="n">
-        <v>958123.5</v>
+        <v>958121.1</v>
       </c>
       <c r="C3690" t="n">
-        <v>908681.1</v>
+        <v>908684.1</v>
       </c>
       <c r="D3690" t="n">
-        <v>40955.8</v>
+        <v>40952</v>
       </c>
       <c r="E3690" t="n">
-        <v>8486.6</v>
+        <v>8485</v>
       </c>
       <c r="F3690" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3691">
@@ -78829,19 +78862,19 @@
         <v>46087</v>
       </c>
       <c r="B3691" t="n">
-        <v>953084.6</v>
+        <v>953084.5</v>
       </c>
       <c r="C3691" t="n">
-        <v>905186.9</v>
+        <v>905190.4</v>
       </c>
       <c r="D3691" t="n">
-        <v>39756.2</v>
+        <v>39752</v>
       </c>
       <c r="E3691" t="n">
-        <v>8141.5</v>
+        <v>8142.1</v>
       </c>
       <c r="F3691" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3692">
@@ -78849,19 +78882,19 @@
         <v>46088</v>
       </c>
       <c r="B3692" t="n">
-        <v>908791</v>
+        <v>908790.4</v>
       </c>
       <c r="C3692" t="n">
-        <v>865313.5</v>
+        <v>865317.1</v>
       </c>
       <c r="D3692" t="n">
-        <v>35715.9</v>
+        <v>35711.7</v>
       </c>
       <c r="E3692" t="n">
         <v>7761.7</v>
       </c>
       <c r="F3692" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3693">
@@ -78869,19 +78902,19 @@
         <v>46089</v>
       </c>
       <c r="B3693" t="n">
-        <v>816004.9</v>
+        <v>816004.6</v>
       </c>
       <c r="C3693" t="n">
-        <v>778355.4</v>
+        <v>778358.6</v>
       </c>
       <c r="D3693" t="n">
-        <v>30329.5</v>
+        <v>30326</v>
       </c>
       <c r="E3693" t="n">
         <v>7320</v>
       </c>
       <c r="F3693" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3694">
@@ -78889,19 +78922,19 @@
         <v>46090</v>
       </c>
       <c r="B3694" t="n">
-        <v>926390.1</v>
+        <v>926389.8</v>
       </c>
       <c r="C3694" t="n">
-        <v>880527</v>
+        <v>880530.3</v>
       </c>
       <c r="D3694" t="n">
-        <v>38112</v>
+        <v>38108.2</v>
       </c>
       <c r="E3694" t="n">
         <v>7751.2</v>
       </c>
       <c r="F3694" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3695">
@@ -78909,19 +78942,19 @@
         <v>46091</v>
       </c>
       <c r="B3695" t="n">
-        <v>957732.8</v>
+        <v>957732.4</v>
       </c>
       <c r="C3695" t="n">
-        <v>908832.4</v>
+        <v>908835.4</v>
       </c>
       <c r="D3695" t="n">
-        <v>41245.7</v>
+        <v>41242.2</v>
       </c>
       <c r="E3695" t="n">
         <v>7654.7</v>
       </c>
       <c r="F3695" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3696">
@@ -78929,19 +78962,19 @@
         <v>46092</v>
       </c>
       <c r="B3696" t="n">
-        <v>966455.2</v>
+        <v>966455</v>
       </c>
       <c r="C3696" t="n">
-        <v>918526.1</v>
+        <v>918529.4</v>
       </c>
       <c r="D3696" t="n">
-        <v>40372.8</v>
+        <v>40369.3</v>
       </c>
       <c r="E3696" t="n">
         <v>7556.3</v>
       </c>
       <c r="F3696" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3697">
@@ -78949,19 +78982,19 @@
         <v>46093</v>
       </c>
       <c r="B3697" t="n">
-        <v>951039</v>
+        <v>951038</v>
       </c>
       <c r="C3697" t="n">
-        <v>900194.8</v>
+        <v>900197.8</v>
       </c>
       <c r="D3697" t="n">
-        <v>43012.3</v>
+        <v>43008.2</v>
       </c>
       <c r="E3697" t="n">
         <v>7831.9</v>
       </c>
       <c r="F3697" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3698">
@@ -78969,19 +79002,19 @@
         <v>46094</v>
       </c>
       <c r="B3698" t="n">
-        <v>937485.5</v>
+        <v>937485.2</v>
       </c>
       <c r="C3698" t="n">
-        <v>883365.9</v>
+        <v>883369.6</v>
       </c>
       <c r="D3698" t="n">
-        <v>45932.1</v>
+        <v>45928.1</v>
       </c>
       <c r="E3698" t="n">
         <v>8187.5</v>
       </c>
       <c r="F3698" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3699">
@@ -78989,19 +79022,19 @@
         <v>46095</v>
       </c>
       <c r="B3699" t="n">
-        <v>899497.7</v>
+        <v>899497</v>
       </c>
       <c r="C3699" t="n">
-        <v>850519.7</v>
+        <v>850523.2</v>
       </c>
       <c r="D3699" t="n">
-        <v>40628.9</v>
+        <v>40624.7</v>
       </c>
       <c r="E3699" t="n">
-        <v>8349.200000000001</v>
+        <v>8349.1</v>
       </c>
       <c r="F3699" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3700">
@@ -79009,19 +79042,19 @@
         <v>46096</v>
       </c>
       <c r="B3700" t="n">
-        <v>823889.1</v>
+        <v>823888</v>
       </c>
       <c r="C3700" t="n">
-        <v>780963.9</v>
+        <v>780967.2</v>
       </c>
       <c r="D3700" t="n">
-        <v>34697.8</v>
+        <v>34693.3</v>
       </c>
       <c r="E3700" t="n">
         <v>8227.5</v>
       </c>
       <c r="F3700" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3701">
@@ -79029,19 +79062,19 @@
         <v>46097</v>
       </c>
       <c r="B3701" t="n">
-        <v>800932.9</v>
+        <v>800932.1</v>
       </c>
       <c r="C3701" t="n">
-        <v>755724.6</v>
+        <v>755727.8</v>
       </c>
       <c r="D3701" t="n">
-        <v>36903.1</v>
+        <v>36899</v>
       </c>
       <c r="E3701" t="n">
         <v>8305.200000000001</v>
       </c>
       <c r="F3701" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3702">
@@ -79049,19 +79082,19 @@
         <v>46098</v>
       </c>
       <c r="B3702" t="n">
-        <v>882648.4</v>
+        <v>882647.4</v>
       </c>
       <c r="C3702" t="n">
-        <v>826335.7</v>
+        <v>826338.8</v>
       </c>
       <c r="D3702" t="n">
-        <v>47579.6</v>
+        <v>47575.5</v>
       </c>
       <c r="E3702" t="n">
         <v>8733.1</v>
       </c>
       <c r="F3702" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3703">
@@ -79069,19 +79102,19 @@
         <v>46099</v>
       </c>
       <c r="B3703" t="n">
-        <v>916260.8</v>
+        <v>916238.1</v>
       </c>
       <c r="C3703" t="n">
-        <v>854626.8</v>
+        <v>854608.7</v>
       </c>
       <c r="D3703" t="n">
-        <v>52827.8</v>
+        <v>52823.2</v>
       </c>
       <c r="E3703" t="n">
         <v>8806.200000000001</v>
       </c>
       <c r="F3703" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3704">
@@ -79089,19 +79122,19 @@
         <v>46100</v>
       </c>
       <c r="B3704" t="n">
-        <v>930669.4</v>
+        <v>930668.6</v>
       </c>
       <c r="C3704" t="n">
-        <v>868218.2</v>
+        <v>868222.1</v>
       </c>
       <c r="D3704" t="n">
-        <v>53481.8</v>
+        <v>53477.1</v>
       </c>
       <c r="E3704" t="n">
         <v>8969.5</v>
       </c>
       <c r="F3704" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3705">
@@ -79109,19 +79142,19 @@
         <v>46101</v>
       </c>
       <c r="B3705" t="n">
-        <v>945494.4</v>
+        <v>945492.7</v>
       </c>
       <c r="C3705" t="n">
-        <v>880382.9</v>
+        <v>880388.6</v>
       </c>
       <c r="D3705" t="n">
-        <v>55696</v>
+        <v>55688.6</v>
       </c>
       <c r="E3705" t="n">
         <v>9415.5</v>
       </c>
       <c r="F3705" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3706">
@@ -79129,19 +79162,19 @@
         <v>46102</v>
       </c>
       <c r="B3706" t="n">
-        <v>905238</v>
+        <v>905254.3</v>
       </c>
       <c r="C3706" t="n">
-        <v>845005.4</v>
+        <v>845008.8</v>
       </c>
       <c r="D3706" t="n">
-        <v>50960.3</v>
+        <v>50973.3</v>
       </c>
       <c r="E3706" t="n">
         <v>9272.299999999999</v>
       </c>
       <c r="F3706" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3707">
@@ -79149,19 +79182,19 @@
         <v>46103</v>
       </c>
       <c r="B3707" t="n">
-        <v>830603.2</v>
+        <v>830610</v>
       </c>
       <c r="C3707" t="n">
-        <v>777060.3</v>
+        <v>777063.5</v>
       </c>
       <c r="D3707" t="n">
-        <v>44977.5</v>
+        <v>44981.1</v>
       </c>
       <c r="E3707" t="n">
         <v>8565.4</v>
       </c>
       <c r="F3707" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3708">
@@ -79169,19 +79202,19 @@
         <v>46104</v>
       </c>
       <c r="B3708" t="n">
-        <v>949431.6</v>
+        <v>949431.1</v>
       </c>
       <c r="C3708" t="n">
-        <v>890373.2</v>
+        <v>890377.8</v>
       </c>
       <c r="D3708" t="n">
-        <v>50008.5</v>
+        <v>50003.3</v>
       </c>
       <c r="E3708" t="n">
         <v>9049.9</v>
       </c>
       <c r="F3708" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3709">
@@ -79189,19 +79222,19 @@
         <v>46105</v>
       </c>
       <c r="B3709" t="n">
-        <v>979634.4</v>
+        <v>979633.6</v>
       </c>
       <c r="C3709" t="n">
-        <v>919476.1</v>
+        <v>919480.6</v>
       </c>
       <c r="D3709" t="n">
-        <v>50982.3</v>
+        <v>50977</v>
       </c>
       <c r="E3709" t="n">
         <v>9175.9</v>
       </c>
       <c r="F3709" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3710">
@@ -80809,19 +80842,19 @@
         <v>46186</v>
       </c>
       <c r="B3790" t="n">
-        <v>1064916.4</v>
+        <v>1064918.7</v>
       </c>
       <c r="C3790" t="n">
-        <v>993272.5</v>
+        <v>993267.4</v>
       </c>
       <c r="D3790" t="n">
-        <v>60968.9</v>
+        <v>60976.4</v>
       </c>
       <c r="E3790" t="n">
         <v>10674.9</v>
       </c>
       <c r="F3790" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3791">
@@ -80829,19 +80862,19 @@
         <v>46187</v>
       </c>
       <c r="B3791" t="n">
-        <v>988727.9</v>
+        <v>988565.1</v>
       </c>
       <c r="C3791" t="n">
-        <v>920715</v>
+        <v>920539.7</v>
       </c>
       <c r="D3791" t="n">
-        <v>57171.4</v>
+        <v>57183.9</v>
       </c>
       <c r="E3791" t="n">
         <v>10841.5</v>
       </c>
       <c r="F3791" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3792">
@@ -80849,19 +80882,19 @@
         <v>46188</v>
       </c>
       <c r="B3792" t="n">
-        <v>1082783</v>
+        <v>1082813.9</v>
       </c>
       <c r="C3792" t="n">
-        <v>1007089.5</v>
+        <v>1007076.3</v>
       </c>
       <c r="D3792" t="n">
-        <v>64032.5</v>
+        <v>64076.6</v>
       </c>
       <c r="E3792" t="n">
         <v>11660.9</v>
       </c>
       <c r="F3792" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3793">
@@ -80869,19 +80902,19 @@
         <v>46189</v>
       </c>
       <c r="B3793" t="n">
-        <v>1116146.3</v>
+        <v>1116085.3</v>
       </c>
       <c r="C3793" t="n">
-        <v>1035921.4</v>
+        <v>1035854.2</v>
       </c>
       <c r="D3793" t="n">
-        <v>68376.39999999999</v>
+        <v>68382.5</v>
       </c>
       <c r="E3793" t="n">
         <v>11848.6</v>
       </c>
       <c r="F3793" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3794">
@@ -80889,19 +80922,19 @@
         <v>46190</v>
       </c>
       <c r="B3794" t="n">
-        <v>1138546.5</v>
+        <v>1138437.1</v>
       </c>
       <c r="C3794" t="n">
-        <v>1061653.8</v>
+        <v>1061540.8</v>
       </c>
       <c r="D3794" t="n">
-        <v>65236.2</v>
+        <v>65239.8</v>
       </c>
       <c r="E3794" t="n">
         <v>11656.5</v>
       </c>
       <c r="F3794" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3795">
@@ -80909,19 +80942,19 @@
         <v>46191</v>
       </c>
       <c r="B3795" t="n">
-        <v>1150983.3</v>
+        <v>1150802.8</v>
       </c>
       <c r="C3795" t="n">
-        <v>1078660.4</v>
+        <v>1078477.4</v>
       </c>
       <c r="D3795" t="n">
-        <v>60992.7</v>
+        <v>60995.3</v>
       </c>
       <c r="E3795" t="n">
         <v>11330.2</v>
       </c>
       <c r="F3795" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3796">
@@ -80929,19 +80962,19 @@
         <v>46192</v>
       </c>
       <c r="B3796" t="n">
-        <v>1137717.4</v>
+        <v>1137630</v>
       </c>
       <c r="C3796" t="n">
-        <v>1067437.7</v>
+        <v>1067347.2</v>
       </c>
       <c r="D3796" t="n">
-        <v>58877.5</v>
+        <v>58880.7</v>
       </c>
       <c r="E3796" t="n">
         <v>11402.2</v>
       </c>
       <c r="F3796" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3797">
@@ -80949,19 +80982,19 @@
         <v>46193</v>
       </c>
       <c r="B3797" t="n">
-        <v>1061411.6</v>
+        <v>1061211.2</v>
       </c>
       <c r="C3797" t="n">
-        <v>996612</v>
+        <v>996395</v>
       </c>
       <c r="D3797" t="n">
-        <v>53167</v>
+        <v>53183.6</v>
       </c>
       <c r="E3797" t="n">
         <v>11632.6</v>
       </c>
       <c r="F3797" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3798">
@@ -80969,19 +81002,19 @@
         <v>46194</v>
       </c>
       <c r="B3798" t="n">
-        <v>974554.9</v>
+        <v>974132.5</v>
       </c>
       <c r="C3798" t="n">
-        <v>914042</v>
+        <v>913616.2</v>
       </c>
       <c r="D3798" t="n">
-        <v>49214.5</v>
+        <v>49218</v>
       </c>
       <c r="E3798" t="n">
         <v>11298.3</v>
       </c>
       <c r="F3798" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3799">
@@ -80989,19 +81022,19 @@
         <v>46195</v>
       </c>
       <c r="B3799" t="n">
-        <v>1115796.1</v>
+        <v>1115656.2</v>
       </c>
       <c r="C3799" t="n">
-        <v>1046126.6</v>
+        <v>1045984.7</v>
       </c>
       <c r="D3799" t="n">
-        <v>57569.6</v>
+        <v>57571.6</v>
       </c>
       <c r="E3799" t="n">
         <v>12099.9</v>
       </c>
       <c r="F3799" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3800">
@@ -81009,19 +81042,19 @@
         <v>46196</v>
       </c>
       <c r="B3800" t="n">
-        <v>1142594.5</v>
+        <v>1142988.4</v>
       </c>
       <c r="C3800" t="n">
-        <v>1067817.7</v>
+        <v>1068207.6</v>
       </c>
       <c r="D3800" t="n">
-        <v>61662.4</v>
+        <v>61666.4</v>
       </c>
       <c r="E3800" t="n">
         <v>13114.4</v>
       </c>
       <c r="F3800" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3801">
@@ -81029,19 +81062,19 @@
         <v>46197</v>
       </c>
       <c r="B3801" t="n">
-        <v>1150314.4</v>
+        <v>1150444.2</v>
       </c>
       <c r="C3801" t="n">
-        <v>1071737.3</v>
+        <v>1071863.2</v>
       </c>
       <c r="D3801" t="n">
-        <v>64763.3</v>
+        <v>64767.3</v>
       </c>
       <c r="E3801" t="n">
         <v>13813.7</v>
       </c>
       <c r="F3801" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3802">
@@ -81049,19 +81082,19 @@
         <v>46198</v>
       </c>
       <c r="B3802" t="n">
-        <v>1153479.1</v>
+        <v>1153519.9</v>
       </c>
       <c r="C3802" t="n">
-        <v>1075162.1</v>
+        <v>1075203.5</v>
       </c>
       <c r="D3802" t="n">
-        <v>64399.5</v>
+        <v>64403.4</v>
       </c>
       <c r="E3802" t="n">
-        <v>13917.5</v>
+        <v>13913</v>
       </c>
       <c r="F3802" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3803">
@@ -81069,19 +81102,19 @@
         <v>46199</v>
       </c>
       <c r="B3803" t="n">
-        <v>1147551.5</v>
+        <v>1147608.5</v>
       </c>
       <c r="C3803" t="n">
-        <v>1072650</v>
+        <v>1072702.9</v>
       </c>
       <c r="D3803" t="n">
-        <v>61506.1</v>
+        <v>61510.1</v>
       </c>
       <c r="E3803" t="n">
         <v>13395.4</v>
       </c>
       <c r="F3803" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3804">
@@ -81089,19 +81122,19 @@
         <v>46200</v>
       </c>
       <c r="B3804" t="n">
-        <v>1094007.6</v>
+        <v>1093949.1</v>
       </c>
       <c r="C3804" t="n">
-        <v>1025712.3</v>
+        <v>1025649.8</v>
       </c>
       <c r="D3804" t="n">
-        <v>55165.7</v>
+        <v>55169.7</v>
       </c>
       <c r="E3804" t="n">
         <v>13129.6</v>
       </c>
       <c r="F3804" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3805">
@@ -81109,19 +81142,19 @@
         <v>46201</v>
       </c>
       <c r="B3805" t="n">
-        <v>1008296.8</v>
+        <v>1008250.8</v>
       </c>
       <c r="C3805" t="n">
-        <v>947047.8</v>
+        <v>946999.8</v>
       </c>
       <c r="D3805" t="n">
-        <v>48134.3</v>
+        <v>48136.3</v>
       </c>
       <c r="E3805" t="n">
         <v>13114.7</v>
       </c>
       <c r="F3805" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3806">
@@ -81129,19 +81162,19 @@
         <v>46202</v>
       </c>
       <c r="B3806" t="n">
-        <v>1112400.9</v>
+        <v>1112477.7</v>
       </c>
       <c r="C3806" t="n">
-        <v>1045185.7</v>
+        <v>1045260.1</v>
       </c>
       <c r="D3806" t="n">
-        <v>53566.9</v>
+        <v>53568.9</v>
       </c>
       <c r="E3806" t="n">
-        <v>13648.4</v>
+        <v>13648.7</v>
       </c>
       <c r="F3806" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3807">
@@ -81149,19 +81182,19 @@
         <v>46203</v>
       </c>
       <c r="B3807" t="n">
-        <v>1128448.2</v>
+        <v>1128878.7</v>
       </c>
       <c r="C3807" t="n">
-        <v>1060199.5</v>
+        <v>1060634</v>
       </c>
       <c r="D3807" t="n">
-        <v>54550.3</v>
+        <v>54545.9</v>
       </c>
       <c r="E3807" t="n">
-        <v>13698.4</v>
+        <v>13698.8</v>
       </c>
       <c r="F3807" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3808">
@@ -81169,19 +81202,19 @@
         <v>46204</v>
       </c>
       <c r="B3808" t="n">
-        <v>1121715.1</v>
+        <v>1121398.3</v>
       </c>
       <c r="C3808" t="n">
-        <v>1051350</v>
+        <v>1051051</v>
       </c>
       <c r="D3808" t="n">
-        <v>56677</v>
+        <v>56650</v>
       </c>
       <c r="E3808" t="n">
-        <v>13688.1</v>
+        <v>13697.3</v>
       </c>
       <c r="F3808" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3809">
@@ -81189,19 +81222,19 @@
         <v>46205</v>
       </c>
       <c r="B3809" t="n">
-        <v>1121379.5</v>
+        <v>1121054.8</v>
       </c>
       <c r="C3809" t="n">
-        <v>1050497.3</v>
+        <v>1050199.3</v>
       </c>
       <c r="D3809" t="n">
-        <v>57432.7</v>
+        <v>57405.8</v>
       </c>
       <c r="E3809" t="n">
-        <v>13449.5</v>
+        <v>13449.8</v>
       </c>
       <c r="F3809" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3810">
@@ -81209,19 +81242,19 @@
         <v>46206</v>
       </c>
       <c r="B3810" t="n">
-        <v>1130478.4</v>
+        <v>1130020.1</v>
       </c>
       <c r="C3810" t="n">
-        <v>1059798.1</v>
+        <v>1059364.9</v>
       </c>
       <c r="D3810" t="n">
-        <v>57049.5</v>
+        <v>57024.3</v>
       </c>
       <c r="E3810" t="n">
-        <v>13630.8</v>
+        <v>13630.9</v>
       </c>
       <c r="F3810" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3811">
@@ -81229,19 +81262,19 @@
         <v>46207</v>
       </c>
       <c r="B3811" t="n">
-        <v>1094763.3</v>
+        <v>1094412</v>
       </c>
       <c r="C3811" t="n">
-        <v>1025852.5</v>
+        <v>1025527.8</v>
       </c>
       <c r="D3811" t="n">
-        <v>55365.7</v>
+        <v>55338.8</v>
       </c>
       <c r="E3811" t="n">
-        <v>13545</v>
+        <v>13545.4</v>
       </c>
       <c r="F3811" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3812">
@@ -81249,19 +81282,19 @@
         <v>46208</v>
       </c>
       <c r="B3812" t="n">
-        <v>1023864.2</v>
+        <v>1023560.5</v>
       </c>
       <c r="C3812" t="n">
-        <v>955112.4</v>
+        <v>954835.3</v>
       </c>
       <c r="D3812" t="n">
-        <v>55588.5</v>
+        <v>55561</v>
       </c>
       <c r="E3812" t="n">
-        <v>13163.4</v>
+        <v>13164.3</v>
       </c>
       <c r="F3812" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3813">
@@ -81269,19 +81302,19 @@
         <v>46209</v>
       </c>
       <c r="B3813" t="n">
-        <v>1127408.8</v>
+        <v>1127022.7</v>
       </c>
       <c r="C3813" t="n">
-        <v>1051774.3</v>
+        <v>1051413.8</v>
       </c>
       <c r="D3813" t="n">
-        <v>62065.1</v>
+        <v>62038.8</v>
       </c>
       <c r="E3813" t="n">
-        <v>13569.3</v>
+        <v>13570.1</v>
       </c>
       <c r="F3813" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3814">
@@ -81289,19 +81322,19 @@
         <v>46210</v>
       </c>
       <c r="B3814" t="n">
-        <v>1137307.6</v>
+        <v>1137181.6</v>
       </c>
       <c r="C3814" t="n">
-        <v>1058290</v>
+        <v>1058134.5</v>
       </c>
       <c r="D3814" t="n">
-        <v>65267.3</v>
+        <v>65240.2</v>
       </c>
       <c r="E3814" t="n">
-        <v>13750.3</v>
+        <v>13807</v>
       </c>
       <c r="F3814" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3815">
@@ -81929,19 +81962,19 @@
         <v>46242</v>
       </c>
       <c r="B3846" t="n">
-        <v>1097405.7</v>
+        <v>1097754.9</v>
       </c>
       <c r="C3846" t="n">
-        <v>1015501.3</v>
+        <v>1015798.7</v>
       </c>
       <c r="D3846" t="n">
-        <v>68094</v>
+        <v>68156.2</v>
       </c>
       <c r="E3846" t="n">
-        <v>13810.3</v>
+        <v>13800</v>
       </c>
       <c r="F3846" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3847">
@@ -81949,19 +81982,19 @@
         <v>46243</v>
       </c>
       <c r="B3847" t="n">
-        <v>1011821.5</v>
+        <v>1011766.7</v>
       </c>
       <c r="C3847" t="n">
-        <v>933207.4</v>
+        <v>933141</v>
       </c>
       <c r="D3847" t="n">
-        <v>65485</v>
+        <v>65501.8</v>
       </c>
       <c r="E3847" t="n">
-        <v>13129</v>
+        <v>13123.9</v>
       </c>
       <c r="F3847" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3848">
@@ -81969,19 +82002,19 @@
         <v>46244</v>
       </c>
       <c r="B3848" t="n">
-        <v>1128799.8</v>
+        <v>1129735.8</v>
       </c>
       <c r="C3848" t="n">
-        <v>1045420.3</v>
+        <v>1046273.5</v>
       </c>
       <c r="D3848" t="n">
-        <v>69958.3</v>
+        <v>70060</v>
       </c>
       <c r="E3848" t="n">
-        <v>13421.2</v>
+        <v>13402.2</v>
       </c>
       <c r="F3848" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3849">
@@ -81989,19 +82022,19 @@
         <v>46245</v>
       </c>
       <c r="B3849" t="n">
-        <v>1158343.3</v>
+        <v>1159558.7</v>
       </c>
       <c r="C3849" t="n">
-        <v>1075219.1</v>
+        <v>1076379.6</v>
       </c>
       <c r="D3849" t="n">
-        <v>69507.5</v>
+        <v>69574.7</v>
       </c>
       <c r="E3849" t="n">
-        <v>13616.7</v>
+        <v>13604.3</v>
       </c>
       <c r="F3849" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3850">
@@ -82009,19 +82042,19 @@
         <v>46246</v>
       </c>
       <c r="B3850" t="n">
-        <v>1158672.3</v>
+        <v>1157744.8</v>
       </c>
       <c r="C3850" t="n">
-        <v>1077923</v>
+        <v>1077017.5</v>
       </c>
       <c r="D3850" t="n">
-        <v>66772.10000000001</v>
+        <v>66762.5</v>
       </c>
       <c r="E3850" t="n">
-        <v>13977.2</v>
+        <v>13964.9</v>
       </c>
       <c r="F3850" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3851">
@@ -82029,19 +82062,19 @@
         <v>46247</v>
       </c>
       <c r="B3851" t="n">
-        <v>1169797.9</v>
+        <v>1170343</v>
       </c>
       <c r="C3851" t="n">
-        <v>1092262.3</v>
+        <v>1092208.3</v>
       </c>
       <c r="D3851" t="n">
-        <v>63275.1</v>
+        <v>63889.3</v>
       </c>
       <c r="E3851" t="n">
-        <v>14260.5</v>
+        <v>14245.4</v>
       </c>
       <c r="F3851" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3852">
@@ -82049,19 +82082,19 @@
         <v>46248</v>
       </c>
       <c r="B3852" t="n">
-        <v>1167559.9</v>
+        <v>1167571</v>
       </c>
       <c r="C3852" t="n">
-        <v>1089522.5</v>
+        <v>1089523.5</v>
       </c>
       <c r="D3852" t="n">
-        <v>63694.5</v>
+        <v>63710.5</v>
       </c>
       <c r="E3852" t="n">
-        <v>14343</v>
+        <v>14337</v>
       </c>
       <c r="F3852" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3853">
@@ -82069,19 +82102,19 @@
         <v>46249</v>
       </c>
       <c r="B3853" t="n">
-        <v>1118236.7</v>
+        <v>1118596.4</v>
       </c>
       <c r="C3853" t="n">
-        <v>1040681.1</v>
+        <v>1041067.2</v>
       </c>
       <c r="D3853" t="n">
-        <v>62944.7</v>
+        <v>62949.1</v>
       </c>
       <c r="E3853" t="n">
-        <v>14610.8</v>
+        <v>14580.1</v>
       </c>
       <c r="F3853" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3854">
@@ -82089,19 +82122,19 @@
         <v>46250</v>
       </c>
       <c r="B3854" t="n">
-        <v>1033191.6</v>
+        <v>1034003.6</v>
       </c>
       <c r="C3854" t="n">
-        <v>957694.4</v>
+        <v>958517.7</v>
       </c>
       <c r="D3854" t="n">
-        <v>60729.9</v>
+        <v>60755.3</v>
       </c>
       <c r="E3854" t="n">
-        <v>14767.4</v>
+        <v>14730.6</v>
       </c>
       <c r="F3854" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3855">
@@ -82109,19 +82142,19 @@
         <v>46251</v>
       </c>
       <c r="B3855" t="n">
-        <v>1148936.9</v>
+        <v>1148471</v>
       </c>
       <c r="C3855" t="n">
-        <v>1064912.3</v>
+        <v>1064398.8</v>
       </c>
       <c r="D3855" t="n">
-        <v>68871</v>
+        <v>68934.8</v>
       </c>
       <c r="E3855" t="n">
-        <v>15153.6</v>
+        <v>15137.4</v>
       </c>
       <c r="F3855" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3856">
@@ -82129,19 +82162,19 @@
         <v>46252</v>
       </c>
       <c r="B3856" t="n">
-        <v>1161985</v>
+        <v>1161416.8</v>
       </c>
       <c r="C3856" t="n">
-        <v>1077171.8</v>
+        <v>1076572.1</v>
       </c>
       <c r="D3856" t="n">
-        <v>71873.89999999999</v>
+        <v>71907.2</v>
       </c>
       <c r="E3856" t="n">
-        <v>12939.3</v>
+        <v>12937.5</v>
       </c>
       <c r="F3856" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3857">
@@ -82149,19 +82182,19 @@
         <v>46253</v>
       </c>
       <c r="B3857" t="n">
-        <v>1179396.1</v>
+        <v>1178901.7</v>
       </c>
       <c r="C3857" t="n">
-        <v>1093682.1</v>
+        <v>1093100.1</v>
       </c>
       <c r="D3857" t="n">
-        <v>72144</v>
+        <v>72249.39999999999</v>
       </c>
       <c r="E3857" t="n">
-        <v>13569.9</v>
+        <v>13552.1</v>
       </c>
       <c r="F3857" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3858">
@@ -82169,19 +82202,19 @@
         <v>46254</v>
       </c>
       <c r="B3858" t="n">
-        <v>1189606.8</v>
+        <v>1189454.2</v>
       </c>
       <c r="C3858" t="n">
-        <v>1107754.9</v>
+        <v>1107663.3</v>
       </c>
       <c r="D3858" t="n">
-        <v>67452.8</v>
+        <v>67419.10000000001</v>
       </c>
       <c r="E3858" t="n">
-        <v>14399.2</v>
+        <v>14371.8</v>
       </c>
       <c r="F3858" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3859">
@@ -82189,19 +82222,19 @@
         <v>46255</v>
       </c>
       <c r="B3859" t="n">
-        <v>1202802.1</v>
+        <v>1201827.1</v>
       </c>
       <c r="C3859" t="n">
-        <v>1119116.4</v>
+        <v>1118087.5</v>
       </c>
       <c r="D3859" t="n">
-        <v>68763.60000000001</v>
+        <v>68843.60000000001</v>
       </c>
       <c r="E3859" t="n">
-        <v>14922.1</v>
+        <v>14896</v>
       </c>
       <c r="F3859" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3860">
@@ -82209,19 +82242,19 @@
         <v>46256</v>
       </c>
       <c r="B3860" t="n">
-        <v>1138945.7</v>
+        <v>1139826.2</v>
       </c>
       <c r="C3860" t="n">
-        <v>1054994.9</v>
+        <v>1055889.7</v>
       </c>
       <c r="D3860" t="n">
-        <v>68840.3</v>
+        <v>68851.8</v>
       </c>
       <c r="E3860" t="n">
-        <v>15110.5</v>
+        <v>15084.6</v>
       </c>
       <c r="F3860" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3861">
@@ -82229,19 +82262,19 @@
         <v>46257</v>
       </c>
       <c r="B3861" t="n">
-        <v>1028749.7</v>
+        <v>1028709.4</v>
       </c>
       <c r="C3861" t="n">
-        <v>949295.5</v>
+        <v>949289.9</v>
       </c>
       <c r="D3861" t="n">
-        <v>65582.60000000001</v>
+        <v>65568.8</v>
       </c>
       <c r="E3861" t="n">
-        <v>13871.7</v>
+        <v>13850.8</v>
       </c>
       <c r="F3861" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3862">
@@ -82249,19 +82282,19 @@
         <v>46258</v>
       </c>
       <c r="B3862" t="n">
-        <v>1147222.9</v>
+        <v>1145373.4</v>
       </c>
       <c r="C3862" t="n">
-        <v>1061595.7</v>
+        <v>1059682.1</v>
       </c>
       <c r="D3862" t="n">
-        <v>71798.39999999999</v>
+        <v>71885.3</v>
       </c>
       <c r="E3862" t="n">
-        <v>13828.8</v>
+        <v>13805.9</v>
       </c>
       <c r="F3862" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3863">
@@ -82269,19 +82302,19 @@
         <v>46259</v>
       </c>
       <c r="B3863" t="n">
-        <v>1185369.1</v>
+        <v>1185269</v>
       </c>
       <c r="C3863" t="n">
-        <v>1097985.6</v>
+        <v>1097832.4</v>
       </c>
       <c r="D3863" t="n">
-        <v>74210.7</v>
+        <v>74281.10000000001</v>
       </c>
       <c r="E3863" t="n">
-        <v>13172.8</v>
+        <v>13155.5</v>
       </c>
       <c r="F3863" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3864">
@@ -82289,19 +82322,19 @@
         <v>46260</v>
       </c>
       <c r="B3864" t="n">
-        <v>1196679.6</v>
+        <v>1195293.6</v>
       </c>
       <c r="C3864" t="n">
-        <v>1107614.2</v>
+        <v>1106307.7</v>
       </c>
       <c r="D3864" t="n">
-        <v>75397.89999999999</v>
+        <v>75339.89999999999</v>
       </c>
       <c r="E3864" t="n">
-        <v>13667.5</v>
+        <v>13646</v>
       </c>
       <c r="F3864" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3865">
@@ -82309,19 +82342,19 @@
         <v>46261</v>
       </c>
       <c r="B3865" t="n">
-        <v>1203502.1</v>
+        <v>1201946.4</v>
       </c>
       <c r="C3865" t="n">
-        <v>1112727.8</v>
+        <v>1111041.7</v>
       </c>
       <c r="D3865" t="n">
-        <v>76028.7</v>
+        <v>76190.89999999999</v>
       </c>
       <c r="E3865" t="n">
-        <v>14745.6</v>
+        <v>14713.8</v>
       </c>
       <c r="F3865" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3866">
@@ -82329,19 +82362,19 @@
         <v>46262</v>
       </c>
       <c r="B3866" t="n">
-        <v>1202302.1</v>
+        <v>1202199.8</v>
       </c>
       <c r="C3866" t="n">
-        <v>1113838.9</v>
+        <v>1113393.2</v>
       </c>
       <c r="D3866" t="n">
-        <v>73172.60000000001</v>
+        <v>73548.8</v>
       </c>
       <c r="E3866" t="n">
-        <v>15290.6</v>
+        <v>15257.8</v>
       </c>
       <c r="F3866" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3867">
@@ -82349,19 +82382,19 @@
         <v>46263</v>
       </c>
       <c r="B3867" t="n">
-        <v>1137185.1</v>
+        <v>1137103.5</v>
       </c>
       <c r="C3867" t="n">
-        <v>1053396.3</v>
+        <v>1052581.3</v>
       </c>
       <c r="D3867" t="n">
-        <v>69227</v>
+        <v>69988.2</v>
       </c>
       <c r="E3867" t="n">
-        <v>14561.8</v>
+        <v>14534.1</v>
       </c>
       <c r="F3867" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3868">
@@ -82369,19 +82402,19 @@
         <v>46264</v>
       </c>
       <c r="B3868" t="n">
-        <v>1045930.4</v>
+        <v>1045998.2</v>
       </c>
       <c r="C3868" t="n">
-        <v>967819.7</v>
+        <v>967289.1</v>
       </c>
       <c r="D3868" t="n">
-        <v>64374.8</v>
+        <v>65002.7</v>
       </c>
       <c r="E3868" t="n">
-        <v>13736</v>
+        <v>13706.4</v>
       </c>
       <c r="F3868" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3869">
@@ -82389,19 +82422,19 @@
         <v>46265</v>
       </c>
       <c r="B3869" t="n">
-        <v>1139524.8</v>
+        <v>1138435.1</v>
       </c>
       <c r="C3869" t="n">
-        <v>1059590.7</v>
+        <v>1058519.1</v>
       </c>
       <c r="D3869" t="n">
-        <v>66758.60000000001</v>
+        <v>66770.89999999999</v>
       </c>
       <c r="E3869" t="n">
-        <v>13175.5</v>
+        <v>13145.1</v>
       </c>
       <c r="F3869" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3870">
@@ -82409,19 +82442,19 @@
         <v>46266</v>
       </c>
       <c r="B3870" t="n">
-        <v>1167798.5</v>
+        <v>1168188.3</v>
       </c>
       <c r="C3870" t="n">
-        <v>1088814.2</v>
+        <v>1089234.1</v>
       </c>
       <c r="D3870" t="n">
-        <v>66342.7</v>
+        <v>66369.2</v>
       </c>
       <c r="E3870" t="n">
-        <v>12641.6</v>
+        <v>12584.9</v>
       </c>
       <c r="F3870" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3871">
@@ -82761,6 +82794,506 @@
         <v>13434.5</v>
       </c>
       <c r="F3887" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3888">
+      <c r="A3888" s="4" t="n">
+        <v>46284</v>
+      </c>
+      <c r="B3888" t="n">
+        <v>1055095.1</v>
+      </c>
+      <c r="C3888" t="n">
+        <v>989094</v>
+      </c>
+      <c r="D3888" t="n">
+        <v>52530.2</v>
+      </c>
+      <c r="E3888" t="n">
+        <v>13470.9</v>
+      </c>
+      <c r="F3888" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3889">
+      <c r="A3889" s="4" t="n">
+        <v>46285</v>
+      </c>
+      <c r="B3889" t="n">
+        <v>989496.3</v>
+      </c>
+      <c r="C3889" t="n">
+        <v>925639.3</v>
+      </c>
+      <c r="D3889" t="n">
+        <v>50709.2</v>
+      </c>
+      <c r="E3889" t="n">
+        <v>13147.8</v>
+      </c>
+      <c r="F3889" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3890">
+      <c r="A3890" s="4" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B3890" t="n">
+        <v>1106212.5</v>
+      </c>
+      <c r="C3890" t="n">
+        <v>1033536.2</v>
+      </c>
+      <c r="D3890" t="n">
+        <v>59314.7</v>
+      </c>
+      <c r="E3890" t="n">
+        <v>13361.6</v>
+      </c>
+      <c r="F3890" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3891">
+      <c r="A3891" s="4" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B3891" t="n">
+        <v>1115781.1</v>
+      </c>
+      <c r="C3891" t="n">
+        <v>1045812.4</v>
+      </c>
+      <c r="D3891" t="n">
+        <v>56875.3</v>
+      </c>
+      <c r="E3891" t="n">
+        <v>13093.4</v>
+      </c>
+      <c r="F3891" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3892">
+      <c r="A3892" s="4" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B3892" t="n">
+        <v>1095929.2</v>
+      </c>
+      <c r="C3892" t="n">
+        <v>1024914.4</v>
+      </c>
+      <c r="D3892" t="n">
+        <v>58145.4</v>
+      </c>
+      <c r="E3892" t="n">
+        <v>12869.4</v>
+      </c>
+      <c r="F3892" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3893">
+      <c r="A3893" s="4" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B3893" t="n">
+        <v>1094193.4</v>
+      </c>
+      <c r="C3893" t="n">
+        <v>1022493.8</v>
+      </c>
+      <c r="D3893" t="n">
+        <v>58295.3</v>
+      </c>
+      <c r="E3893" t="n">
+        <v>13404.3</v>
+      </c>
+      <c r="F3893" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3894">
+      <c r="A3894" s="4" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B3894" t="n">
+        <v>1098763.1</v>
+      </c>
+      <c r="C3894" t="n">
+        <v>1027618.4</v>
+      </c>
+      <c r="D3894" t="n">
+        <v>57998.9</v>
+      </c>
+      <c r="E3894" t="n">
+        <v>13145.8</v>
+      </c>
+      <c r="F3894" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3895">
+      <c r="A3895" s="4" t="n">
+        <v>46291</v>
+      </c>
+      <c r="B3895" t="n">
+        <v>1055194.1</v>
+      </c>
+      <c r="C3895" t="n">
+        <v>984513.4</v>
+      </c>
+      <c r="D3895" t="n">
+        <v>57666.2</v>
+      </c>
+      <c r="E3895" t="n">
+        <v>13014.6</v>
+      </c>
+      <c r="F3895" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3896">
+      <c r="A3896" s="4" t="n">
+        <v>46292</v>
+      </c>
+      <c r="B3896" t="n">
+        <v>975967.5</v>
+      </c>
+      <c r="C3896" t="n">
+        <v>914314.7</v>
+      </c>
+      <c r="D3896" t="n">
+        <v>48977.4</v>
+      </c>
+      <c r="E3896" t="n">
+        <v>12675.4</v>
+      </c>
+      <c r="F3896" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3897">
+      <c r="A3897" s="4" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B3897" t="n">
+        <v>1077505.5</v>
+      </c>
+      <c r="C3897" t="n">
+        <v>1016035.1</v>
+      </c>
+      <c r="D3897" t="n">
+        <v>49105.7</v>
+      </c>
+      <c r="E3897" t="n">
+        <v>12364.7</v>
+      </c>
+      <c r="F3897" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3898">
+      <c r="A3898" s="4" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B3898" t="n">
+        <v>1094935.9</v>
+      </c>
+      <c r="C3898" t="n">
+        <v>1032830.3</v>
+      </c>
+      <c r="D3898" t="n">
+        <v>49766.8</v>
+      </c>
+      <c r="E3898" t="n">
+        <v>12338.9</v>
+      </c>
+      <c r="F3898" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3899">
+      <c r="A3899" s="4" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B3899" t="n">
+        <v>1092257.1</v>
+      </c>
+      <c r="C3899" t="n">
+        <v>1025362.4</v>
+      </c>
+      <c r="D3899" t="n">
+        <v>54322.2</v>
+      </c>
+      <c r="E3899" t="n">
+        <v>12572.5</v>
+      </c>
+      <c r="F3899" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3900">
+      <c r="A3900" s="4" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B3900" t="n">
+        <v>1072835.5</v>
+      </c>
+      <c r="C3900" t="n">
+        <v>1005841.2</v>
+      </c>
+      <c r="D3900" t="n">
+        <v>54889.3</v>
+      </c>
+      <c r="E3900" t="n">
+        <v>12105</v>
+      </c>
+      <c r="F3900" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3901">
+      <c r="A3901" s="4" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B3901" t="n">
+        <v>1048732.9</v>
+      </c>
+      <c r="C3901" t="n">
+        <v>973649.1</v>
+      </c>
+      <c r="D3901" t="n">
+        <v>63245.6</v>
+      </c>
+      <c r="E3901" t="n">
+        <v>11838.2</v>
+      </c>
+      <c r="F3901" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3902">
+      <c r="A3902" s="4" t="n">
+        <v>46298</v>
+      </c>
+      <c r="B3902" t="n">
+        <v>987608.8</v>
+      </c>
+      <c r="C3902" t="n">
+        <v>911709.2</v>
+      </c>
+      <c r="D3902" t="n">
+        <v>63883.9</v>
+      </c>
+      <c r="E3902" t="n">
+        <v>12015.7</v>
+      </c>
+      <c r="F3902" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3903">
+      <c r="A3903" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B3903" t="n">
+        <v>905666</v>
+      </c>
+      <c r="C3903" t="n">
+        <v>833263.1</v>
+      </c>
+      <c r="D3903" t="n">
+        <v>61311.6</v>
+      </c>
+      <c r="E3903" t="n">
+        <v>11091.2</v>
+      </c>
+      <c r="F3903" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3904">
+      <c r="A3904" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B3904" t="n">
+        <v>1000735.3</v>
+      </c>
+      <c r="C3904" t="n">
+        <v>923551.2</v>
+      </c>
+      <c r="D3904" t="n">
+        <v>65602.39999999999</v>
+      </c>
+      <c r="E3904" t="n">
+        <v>11581.6</v>
+      </c>
+      <c r="F3904" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3905">
+      <c r="A3905" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B3905" t="n">
+        <v>1041605.3</v>
+      </c>
+      <c r="C3905" t="n">
+        <v>964520.4</v>
+      </c>
+      <c r="D3905" t="n">
+        <v>64829.2</v>
+      </c>
+      <c r="E3905" t="n">
+        <v>12255.7</v>
+      </c>
+      <c r="F3905" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3906">
+      <c r="A3906" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B3906" t="n">
+        <v>1061425.2</v>
+      </c>
+      <c r="C3906" t="n">
+        <v>984337.1</v>
+      </c>
+      <c r="D3906" t="n">
+        <v>64297.6</v>
+      </c>
+      <c r="E3906" t="n">
+        <v>12790.5</v>
+      </c>
+      <c r="F3906" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3907">
+      <c r="A3907" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B3907" t="n">
+        <v>1064700</v>
+      </c>
+      <c r="C3907" t="n">
+        <v>987207.5</v>
+      </c>
+      <c r="D3907" t="n">
+        <v>63927</v>
+      </c>
+      <c r="E3907" t="n">
+        <v>13565.5</v>
+      </c>
+      <c r="F3907" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3908">
+      <c r="A3908" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B3908" t="n">
+        <v>1053505.9</v>
+      </c>
+      <c r="C3908" t="n">
+        <v>977351</v>
+      </c>
+      <c r="D3908" t="n">
+        <v>62253.2</v>
+      </c>
+      <c r="E3908" t="n">
+        <v>13901.6</v>
+      </c>
+      <c r="F3908" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3909">
+      <c r="A3909" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B3909" t="n">
+        <v>989738.9</v>
+      </c>
+      <c r="C3909" t="n">
+        <v>926128</v>
+      </c>
+      <c r="D3909" t="n">
+        <v>50339.4</v>
+      </c>
+      <c r="E3909" t="n">
+        <v>13271.5</v>
+      </c>
+      <c r="F3909" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3910">
+      <c r="A3910" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B3910" t="n">
+        <v>897828.1</v>
+      </c>
+      <c r="C3910" t="n">
+        <v>848460.6</v>
+      </c>
+      <c r="D3910" t="n">
+        <v>36988.3</v>
+      </c>
+      <c r="E3910" t="n">
+        <v>12379.2</v>
+      </c>
+      <c r="F3910" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3911">
+      <c r="A3911" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B3911" t="n">
+        <v>1014971.2</v>
+      </c>
+      <c r="C3911" t="n">
+        <v>961263.5</v>
+      </c>
+      <c r="D3911" t="n">
+        <v>41485.5</v>
+      </c>
+      <c r="E3911" t="n">
+        <v>12222.2</v>
+      </c>
+      <c r="F3911" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3912">
+      <c r="A3912" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B3912" t="n">
+        <v>1054324.5</v>
+      </c>
+      <c r="C3912" t="n">
+        <v>1000642.9</v>
+      </c>
+      <c r="D3912" t="n">
+        <v>41358.8</v>
+      </c>
+      <c r="E3912" t="n">
+        <v>12322.8</v>
+      </c>
+      <c r="F3912" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
+++ b/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,12 +61,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -623,7 +624,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -638,7 +638,6 @@
         </is>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -653,7 +652,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -668,7 +666,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -713,7 +710,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>42394</v>
       </c>
       <c r="B2" t="n">
@@ -721,7 +718,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>42401</v>
       </c>
       <c r="B3" t="n">
@@ -729,7 +726,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>42408</v>
       </c>
       <c r="B4" t="n">
@@ -737,7 +734,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>42415</v>
       </c>
       <c r="B5" t="n">
@@ -745,7 +742,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="5" t="n">
         <v>42422</v>
       </c>
       <c r="B6" t="n">
@@ -753,7 +750,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="5" t="n">
         <v>42429</v>
       </c>
       <c r="B7" t="n">
@@ -761,7 +758,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="5" t="n">
         <v>42436</v>
       </c>
       <c r="B8" t="n">
@@ -769,7 +766,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="5" t="n">
         <v>42443</v>
       </c>
       <c r="B9" t="n">
@@ -777,7 +774,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="5" t="n">
         <v>42450</v>
       </c>
       <c r="B10" t="n">
@@ -785,7 +782,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="5" t="n">
         <v>42457</v>
       </c>
       <c r="B11" t="n">
@@ -793,7 +790,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="5" t="n">
         <v>42464</v>
       </c>
       <c r="B12" t="n">
@@ -801,7 +798,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="5" t="n">
         <v>42471</v>
       </c>
       <c r="B13" t="n">
@@ -809,7 +806,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="5" t="n">
         <v>42478</v>
       </c>
       <c r="B14" t="n">
@@ -817,7 +814,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="5" t="n">
         <v>42485</v>
       </c>
       <c r="B15" t="n">
@@ -825,7 +822,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="5" t="n">
         <v>42492</v>
       </c>
       <c r="B16" t="n">
@@ -833,7 +830,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="n">
+      <c r="A17" s="5" t="n">
         <v>42499</v>
       </c>
       <c r="B17" t="n">
@@ -841,7 +838,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="n">
+      <c r="A18" s="5" t="n">
         <v>42506</v>
       </c>
       <c r="B18" t="n">
@@ -849,7 +846,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="n">
+      <c r="A19" s="5" t="n">
         <v>42513</v>
       </c>
       <c r="B19" t="n">
@@ -857,7 +854,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="n">
+      <c r="A20" s="5" t="n">
         <v>42520</v>
       </c>
       <c r="B20" t="n">
@@ -865,7 +862,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="n">
+      <c r="A21" s="5" t="n">
         <v>42527</v>
       </c>
       <c r="B21" t="n">
@@ -873,7 +870,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="n">
+      <c r="A22" s="5" t="n">
         <v>42534</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +878,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="n">
+      <c r="A23" s="5" t="n">
         <v>42541</v>
       </c>
       <c r="B23" t="n">
@@ -889,7 +886,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="n">
+      <c r="A24" s="5" t="n">
         <v>42548</v>
       </c>
       <c r="B24" t="n">
@@ -897,7 +894,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="n">
+      <c r="A25" s="5" t="n">
         <v>42555</v>
       </c>
       <c r="B25" t="n">
@@ -905,7 +902,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="n">
+      <c r="A26" s="5" t="n">
         <v>42562</v>
       </c>
       <c r="B26" t="n">
@@ -913,7 +910,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="n">
+      <c r="A27" s="5" t="n">
         <v>42569</v>
       </c>
       <c r="B27" t="n">
@@ -921,7 +918,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="n">
+      <c r="A28" s="5" t="n">
         <v>42576</v>
       </c>
       <c r="B28" t="n">
@@ -929,7 +926,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="n">
+      <c r="A29" s="5" t="n">
         <v>42583</v>
       </c>
       <c r="B29" t="n">
@@ -937,7 +934,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="n">
+      <c r="A30" s="5" t="n">
         <v>42590</v>
       </c>
       <c r="B30" t="n">
@@ -945,7 +942,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="n">
+      <c r="A31" s="5" t="n">
         <v>42597</v>
       </c>
       <c r="B31" t="n">
@@ -953,7 +950,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="n">
+      <c r="A32" s="5" t="n">
         <v>42604</v>
       </c>
       <c r="B32" t="n">
@@ -961,7 +958,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="n">
+      <c r="A33" s="5" t="n">
         <v>42611</v>
       </c>
       <c r="B33" t="n">
@@ -969,7 +966,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="n">
+      <c r="A34" s="5" t="n">
         <v>42618</v>
       </c>
       <c r="B34" t="n">
@@ -977,7 +974,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="n">
+      <c r="A35" s="5" t="n">
         <v>42625</v>
       </c>
       <c r="B35" t="n">
@@ -985,7 +982,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="n">
+      <c r="A36" s="5" t="n">
         <v>42632</v>
       </c>
       <c r="B36" t="n">
@@ -993,7 +990,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="n">
+      <c r="A37" s="5" t="n">
         <v>42639</v>
       </c>
       <c r="B37" t="n">
@@ -1001,7 +998,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="n">
+      <c r="A38" s="5" t="n">
         <v>42646</v>
       </c>
       <c r="B38" t="n">
@@ -1009,7 +1006,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="n">
+      <c r="A39" s="5" t="n">
         <v>42653</v>
       </c>
       <c r="B39" t="n">
@@ -1017,7 +1014,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="n">
+      <c r="A40" s="5" t="n">
         <v>42660</v>
       </c>
       <c r="B40" t="n">
@@ -1025,7 +1022,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="n">
+      <c r="A41" s="5" t="n">
         <v>42667</v>
       </c>
       <c r="B41" t="n">
@@ -1033,7 +1030,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="n">
+      <c r="A42" s="5" t="n">
         <v>42674</v>
       </c>
       <c r="B42" t="n">
@@ -1041,7 +1038,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="n">
+      <c r="A43" s="5" t="n">
         <v>42681</v>
       </c>
       <c r="B43" t="n">
@@ -1049,7 +1046,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="n">
+      <c r="A44" s="5" t="n">
         <v>42688</v>
       </c>
       <c r="B44" t="n">
@@ -1057,7 +1054,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="n">
+      <c r="A45" s="5" t="n">
         <v>42695</v>
       </c>
       <c r="B45" t="n">
@@ -1065,7 +1062,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="n">
+      <c r="A46" s="5" t="n">
         <v>42702</v>
       </c>
       <c r="B46" t="n">
@@ -1073,7 +1070,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="n">
+      <c r="A47" s="5" t="n">
         <v>42709</v>
       </c>
       <c r="B47" t="n">
@@ -1081,7 +1078,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="n">
+      <c r="A48" s="5" t="n">
         <v>42716</v>
       </c>
       <c r="B48" t="n">
@@ -1089,7 +1086,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="n">
+      <c r="A49" s="5" t="n">
         <v>42723</v>
       </c>
       <c r="B49" t="n">
@@ -1097,7 +1094,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="n">
+      <c r="A50" s="5" t="n">
         <v>42730</v>
       </c>
       <c r="B50" t="n">
@@ -1105,7 +1102,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="n">
+      <c r="A51" s="5" t="n">
         <v>42737</v>
       </c>
       <c r="B51" t="n">
@@ -1113,7 +1110,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="n">
+      <c r="A52" s="5" t="n">
         <v>42744</v>
       </c>
       <c r="B52" t="n">
@@ -1121,7 +1118,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="n">
+      <c r="A53" s="5" t="n">
         <v>42751</v>
       </c>
       <c r="B53" t="n">
@@ -1129,7 +1126,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="n">
+      <c r="A54" s="5" t="n">
         <v>42758</v>
       </c>
       <c r="B54" t="n">
@@ -1137,7 +1134,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="n">
+      <c r="A55" s="5" t="n">
         <v>42765</v>
       </c>
       <c r="B55" t="n">
@@ -1145,7 +1142,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="n">
+      <c r="A56" s="5" t="n">
         <v>42772</v>
       </c>
       <c r="B56" t="n">
@@ -1153,7 +1150,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="n">
+      <c r="A57" s="5" t="n">
         <v>42779</v>
       </c>
       <c r="B57" t="n">
@@ -1161,7 +1158,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="n">
+      <c r="A58" s="5" t="n">
         <v>42786</v>
       </c>
       <c r="B58" t="n">
@@ -1169,7 +1166,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="n">
+      <c r="A59" s="5" t="n">
         <v>42793</v>
       </c>
       <c r="B59" t="n">
@@ -1177,7 +1174,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="n">
+      <c r="A60" s="5" t="n">
         <v>42800</v>
       </c>
       <c r="B60" t="n">
@@ -1185,7 +1182,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="n">
+      <c r="A61" s="5" t="n">
         <v>42807</v>
       </c>
       <c r="B61" t="n">
@@ -1193,7 +1190,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="n">
+      <c r="A62" s="5" t="n">
         <v>42814</v>
       </c>
       <c r="B62" t="n">
@@ -1201,7 +1198,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="n">
+      <c r="A63" s="5" t="n">
         <v>42821</v>
       </c>
       <c r="B63" t="n">
@@ -1209,7 +1206,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="n">
+      <c r="A64" s="5" t="n">
         <v>42828</v>
       </c>
       <c r="B64" t="n">
@@ -1217,7 +1214,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="n">
+      <c r="A65" s="5" t="n">
         <v>42835</v>
       </c>
       <c r="B65" t="n">
@@ -1225,7 +1222,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="n">
+      <c r="A66" s="5" t="n">
         <v>42842</v>
       </c>
       <c r="B66" t="n">
@@ -1233,7 +1230,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="n">
+      <c r="A67" s="5" t="n">
         <v>42849</v>
       </c>
       <c r="B67" t="n">
@@ -1241,7 +1238,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="n">
+      <c r="A68" s="5" t="n">
         <v>42856</v>
       </c>
       <c r="B68" t="n">
@@ -1249,7 +1246,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="n">
+      <c r="A69" s="5" t="n">
         <v>42863</v>
       </c>
       <c r="B69" t="n">
@@ -1257,7 +1254,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="n">
+      <c r="A70" s="5" t="n">
         <v>42870</v>
       </c>
       <c r="B70" t="n">
@@ -1265,7 +1262,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="n">
+      <c r="A71" s="5" t="n">
         <v>42877</v>
       </c>
       <c r="B71" t="n">
@@ -1273,7 +1270,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="n">
+      <c r="A72" s="5" t="n">
         <v>42884</v>
       </c>
       <c r="B72" t="n">
@@ -1281,7 +1278,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="n">
+      <c r="A73" s="5" t="n">
         <v>42891</v>
       </c>
       <c r="B73" t="n">
@@ -1289,7 +1286,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="n">
+      <c r="A74" s="5" t="n">
         <v>42898</v>
       </c>
       <c r="B74" t="n">
@@ -1297,7 +1294,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="n">
+      <c r="A75" s="5" t="n">
         <v>42905</v>
       </c>
       <c r="B75" t="n">
@@ -1305,7 +1302,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="n">
+      <c r="A76" s="5" t="n">
         <v>42912</v>
       </c>
       <c r="B76" t="n">
@@ -1313,7 +1310,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="n">
+      <c r="A77" s="5" t="n">
         <v>42919</v>
       </c>
       <c r="B77" t="n">
@@ -1321,7 +1318,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="n">
+      <c r="A78" s="5" t="n">
         <v>42926</v>
       </c>
       <c r="B78" t="n">
@@ -1329,7 +1326,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="n">
+      <c r="A79" s="5" t="n">
         <v>42933</v>
       </c>
       <c r="B79" t="n">
@@ -1337,7 +1334,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="n">
+      <c r="A80" s="5" t="n">
         <v>42940</v>
       </c>
       <c r="B80" t="n">
@@ -1345,7 +1342,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="n">
+      <c r="A81" s="5" t="n">
         <v>42947</v>
       </c>
       <c r="B81" t="n">
@@ -1353,7 +1350,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="n">
+      <c r="A82" s="5" t="n">
         <v>42954</v>
       </c>
       <c r="B82" t="n">
@@ -1361,7 +1358,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="n">
+      <c r="A83" s="5" t="n">
         <v>42961</v>
       </c>
       <c r="B83" t="n">
@@ -1369,7 +1366,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="n">
+      <c r="A84" s="5" t="n">
         <v>42968</v>
       </c>
       <c r="B84" t="n">
@@ -1377,7 +1374,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="n">
+      <c r="A85" s="5" t="n">
         <v>42975</v>
       </c>
       <c r="B85" t="n">
@@ -1385,7 +1382,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="n">
+      <c r="A86" s="5" t="n">
         <v>42982</v>
       </c>
       <c r="B86" t="n">
@@ -1393,7 +1390,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="n">
+      <c r="A87" s="5" t="n">
         <v>42989</v>
       </c>
       <c r="B87" t="n">
@@ -1401,7 +1398,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="n">
+      <c r="A88" s="5" t="n">
         <v>42996</v>
       </c>
       <c r="B88" t="n">
@@ -1409,7 +1406,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="n">
+      <c r="A89" s="5" t="n">
         <v>43003</v>
       </c>
       <c r="B89" t="n">
@@ -1417,7 +1414,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="n">
+      <c r="A90" s="5" t="n">
         <v>43010</v>
       </c>
       <c r="B90" t="n">
@@ -1425,7 +1422,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="n">
+      <c r="A91" s="5" t="n">
         <v>43017</v>
       </c>
       <c r="B91" t="n">
@@ -1433,7 +1430,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="n">
+      <c r="A92" s="5" t="n">
         <v>43024</v>
       </c>
       <c r="B92" t="n">
@@ -1441,7 +1438,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="n">
+      <c r="A93" s="5" t="n">
         <v>43031</v>
       </c>
       <c r="B93" t="n">
@@ -1449,7 +1446,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="n">
+      <c r="A94" s="5" t="n">
         <v>43038</v>
       </c>
       <c r="B94" t="n">
@@ -1457,7 +1454,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="n">
+      <c r="A95" s="5" t="n">
         <v>43045</v>
       </c>
       <c r="B95" t="n">
@@ -1465,7 +1462,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="n">
+      <c r="A96" s="5" t="n">
         <v>43052</v>
       </c>
       <c r="B96" t="n">
@@ -1473,7 +1470,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="n">
+      <c r="A97" s="5" t="n">
         <v>43059</v>
       </c>
       <c r="B97" t="n">
@@ -1481,7 +1478,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="n">
+      <c r="A98" s="5" t="n">
         <v>43066</v>
       </c>
       <c r="B98" t="n">
@@ -1489,7 +1486,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="n">
+      <c r="A99" s="5" t="n">
         <v>43073</v>
       </c>
       <c r="B99" t="n">
@@ -1497,7 +1494,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="n">
+      <c r="A100" s="5" t="n">
         <v>43080</v>
       </c>
       <c r="B100" t="n">
@@ -1505,7 +1502,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="n">
+      <c r="A101" s="5" t="n">
         <v>43087</v>
       </c>
       <c r="B101" t="n">
@@ -1513,7 +1510,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="n">
+      <c r="A102" s="5" t="n">
         <v>43094</v>
       </c>
       <c r="B102" t="n">
@@ -1521,7 +1518,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="n">
+      <c r="A103" s="5" t="n">
         <v>43101</v>
       </c>
       <c r="B103" t="n">
@@ -1529,7 +1526,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="n">
+      <c r="A104" s="5" t="n">
         <v>43108</v>
       </c>
       <c r="B104" t="n">
@@ -1537,7 +1534,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="n">
+      <c r="A105" s="5" t="n">
         <v>43115</v>
       </c>
       <c r="B105" t="n">
@@ -1545,7 +1542,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="n">
+      <c r="A106" s="5" t="n">
         <v>43122</v>
       </c>
       <c r="B106" t="n">
@@ -1553,7 +1550,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="n">
+      <c r="A107" s="5" t="n">
         <v>43129</v>
       </c>
       <c r="B107" t="n">
@@ -1561,7 +1558,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="n">
+      <c r="A108" s="5" t="n">
         <v>43136</v>
       </c>
       <c r="B108" t="n">
@@ -1569,7 +1566,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="n">
+      <c r="A109" s="5" t="n">
         <v>43143</v>
       </c>
       <c r="B109" t="n">
@@ -1577,7 +1574,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="n">
+      <c r="A110" s="5" t="n">
         <v>43150</v>
       </c>
       <c r="B110" t="n">
@@ -1585,7 +1582,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="n">
+      <c r="A111" s="5" t="n">
         <v>43157</v>
       </c>
       <c r="B111" t="n">
@@ -1593,7 +1590,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="n">
+      <c r="A112" s="5" t="n">
         <v>43164</v>
       </c>
       <c r="B112" t="n">
@@ -1601,7 +1598,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="n">
+      <c r="A113" s="5" t="n">
         <v>43171</v>
       </c>
       <c r="B113" t="n">
@@ -1609,7 +1606,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="n">
+      <c r="A114" s="5" t="n">
         <v>43178</v>
       </c>
       <c r="B114" t="n">
@@ -1617,7 +1614,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="n">
+      <c r="A115" s="5" t="n">
         <v>43185</v>
       </c>
       <c r="B115" t="n">
@@ -1625,7 +1622,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="n">
+      <c r="A116" s="5" t="n">
         <v>43192</v>
       </c>
       <c r="B116" t="n">
@@ -1633,7 +1630,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="n">
+      <c r="A117" s="5" t="n">
         <v>43199</v>
       </c>
       <c r="B117" t="n">
@@ -1641,7 +1638,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="n">
+      <c r="A118" s="5" t="n">
         <v>43206</v>
       </c>
       <c r="B118" t="n">
@@ -1649,7 +1646,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="n">
+      <c r="A119" s="5" t="n">
         <v>43213</v>
       </c>
       <c r="B119" t="n">
@@ -1657,7 +1654,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="n">
+      <c r="A120" s="5" t="n">
         <v>43220</v>
       </c>
       <c r="B120" t="n">
@@ -1665,7 +1662,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="n">
+      <c r="A121" s="5" t="n">
         <v>43227</v>
       </c>
       <c r="B121" t="n">
@@ -1673,7 +1670,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="n">
+      <c r="A122" s="5" t="n">
         <v>43234</v>
       </c>
       <c r="B122" t="n">
@@ -1681,7 +1678,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="n">
+      <c r="A123" s="5" t="n">
         <v>43241</v>
       </c>
       <c r="B123" t="n">
@@ -1689,7 +1686,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="n">
+      <c r="A124" s="5" t="n">
         <v>43248</v>
       </c>
       <c r="B124" t="n">
@@ -1697,7 +1694,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="n">
+      <c r="A125" s="5" t="n">
         <v>43255</v>
       </c>
       <c r="B125" t="n">
@@ -1705,7 +1702,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="n">
+      <c r="A126" s="5" t="n">
         <v>43262</v>
       </c>
       <c r="B126" t="n">
@@ -1713,7 +1710,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="n">
+      <c r="A127" s="5" t="n">
         <v>43269</v>
       </c>
       <c r="B127" t="n">
@@ -1721,7 +1718,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="n">
+      <c r="A128" s="5" t="n">
         <v>43276</v>
       </c>
       <c r="B128" t="n">
@@ -1729,7 +1726,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="n">
+      <c r="A129" s="5" t="n">
         <v>43283</v>
       </c>
       <c r="B129" t="n">
@@ -1737,7 +1734,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="n">
+      <c r="A130" s="5" t="n">
         <v>43290</v>
       </c>
       <c r="B130" t="n">
@@ -1745,7 +1742,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="n">
+      <c r="A131" s="5" t="n">
         <v>43297</v>
       </c>
       <c r="B131" t="n">
@@ -1753,7 +1750,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="n">
+      <c r="A132" s="5" t="n">
         <v>43304</v>
       </c>
       <c r="B132" t="n">
@@ -1761,7 +1758,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="n">
+      <c r="A133" s="5" t="n">
         <v>43311</v>
       </c>
       <c r="B133" t="n">
@@ -1769,7 +1766,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="n">
+      <c r="A134" s="5" t="n">
         <v>43318</v>
       </c>
       <c r="B134" t="n">
@@ -1777,7 +1774,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="n">
+      <c r="A135" s="5" t="n">
         <v>43325</v>
       </c>
       <c r="B135" t="n">
@@ -1785,7 +1782,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="n">
+      <c r="A136" s="5" t="n">
         <v>43332</v>
       </c>
       <c r="B136" t="n">
@@ -1793,7 +1790,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="n">
+      <c r="A137" s="5" t="n">
         <v>43339</v>
       </c>
       <c r="B137" t="n">
@@ -1801,7 +1798,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="n">
+      <c r="A138" s="5" t="n">
         <v>43346</v>
       </c>
       <c r="B138" t="n">
@@ -1809,7 +1806,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="n">
+      <c r="A139" s="5" t="n">
         <v>43353</v>
       </c>
       <c r="B139" t="n">
@@ -1817,7 +1814,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="n">
+      <c r="A140" s="5" t="n">
         <v>43360</v>
       </c>
       <c r="B140" t="n">
@@ -1825,7 +1822,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="n">
+      <c r="A141" s="5" t="n">
         <v>43367</v>
       </c>
       <c r="B141" t="n">
@@ -1833,7 +1830,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="n">
+      <c r="A142" s="5" t="n">
         <v>43374</v>
       </c>
       <c r="B142" t="n">
@@ -1841,7 +1838,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="n">
+      <c r="A143" s="5" t="n">
         <v>43381</v>
       </c>
       <c r="B143" t="n">
@@ -1849,7 +1846,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="n">
+      <c r="A144" s="5" t="n">
         <v>43388</v>
       </c>
       <c r="B144" t="n">
@@ -1857,7 +1854,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="n">
+      <c r="A145" s="5" t="n">
         <v>43395</v>
       </c>
       <c r="B145" t="n">
@@ -1865,7 +1862,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="n">
+      <c r="A146" s="5" t="n">
         <v>43402</v>
       </c>
       <c r="B146" t="n">
@@ -1873,7 +1870,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="n">
+      <c r="A147" s="5" t="n">
         <v>43409</v>
       </c>
       <c r="B147" t="n">
@@ -1881,7 +1878,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="n">
+      <c r="A148" s="5" t="n">
         <v>43416</v>
       </c>
       <c r="B148" t="n">
@@ -1889,7 +1886,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="n">
+      <c r="A149" s="5" t="n">
         <v>43423</v>
       </c>
       <c r="B149" t="n">
@@ -1897,7 +1894,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="n">
+      <c r="A150" s="5" t="n">
         <v>43430</v>
       </c>
       <c r="B150" t="n">
@@ -1905,7 +1902,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="n">
+      <c r="A151" s="5" t="n">
         <v>43437</v>
       </c>
       <c r="B151" t="n">
@@ -1913,7 +1910,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="n">
+      <c r="A152" s="5" t="n">
         <v>43444</v>
       </c>
       <c r="B152" t="n">
@@ -1921,7 +1918,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="n">
+      <c r="A153" s="5" t="n">
         <v>43451</v>
       </c>
       <c r="B153" t="n">
@@ -1929,7 +1926,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="n">
+      <c r="A154" s="5" t="n">
         <v>43458</v>
       </c>
       <c r="B154" t="n">
@@ -1937,7 +1934,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="n">
+      <c r="A155" s="5" t="n">
         <v>43465</v>
       </c>
       <c r="B155" t="n">
@@ -1945,7 +1942,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="n">
+      <c r="A156" s="5" t="n">
         <v>43472</v>
       </c>
       <c r="B156" t="n">
@@ -1953,7 +1950,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="n">
+      <c r="A157" s="5" t="n">
         <v>43479</v>
       </c>
       <c r="B157" t="n">
@@ -1961,7 +1958,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="n">
+      <c r="A158" s="5" t="n">
         <v>43486</v>
       </c>
       <c r="B158" t="n">
@@ -1969,7 +1966,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="n">
+      <c r="A159" s="5" t="n">
         <v>43493</v>
       </c>
       <c r="B159" t="n">
@@ -1977,7 +1974,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="n">
+      <c r="A160" s="5" t="n">
         <v>43500</v>
       </c>
       <c r="B160" t="n">
@@ -1985,7 +1982,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="n">
+      <c r="A161" s="5" t="n">
         <v>43507</v>
       </c>
       <c r="B161" t="n">
@@ -1993,7 +1990,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="n">
+      <c r="A162" s="5" t="n">
         <v>43514</v>
       </c>
       <c r="B162" t="n">
@@ -2001,7 +1998,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="n">
+      <c r="A163" s="5" t="n">
         <v>43521</v>
       </c>
       <c r="B163" t="n">
@@ -2009,7 +2006,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="n">
+      <c r="A164" s="5" t="n">
         <v>43528</v>
       </c>
       <c r="B164" t="n">
@@ -2017,7 +2014,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="n">
+      <c r="A165" s="5" t="n">
         <v>43535</v>
       </c>
       <c r="B165" t="n">
@@ -2025,7 +2022,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="n">
+      <c r="A166" s="5" t="n">
         <v>43542</v>
       </c>
       <c r="B166" t="n">
@@ -2033,7 +2030,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="n">
+      <c r="A167" s="5" t="n">
         <v>43549</v>
       </c>
       <c r="B167" t="n">
@@ -2041,7 +2038,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="n">
+      <c r="A168" s="5" t="n">
         <v>43556</v>
       </c>
       <c r="B168" t="n">
@@ -2049,7 +2046,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="n">
+      <c r="A169" s="5" t="n">
         <v>43563</v>
       </c>
       <c r="B169" t="n">
@@ -2057,7 +2054,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="n">
+      <c r="A170" s="5" t="n">
         <v>43570</v>
       </c>
       <c r="B170" t="n">
@@ -2065,7 +2062,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="n">
+      <c r="A171" s="5" t="n">
         <v>43577</v>
       </c>
       <c r="B171" t="n">
@@ -2073,7 +2070,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="n">
+      <c r="A172" s="5" t="n">
         <v>43584</v>
       </c>
       <c r="B172" t="n">
@@ -2081,7 +2078,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="n">
+      <c r="A173" s="5" t="n">
         <v>43591</v>
       </c>
       <c r="B173" t="n">
@@ -2089,7 +2086,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="n">
+      <c r="A174" s="5" t="n">
         <v>43598</v>
       </c>
       <c r="B174" t="n">
@@ -2097,7 +2094,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="n">
+      <c r="A175" s="5" t="n">
         <v>43605</v>
       </c>
       <c r="B175" t="n">
@@ -2105,7 +2102,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="n">
+      <c r="A176" s="5" t="n">
         <v>43612</v>
       </c>
       <c r="B176" t="n">
@@ -2113,7 +2110,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="n">
+      <c r="A177" s="5" t="n">
         <v>43619</v>
       </c>
       <c r="B177" t="n">
@@ -2121,7 +2118,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="n">
+      <c r="A178" s="5" t="n">
         <v>43626</v>
       </c>
       <c r="B178" t="n">
@@ -2129,7 +2126,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="n">
+      <c r="A179" s="5" t="n">
         <v>43633</v>
       </c>
       <c r="B179" t="n">
@@ -2137,7 +2134,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="n">
+      <c r="A180" s="5" t="n">
         <v>43640</v>
       </c>
       <c r="B180" t="n">
@@ -2145,7 +2142,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="n">
+      <c r="A181" s="5" t="n">
         <v>43647</v>
       </c>
       <c r="B181" t="n">
@@ -2153,7 +2150,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="n">
+      <c r="A182" s="5" t="n">
         <v>43654</v>
       </c>
       <c r="B182" t="n">
@@ -2161,7 +2158,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="n">
+      <c r="A183" s="5" t="n">
         <v>43661</v>
       </c>
       <c r="B183" t="n">
@@ -2169,7 +2166,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="n">
+      <c r="A184" s="5" t="n">
         <v>43668</v>
       </c>
       <c r="B184" t="n">
@@ -2177,7 +2174,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="n">
+      <c r="A185" s="5" t="n">
         <v>43675</v>
       </c>
       <c r="B185" t="n">
@@ -2185,7 +2182,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="n">
+      <c r="A186" s="5" t="n">
         <v>43682</v>
       </c>
       <c r="B186" t="n">
@@ -2193,7 +2190,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="n">
+      <c r="A187" s="5" t="n">
         <v>43689</v>
       </c>
       <c r="B187" t="n">
@@ -2201,7 +2198,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="n">
+      <c r="A188" s="5" t="n">
         <v>43696</v>
       </c>
       <c r="B188" t="n">
@@ -2209,7 +2206,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="n">
+      <c r="A189" s="5" t="n">
         <v>43703</v>
       </c>
       <c r="B189" t="n">
@@ -2217,7 +2214,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="n">
+      <c r="A190" s="5" t="n">
         <v>43710</v>
       </c>
       <c r="B190" t="n">
@@ -2225,7 +2222,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="n">
+      <c r="A191" s="5" t="n">
         <v>43717</v>
       </c>
       <c r="B191" t="n">
@@ -2233,7 +2230,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="n">
+      <c r="A192" s="5" t="n">
         <v>43724</v>
       </c>
       <c r="B192" t="n">
@@ -2241,7 +2238,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="n">
+      <c r="A193" s="5" t="n">
         <v>43731</v>
       </c>
       <c r="B193" t="n">
@@ -2249,7 +2246,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="n">
+      <c r="A194" s="5" t="n">
         <v>43738</v>
       </c>
       <c r="B194" t="n">
@@ -2257,7 +2254,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="3" t="n">
+      <c r="A195" s="5" t="n">
         <v>43745</v>
       </c>
       <c r="B195" t="n">
@@ -2265,7 +2262,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="n">
+      <c r="A196" s="5" t="n">
         <v>43752</v>
       </c>
       <c r="B196" t="n">
@@ -2273,7 +2270,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="n">
+      <c r="A197" s="5" t="n">
         <v>43759</v>
       </c>
       <c r="B197" t="n">
@@ -2281,7 +2278,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="n">
+      <c r="A198" s="5" t="n">
         <v>43766</v>
       </c>
       <c r="B198" t="n">
@@ -2289,7 +2286,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="n">
+      <c r="A199" s="5" t="n">
         <v>43773</v>
       </c>
       <c r="B199" t="n">
@@ -2297,7 +2294,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="n">
+      <c r="A200" s="5" t="n">
         <v>43780</v>
       </c>
       <c r="B200" t="n">
@@ -2305,7 +2302,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="3" t="n">
+      <c r="A201" s="5" t="n">
         <v>43787</v>
       </c>
       <c r="B201" t="n">
@@ -2313,7 +2310,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="3" t="n">
+      <c r="A202" s="5" t="n">
         <v>43794</v>
       </c>
       <c r="B202" t="n">
@@ -2321,7 +2318,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="3" t="n">
+      <c r="A203" s="5" t="n">
         <v>43801</v>
       </c>
       <c r="B203" t="n">
@@ -2329,7 +2326,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="3" t="n">
+      <c r="A204" s="5" t="n">
         <v>43808</v>
       </c>
       <c r="B204" t="n">
@@ -2337,7 +2334,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="3" t="n">
+      <c r="A205" s="5" t="n">
         <v>43815</v>
       </c>
       <c r="B205" t="n">
@@ -2345,7 +2342,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="3" t="n">
+      <c r="A206" s="5" t="n">
         <v>43822</v>
       </c>
       <c r="B206" t="n">
@@ -2353,7 +2350,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="3" t="n">
+      <c r="A207" s="5" t="n">
         <v>43829</v>
       </c>
       <c r="B207" t="n">
@@ -2361,7 +2358,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="3" t="n">
+      <c r="A208" s="5" t="n">
         <v>43836</v>
       </c>
       <c r="B208" t="n">
@@ -2369,7 +2366,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="3" t="n">
+      <c r="A209" s="5" t="n">
         <v>43843</v>
       </c>
       <c r="B209" t="n">
@@ -2377,7 +2374,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="3" t="n">
+      <c r="A210" s="5" t="n">
         <v>43850</v>
       </c>
       <c r="B210" t="n">
@@ -2385,7 +2382,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="3" t="n">
+      <c r="A211" s="5" t="n">
         <v>43857</v>
       </c>
       <c r="B211" t="n">
@@ -2393,7 +2390,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="3" t="n">
+      <c r="A212" s="5" t="n">
         <v>43864</v>
       </c>
       <c r="B212" t="n">
@@ -2401,7 +2398,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="3" t="n">
+      <c r="A213" s="5" t="n">
         <v>43871</v>
       </c>
       <c r="B213" t="n">
@@ -2409,7 +2406,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="3" t="n">
+      <c r="A214" s="5" t="n">
         <v>43878</v>
       </c>
       <c r="B214" t="n">
@@ -2417,7 +2414,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="3" t="n">
+      <c r="A215" s="5" t="n">
         <v>43885</v>
       </c>
       <c r="B215" t="n">
@@ -2425,7 +2422,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="3" t="n">
+      <c r="A216" s="5" t="n">
         <v>43892</v>
       </c>
       <c r="B216" t="n">
@@ -2433,7 +2430,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="3" t="n">
+      <c r="A217" s="5" t="n">
         <v>43899</v>
       </c>
       <c r="B217" t="n">
@@ -2441,7 +2438,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="3" t="n">
+      <c r="A218" s="5" t="n">
         <v>43906</v>
       </c>
       <c r="B218" t="n">
@@ -2449,7 +2446,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="3" t="n">
+      <c r="A219" s="5" t="n">
         <v>43913</v>
       </c>
       <c r="B219" t="n">
@@ -2457,7 +2454,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="3" t="n">
+      <c r="A220" s="5" t="n">
         <v>43920</v>
       </c>
       <c r="B220" t="n">
@@ -2465,7 +2462,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="3" t="n">
+      <c r="A221" s="5" t="n">
         <v>43927</v>
       </c>
       <c r="B221" t="n">
@@ -2473,7 +2470,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="3" t="n">
+      <c r="A222" s="5" t="n">
         <v>43934</v>
       </c>
       <c r="B222" t="n">
@@ -2481,7 +2478,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="3" t="n">
+      <c r="A223" s="5" t="n">
         <v>43941</v>
       </c>
       <c r="B223" t="n">
@@ -2489,7 +2486,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="3" t="n">
+      <c r="A224" s="5" t="n">
         <v>43948</v>
       </c>
       <c r="B224" t="n">
@@ -2497,7 +2494,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="3" t="n">
+      <c r="A225" s="5" t="n">
         <v>43955</v>
       </c>
       <c r="B225" t="n">
@@ -2505,7 +2502,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="3" t="n">
+      <c r="A226" s="5" t="n">
         <v>43962</v>
       </c>
       <c r="B226" t="n">
@@ -2513,7 +2510,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="3" t="n">
+      <c r="A227" s="5" t="n">
         <v>43969</v>
       </c>
       <c r="B227" t="n">
@@ -2521,7 +2518,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="3" t="n">
+      <c r="A228" s="5" t="n">
         <v>43976</v>
       </c>
       <c r="B228" t="n">
@@ -2529,7 +2526,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="3" t="n">
+      <c r="A229" s="5" t="n">
         <v>43983</v>
       </c>
       <c r="B229" t="n">
@@ -2537,7 +2534,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="3" t="n">
+      <c r="A230" s="5" t="n">
         <v>43990</v>
       </c>
       <c r="B230" t="n">
@@ -2545,7 +2542,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="3" t="n">
+      <c r="A231" s="5" t="n">
         <v>43997</v>
       </c>
       <c r="B231" t="n">
@@ -2553,7 +2550,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="3" t="n">
+      <c r="A232" s="5" t="n">
         <v>44004</v>
       </c>
       <c r="B232" t="n">
@@ -2561,7 +2558,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="3" t="n">
+      <c r="A233" s="5" t="n">
         <v>44011</v>
       </c>
       <c r="B233" t="n">
@@ -2569,7 +2566,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="3" t="n">
+      <c r="A234" s="5" t="n">
         <v>44018</v>
       </c>
       <c r="B234" t="n">
@@ -2577,7 +2574,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="3" t="n">
+      <c r="A235" s="5" t="n">
         <v>44025</v>
       </c>
       <c r="B235" t="n">
@@ -2585,7 +2582,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="3" t="n">
+      <c r="A236" s="5" t="n">
         <v>44032</v>
       </c>
       <c r="B236" t="n">
@@ -2593,7 +2590,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="3" t="n">
+      <c r="A237" s="5" t="n">
         <v>44039</v>
       </c>
       <c r="B237" t="n">
@@ -2601,7 +2598,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="3" t="n">
+      <c r="A238" s="5" t="n">
         <v>44046</v>
       </c>
       <c r="B238" t="n">
@@ -2609,7 +2606,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="3" t="n">
+      <c r="A239" s="5" t="n">
         <v>44053</v>
       </c>
       <c r="B239" t="n">
@@ -2617,7 +2614,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="3" t="n">
+      <c r="A240" s="5" t="n">
         <v>44060</v>
       </c>
       <c r="B240" t="n">
@@ -2625,7 +2622,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="3" t="n">
+      <c r="A241" s="5" t="n">
         <v>44067</v>
       </c>
       <c r="B241" t="n">
@@ -2633,7 +2630,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="3" t="n">
+      <c r="A242" s="5" t="n">
         <v>44074</v>
       </c>
       <c r="B242" t="n">
@@ -2641,7 +2638,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="3" t="n">
+      <c r="A243" s="5" t="n">
         <v>44081</v>
       </c>
       <c r="B243" t="n">
@@ -2649,7 +2646,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="3" t="n">
+      <c r="A244" s="5" t="n">
         <v>44088</v>
       </c>
       <c r="B244" t="n">
@@ -2657,7 +2654,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="3" t="n">
+      <c r="A245" s="5" t="n">
         <v>44095</v>
       </c>
       <c r="B245" t="n">
@@ -2665,7 +2662,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="3" t="n">
+      <c r="A246" s="5" t="n">
         <v>44102</v>
       </c>
       <c r="B246" t="n">
@@ -2673,7 +2670,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="3" t="n">
+      <c r="A247" s="5" t="n">
         <v>44109</v>
       </c>
       <c r="B247" t="n">
@@ -2681,7 +2678,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="n">
+      <c r="A248" s="5" t="n">
         <v>44116</v>
       </c>
       <c r="B248" t="n">
@@ -2689,7 +2686,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="3" t="n">
+      <c r="A249" s="5" t="n">
         <v>44123</v>
       </c>
       <c r="B249" t="n">
@@ -2697,7 +2694,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="3" t="n">
+      <c r="A250" s="5" t="n">
         <v>44130</v>
       </c>
       <c r="B250" t="n">
@@ -2705,7 +2702,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="3" t="n">
+      <c r="A251" s="5" t="n">
         <v>44137</v>
       </c>
       <c r="B251" t="n">
@@ -2713,7 +2710,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="3" t="n">
+      <c r="A252" s="5" t="n">
         <v>44144</v>
       </c>
       <c r="B252" t="n">
@@ -2721,7 +2718,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="3" t="n">
+      <c r="A253" s="5" t="n">
         <v>44151</v>
       </c>
       <c r="B253" t="n">
@@ -2729,7 +2726,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="3" t="n">
+      <c r="A254" s="5" t="n">
         <v>44158</v>
       </c>
       <c r="B254" t="n">
@@ -2737,7 +2734,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="3" t="n">
+      <c r="A255" s="5" t="n">
         <v>44165</v>
       </c>
       <c r="B255" t="n">
@@ -2745,7 +2742,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="3" t="n">
+      <c r="A256" s="5" t="n">
         <v>44172</v>
       </c>
       <c r="B256" t="n">
@@ -2753,7 +2750,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="3" t="n">
+      <c r="A257" s="5" t="n">
         <v>44179</v>
       </c>
       <c r="B257" t="n">
@@ -2761,7 +2758,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="3" t="n">
+      <c r="A258" s="5" t="n">
         <v>44186</v>
       </c>
       <c r="B258" t="n">
@@ -2769,7 +2766,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="3" t="n">
+      <c r="A259" s="5" t="n">
         <v>44193</v>
       </c>
       <c r="B259" t="n">
@@ -2777,7 +2774,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="3" t="n">
+      <c r="A260" s="5" t="n">
         <v>44200</v>
       </c>
       <c r="B260" t="n">
@@ -2785,7 +2782,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="3" t="n">
+      <c r="A261" s="5" t="n">
         <v>44207</v>
       </c>
       <c r="B261" t="n">
@@ -2793,7 +2790,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="3" t="n">
+      <c r="A262" s="5" t="n">
         <v>44214</v>
       </c>
       <c r="B262" t="n">
@@ -2801,7 +2798,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="3" t="n">
+      <c r="A263" s="5" t="n">
         <v>44221</v>
       </c>
       <c r="B263" t="n">
@@ -2809,7 +2806,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="3" t="n">
+      <c r="A264" s="5" t="n">
         <v>44228</v>
       </c>
       <c r="B264" t="n">
@@ -2817,7 +2814,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="3" t="n">
+      <c r="A265" s="5" t="n">
         <v>44235</v>
       </c>
       <c r="B265" t="n">
@@ -2825,7 +2822,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="3" t="n">
+      <c r="A266" s="5" t="n">
         <v>44242</v>
       </c>
       <c r="B266" t="n">
@@ -2833,7 +2830,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="3" t="n">
+      <c r="A267" s="5" t="n">
         <v>44249</v>
       </c>
       <c r="B267" t="n">
@@ -2841,7 +2838,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="3" t="n">
+      <c r="A268" s="5" t="n">
         <v>44256</v>
       </c>
       <c r="B268" t="n">
@@ -2849,7 +2846,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="3" t="n">
+      <c r="A269" s="5" t="n">
         <v>44263</v>
       </c>
       <c r="B269" t="n">
@@ -2857,7 +2854,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="3" t="n">
+      <c r="A270" s="5" t="n">
         <v>44270</v>
       </c>
       <c r="B270" t="n">
@@ -2865,7 +2862,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="3" t="n">
+      <c r="A271" s="5" t="n">
         <v>44277</v>
       </c>
       <c r="B271" t="n">
@@ -2873,7 +2870,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="3" t="n">
+      <c r="A272" s="5" t="n">
         <v>44284</v>
       </c>
       <c r="B272" t="n">
@@ -2881,7 +2878,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="3" t="n">
+      <c r="A273" s="5" t="n">
         <v>44291</v>
       </c>
       <c r="B273" t="n">
@@ -2889,7 +2886,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="3" t="n">
+      <c r="A274" s="5" t="n">
         <v>44298</v>
       </c>
       <c r="B274" t="n">
@@ -2897,7 +2894,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="3" t="n">
+      <c r="A275" s="5" t="n">
         <v>44305</v>
       </c>
       <c r="B275" t="n">
@@ -2905,7 +2902,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="3" t="n">
+      <c r="A276" s="5" t="n">
         <v>44312</v>
       </c>
       <c r="B276" t="n">
@@ -2913,7 +2910,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="3" t="n">
+      <c r="A277" s="5" t="n">
         <v>44319</v>
       </c>
       <c r="B277" t="n">
@@ -2921,7 +2918,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="3" t="n">
+      <c r="A278" s="5" t="n">
         <v>44326</v>
       </c>
       <c r="B278" t="n">
@@ -2929,7 +2926,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="3" t="n">
+      <c r="A279" s="5" t="n">
         <v>44333</v>
       </c>
       <c r="B279" t="n">
@@ -2937,7 +2934,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="3" t="n">
+      <c r="A280" s="5" t="n">
         <v>44340</v>
       </c>
       <c r="B280" t="n">
@@ -2945,7 +2942,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="3" t="n">
+      <c r="A281" s="5" t="n">
         <v>44347</v>
       </c>
       <c r="B281" t="n">
@@ -2953,7 +2950,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="3" t="n">
+      <c r="A282" s="5" t="n">
         <v>44354</v>
       </c>
       <c r="B282" t="n">
@@ -2961,7 +2958,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="3" t="n">
+      <c r="A283" s="5" t="n">
         <v>44361</v>
       </c>
       <c r="B283" t="n">
@@ -2969,7 +2966,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="3" t="n">
+      <c r="A284" s="5" t="n">
         <v>44368</v>
       </c>
       <c r="B284" t="n">
@@ -2977,7 +2974,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="3" t="n">
+      <c r="A285" s="5" t="n">
         <v>44375</v>
       </c>
       <c r="B285" t="n">
@@ -2985,7 +2982,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="3" t="n">
+      <c r="A286" s="5" t="n">
         <v>44382</v>
       </c>
       <c r="B286" t="n">
@@ -2993,7 +2990,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="3" t="n">
+      <c r="A287" s="5" t="n">
         <v>44389</v>
       </c>
       <c r="B287" t="n">
@@ -3001,7 +2998,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="3" t="n">
+      <c r="A288" s="5" t="n">
         <v>44396</v>
       </c>
       <c r="B288" t="n">
@@ -3009,7 +3006,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="3" t="n">
+      <c r="A289" s="5" t="n">
         <v>44403</v>
       </c>
       <c r="B289" t="n">
@@ -3017,7 +3014,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="3" t="n">
+      <c r="A290" s="5" t="n">
         <v>44410</v>
       </c>
       <c r="B290" t="n">
@@ -3025,7 +3022,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="3" t="n">
+      <c r="A291" s="5" t="n">
         <v>44417</v>
       </c>
       <c r="B291" t="n">
@@ -3033,7 +3030,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="3" t="n">
+      <c r="A292" s="5" t="n">
         <v>44424</v>
       </c>
       <c r="B292" t="n">
@@ -3041,7 +3038,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="3" t="n">
+      <c r="A293" s="5" t="n">
         <v>44431</v>
       </c>
       <c r="B293" t="n">
@@ -3049,7 +3046,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="3" t="n">
+      <c r="A294" s="5" t="n">
         <v>44438</v>
       </c>
       <c r="B294" t="n">
@@ -3057,7 +3054,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="3" t="n">
+      <c r="A295" s="5" t="n">
         <v>44445</v>
       </c>
       <c r="B295" t="n">
@@ -3065,7 +3062,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="3" t="n">
+      <c r="A296" s="5" t="n">
         <v>44452</v>
       </c>
       <c r="B296" t="n">
@@ -3073,7 +3070,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="3" t="n">
+      <c r="A297" s="5" t="n">
         <v>44459</v>
       </c>
       <c r="B297" t="n">
@@ -3081,7 +3078,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="3" t="n">
+      <c r="A298" s="5" t="n">
         <v>44466</v>
       </c>
       <c r="B298" t="n">
@@ -3089,7 +3086,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="3" t="n">
+      <c r="A299" s="5" t="n">
         <v>44473</v>
       </c>
       <c r="B299" t="n">
@@ -3097,7 +3094,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="3" t="n">
+      <c r="A300" s="5" t="n">
         <v>44480</v>
       </c>
       <c r="B300" t="n">
@@ -3105,7 +3102,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="3" t="n">
+      <c r="A301" s="5" t="n">
         <v>44487</v>
       </c>
       <c r="B301" t="n">
@@ -3113,7 +3110,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="3" t="n">
+      <c r="A302" s="5" t="n">
         <v>44494</v>
       </c>
       <c r="B302" t="n">
@@ -3121,7 +3118,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="3" t="n">
+      <c r="A303" s="5" t="n">
         <v>44501</v>
       </c>
       <c r="B303" t="n">
@@ -3129,7 +3126,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="3" t="n">
+      <c r="A304" s="5" t="n">
         <v>44508</v>
       </c>
       <c r="B304" t="n">
@@ -3137,7 +3134,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="3" t="n">
+      <c r="A305" s="5" t="n">
         <v>44515</v>
       </c>
       <c r="B305" t="n">
@@ -3145,7 +3142,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="3" t="n">
+      <c r="A306" s="5" t="n">
         <v>44522</v>
       </c>
       <c r="B306" t="n">
@@ -3153,7 +3150,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="3" t="n">
+      <c r="A307" s="5" t="n">
         <v>44529</v>
       </c>
       <c r="B307" t="n">
@@ -3161,7 +3158,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="3" t="n">
+      <c r="A308" s="5" t="n">
         <v>44536</v>
       </c>
       <c r="B308" t="n">
@@ -3169,7 +3166,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="3" t="n">
+      <c r="A309" s="5" t="n">
         <v>44543</v>
       </c>
       <c r="B309" t="n">
@@ -3177,7 +3174,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="3" t="n">
+      <c r="A310" s="5" t="n">
         <v>44550</v>
       </c>
       <c r="B310" t="n">
@@ -3185,7 +3182,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="3" t="n">
+      <c r="A311" s="5" t="n">
         <v>44557</v>
       </c>
       <c r="B311" t="n">
@@ -3193,7 +3190,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="3" t="n">
+      <c r="A312" s="5" t="n">
         <v>44564</v>
       </c>
       <c r="B312" t="n">
@@ -3201,7 +3198,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="3" t="n">
+      <c r="A313" s="5" t="n">
         <v>44571</v>
       </c>
       <c r="B313" t="n">
@@ -3209,7 +3206,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="3" t="n">
+      <c r="A314" s="5" t="n">
         <v>44578</v>
       </c>
       <c r="B314" t="n">
@@ -3217,7 +3214,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="3" t="n">
+      <c r="A315" s="5" t="n">
         <v>44585</v>
       </c>
       <c r="B315" t="n">
@@ -3225,7 +3222,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="3" t="n">
+      <c r="A316" s="5" t="n">
         <v>44592</v>
       </c>
       <c r="B316" t="n">
@@ -3233,7 +3230,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="3" t="n">
+      <c r="A317" s="5" t="n">
         <v>44599</v>
       </c>
       <c r="B317" t="n">
@@ -3241,7 +3238,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="3" t="n">
+      <c r="A318" s="5" t="n">
         <v>44606</v>
       </c>
       <c r="B318" t="n">
@@ -3249,7 +3246,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="3" t="n">
+      <c r="A319" s="5" t="n">
         <v>44613</v>
       </c>
       <c r="B319" t="n">
@@ -3257,7 +3254,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="3" t="n">
+      <c r="A320" s="5" t="n">
         <v>44620</v>
       </c>
       <c r="B320" t="n">
@@ -3265,7 +3262,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="3" t="n">
+      <c r="A321" s="5" t="n">
         <v>44627</v>
       </c>
       <c r="B321" t="n">
@@ -3273,7 +3270,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="3" t="n">
+      <c r="A322" s="5" t="n">
         <v>44634</v>
       </c>
       <c r="B322" t="n">
@@ -3281,7 +3278,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="3" t="n">
+      <c r="A323" s="5" t="n">
         <v>44641</v>
       </c>
       <c r="B323" t="n">
@@ -3289,7 +3286,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="3" t="n">
+      <c r="A324" s="5" t="n">
         <v>44648</v>
       </c>
       <c r="B324" t="n">
@@ -3297,7 +3294,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="3" t="n">
+      <c r="A325" s="5" t="n">
         <v>44655</v>
       </c>
       <c r="B325" t="n">
@@ -3305,7 +3302,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="3" t="n">
+      <c r="A326" s="5" t="n">
         <v>44662</v>
       </c>
       <c r="B326" t="n">
@@ -3313,7 +3310,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="3" t="n">
+      <c r="A327" s="5" t="n">
         <v>44669</v>
       </c>
       <c r="B327" t="n">
@@ -3321,7 +3318,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="3" t="n">
+      <c r="A328" s="5" t="n">
         <v>44676</v>
       </c>
       <c r="B328" t="n">
@@ -3329,7 +3326,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="3" t="n">
+      <c r="A329" s="5" t="n">
         <v>44683</v>
       </c>
       <c r="B329" t="n">
@@ -3337,7 +3334,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="3" t="n">
+      <c r="A330" s="5" t="n">
         <v>44690</v>
       </c>
       <c r="B330" t="n">
@@ -3345,7 +3342,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="3" t="n">
+      <c r="A331" s="5" t="n">
         <v>44697</v>
       </c>
       <c r="B331" t="n">
@@ -3353,7 +3350,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="3" t="n">
+      <c r="A332" s="5" t="n">
         <v>44704</v>
       </c>
       <c r="B332" t="n">
@@ -3361,7 +3358,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="3" t="n">
+      <c r="A333" s="5" t="n">
         <v>44711</v>
       </c>
       <c r="B333" t="n">
@@ -3369,7 +3366,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="3" t="n">
+      <c r="A334" s="5" t="n">
         <v>44718</v>
       </c>
       <c r="B334" t="n">
@@ -3377,7 +3374,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="3" t="n">
+      <c r="A335" s="5" t="n">
         <v>44725</v>
       </c>
       <c r="B335" t="n">
@@ -3385,7 +3382,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="3" t="n">
+      <c r="A336" s="5" t="n">
         <v>44732</v>
       </c>
       <c r="B336" t="n">
@@ -3393,7 +3390,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="3" t="n">
+      <c r="A337" s="5" t="n">
         <v>44739</v>
       </c>
       <c r="B337" t="n">
@@ -3401,7 +3398,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="3" t="n">
+      <c r="A338" s="5" t="n">
         <v>44746</v>
       </c>
       <c r="B338" t="n">
@@ -3409,7 +3406,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="3" t="n">
+      <c r="A339" s="5" t="n">
         <v>44753</v>
       </c>
       <c r="B339" t="n">
@@ -3417,7 +3414,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="3" t="n">
+      <c r="A340" s="5" t="n">
         <v>44760</v>
       </c>
       <c r="B340" t="n">
@@ -3425,7 +3422,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="3" t="n">
+      <c r="A341" s="5" t="n">
         <v>44767</v>
       </c>
       <c r="B341" t="n">
@@ -3433,7 +3430,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="3" t="n">
+      <c r="A342" s="5" t="n">
         <v>44774</v>
       </c>
       <c r="B342" t="n">
@@ -3441,7 +3438,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="3" t="n">
+      <c r="A343" s="5" t="n">
         <v>44781</v>
       </c>
       <c r="B343" t="n">
@@ -3449,7 +3446,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="3" t="n">
+      <c r="A344" s="5" t="n">
         <v>44788</v>
       </c>
       <c r="B344" t="n">
@@ -3457,7 +3454,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="3" t="n">
+      <c r="A345" s="5" t="n">
         <v>44795</v>
       </c>
       <c r="B345" t="n">
@@ -3465,7 +3462,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="3" t="n">
+      <c r="A346" s="5" t="n">
         <v>44802</v>
       </c>
       <c r="B346" t="n">
@@ -3473,7 +3470,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="3" t="n">
+      <c r="A347" s="5" t="n">
         <v>44809</v>
       </c>
       <c r="B347" t="n">
@@ -3481,7 +3478,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="3" t="n">
+      <c r="A348" s="5" t="n">
         <v>44816</v>
       </c>
       <c r="B348" t="n">
@@ -3489,7 +3486,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="3" t="n">
+      <c r="A349" s="5" t="n">
         <v>44823</v>
       </c>
       <c r="B349" t="n">
@@ -3497,7 +3494,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="3" t="n">
+      <c r="A350" s="5" t="n">
         <v>44830</v>
       </c>
       <c r="B350" t="n">
@@ -3505,7 +3502,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="3" t="n">
+      <c r="A351" s="5" t="n">
         <v>44837</v>
       </c>
       <c r="B351" t="n">
@@ -3513,7 +3510,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="3" t="n">
+      <c r="A352" s="5" t="n">
         <v>44844</v>
       </c>
       <c r="B352" t="n">
@@ -3521,7 +3518,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="3" t="n">
+      <c r="A353" s="5" t="n">
         <v>44851</v>
       </c>
       <c r="B353" t="n">
@@ -3529,7 +3526,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="3" t="n">
+      <c r="A354" s="5" t="n">
         <v>44858</v>
       </c>
       <c r="B354" t="n">
@@ -3537,7 +3534,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="3" t="n">
+      <c r="A355" s="5" t="n">
         <v>44865</v>
       </c>
       <c r="B355" t="n">
@@ -3545,7 +3542,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="3" t="n">
+      <c r="A356" s="5" t="n">
         <v>44872</v>
       </c>
       <c r="B356" t="n">
@@ -3553,7 +3550,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="3" t="n">
+      <c r="A357" s="5" t="n">
         <v>44879</v>
       </c>
       <c r="B357" t="n">
@@ -3561,7 +3558,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="3" t="n">
+      <c r="A358" s="5" t="n">
         <v>44886</v>
       </c>
       <c r="B358" t="n">
@@ -3569,7 +3566,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="3" t="n">
+      <c r="A359" s="5" t="n">
         <v>44893</v>
       </c>
       <c r="B359" t="n">
@@ -3577,7 +3574,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="3" t="n">
+      <c r="A360" s="5" t="n">
         <v>44900</v>
       </c>
       <c r="B360" t="n">
@@ -3585,7 +3582,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="3" t="n">
+      <c r="A361" s="5" t="n">
         <v>44907</v>
       </c>
       <c r="B361" t="n">
@@ -3593,7 +3590,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="3" t="n">
+      <c r="A362" s="5" t="n">
         <v>44914</v>
       </c>
       <c r="B362" t="n">
@@ -3601,7 +3598,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="3" t="n">
+      <c r="A363" s="5" t="n">
         <v>44921</v>
       </c>
       <c r="B363" t="n">
@@ -3609,7 +3606,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="3" t="n">
+      <c r="A364" s="5" t="n">
         <v>44928</v>
       </c>
       <c r="B364" t="n">
@@ -3617,7 +3614,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="3" t="n">
+      <c r="A365" s="5" t="n">
         <v>44935</v>
       </c>
       <c r="B365" t="n">
@@ -3625,7 +3622,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="3" t="n">
+      <c r="A366" s="5" t="n">
         <v>44942</v>
       </c>
       <c r="B366" t="n">
@@ -3633,7 +3630,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="3" t="n">
+      <c r="A367" s="5" t="n">
         <v>44949</v>
       </c>
       <c r="B367" t="n">
@@ -3641,7 +3638,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="3" t="n">
+      <c r="A368" s="5" t="n">
         <v>44956</v>
       </c>
       <c r="B368" t="n">
@@ -3649,7 +3646,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="3" t="n">
+      <c r="A369" s="5" t="n">
         <v>44963</v>
       </c>
       <c r="B369" t="n">
@@ -3657,7 +3654,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="3" t="n">
+      <c r="A370" s="5" t="n">
         <v>44970</v>
       </c>
       <c r="B370" t="n">
@@ -3665,7 +3662,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="3" t="n">
+      <c r="A371" s="5" t="n">
         <v>44977</v>
       </c>
       <c r="B371" t="n">
@@ -3673,7 +3670,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="3" t="n">
+      <c r="A372" s="5" t="n">
         <v>44984</v>
       </c>
       <c r="B372" t="n">
@@ -3681,7 +3678,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="3" t="n">
+      <c r="A373" s="5" t="n">
         <v>44991</v>
       </c>
       <c r="B373" t="n">
@@ -3689,7 +3686,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="3" t="n">
+      <c r="A374" s="5" t="n">
         <v>44998</v>
       </c>
       <c r="B374" t="n">
@@ -3697,7 +3694,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="3" t="n">
+      <c r="A375" s="5" t="n">
         <v>45005</v>
       </c>
       <c r="B375" t="n">
@@ -3705,7 +3702,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="3" t="n">
+      <c r="A376" s="5" t="n">
         <v>45012</v>
       </c>
       <c r="B376" t="n">
@@ -3713,7 +3710,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="3" t="n">
+      <c r="A377" s="5" t="n">
         <v>45019</v>
       </c>
       <c r="B377" t="n">
@@ -3721,7 +3718,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="3" t="n">
+      <c r="A378" s="5" t="n">
         <v>45026</v>
       </c>
       <c r="B378" t="n">
@@ -3729,7 +3726,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="3" t="n">
+      <c r="A379" s="5" t="n">
         <v>45033</v>
       </c>
       <c r="B379" t="n">
@@ -3737,7 +3734,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="3" t="n">
+      <c r="A380" s="5" t="n">
         <v>45040</v>
       </c>
       <c r="B380" t="n">
@@ -3745,7 +3742,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="3" t="n">
+      <c r="A381" s="5" t="n">
         <v>45047</v>
       </c>
       <c r="B381" t="n">
@@ -3753,7 +3750,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="3" t="n">
+      <c r="A382" s="5" t="n">
         <v>45054</v>
       </c>
       <c r="B382" t="n">
@@ -3761,7 +3758,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="3" t="n">
+      <c r="A383" s="5" t="n">
         <v>45061</v>
       </c>
       <c r="B383" t="n">
@@ -3769,7 +3766,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="3" t="n">
+      <c r="A384" s="5" t="n">
         <v>45068</v>
       </c>
       <c r="B384" t="n">
@@ -3777,7 +3774,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="3" t="n">
+      <c r="A385" s="5" t="n">
         <v>45075</v>
       </c>
       <c r="B385" t="n">
@@ -3785,7 +3782,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="3" t="n">
+      <c r="A386" s="5" t="n">
         <v>45082</v>
       </c>
       <c r="B386" t="n">
@@ -3793,7 +3790,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="3" t="n">
+      <c r="A387" s="5" t="n">
         <v>45089</v>
       </c>
       <c r="B387" t="n">
@@ -3801,7 +3798,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="3" t="n">
+      <c r="A388" s="5" t="n">
         <v>45096</v>
       </c>
       <c r="B388" t="n">
@@ -3809,7 +3806,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="3" t="n">
+      <c r="A389" s="5" t="n">
         <v>45103</v>
       </c>
       <c r="B389" t="n">
@@ -3817,7 +3814,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="3" t="n">
+      <c r="A390" s="5" t="n">
         <v>45110</v>
       </c>
       <c r="B390" t="n">
@@ -3825,7 +3822,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="3" t="n">
+      <c r="A391" s="5" t="n">
         <v>45117</v>
       </c>
       <c r="B391" t="n">
@@ -3833,7 +3830,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="3" t="n">
+      <c r="A392" s="5" t="n">
         <v>45124</v>
       </c>
       <c r="B392" t="n">
@@ -3841,7 +3838,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="3" t="n">
+      <c r="A393" s="5" t="n">
         <v>45131</v>
       </c>
       <c r="B393" t="n">
@@ -3849,7 +3846,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="3" t="n">
+      <c r="A394" s="5" t="n">
         <v>45138</v>
       </c>
       <c r="B394" t="n">
@@ -3857,7 +3854,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="3" t="n">
+      <c r="A395" s="5" t="n">
         <v>45145</v>
       </c>
       <c r="B395" t="n">
@@ -3865,7 +3862,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="3" t="n">
+      <c r="A396" s="5" t="n">
         <v>45152</v>
       </c>
       <c r="B396" t="n">
@@ -3873,7 +3870,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="3" t="n">
+      <c r="A397" s="5" t="n">
         <v>45159</v>
       </c>
       <c r="B397" t="n">
@@ -3881,7 +3878,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="3" t="n">
+      <c r="A398" s="5" t="n">
         <v>45166</v>
       </c>
       <c r="B398" t="n">
@@ -3889,7 +3886,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="3" t="n">
+      <c r="A399" s="5" t="n">
         <v>45173</v>
       </c>
       <c r="B399" t="n">
@@ -3897,7 +3894,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="3" t="n">
+      <c r="A400" s="5" t="n">
         <v>45180</v>
       </c>
       <c r="B400" t="n">
@@ -3905,7 +3902,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="3" t="n">
+      <c r="A401" s="5" t="n">
         <v>45187</v>
       </c>
       <c r="B401" t="n">
@@ -3913,7 +3910,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="3" t="n">
+      <c r="A402" s="5" t="n">
         <v>45194</v>
       </c>
       <c r="B402" t="n">
@@ -3921,7 +3918,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="3" t="n">
+      <c r="A403" s="5" t="n">
         <v>45201</v>
       </c>
       <c r="B403" t="n">
@@ -3929,7 +3926,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="3" t="n">
+      <c r="A404" s="5" t="n">
         <v>45208</v>
       </c>
       <c r="B404" t="n">
@@ -3937,7 +3934,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="3" t="n">
+      <c r="A405" s="5" t="n">
         <v>45215</v>
       </c>
       <c r="B405" t="n">
@@ -3945,7 +3942,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="3" t="n">
+      <c r="A406" s="5" t="n">
         <v>45222</v>
       </c>
       <c r="B406" t="n">
@@ -3953,7 +3950,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="3" t="n">
+      <c r="A407" s="5" t="n">
         <v>45229</v>
       </c>
       <c r="B407" t="n">
@@ -3961,7 +3958,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="3" t="n">
+      <c r="A408" s="5" t="n">
         <v>45236</v>
       </c>
       <c r="B408" t="n">
@@ -3969,7 +3966,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="3" t="n">
+      <c r="A409" s="5" t="n">
         <v>45243</v>
       </c>
       <c r="B409" t="n">
@@ -3977,7 +3974,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="3" t="n">
+      <c r="A410" s="5" t="n">
         <v>45250</v>
       </c>
       <c r="B410" t="n">
@@ -3985,7 +3982,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="3" t="n">
+      <c r="A411" s="5" t="n">
         <v>45257</v>
       </c>
       <c r="B411" t="n">
@@ -3993,7 +3990,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="3" t="n">
+      <c r="A412" s="5" t="n">
         <v>45264</v>
       </c>
       <c r="B412" t="n">
@@ -4001,7 +3998,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="3" t="n">
+      <c r="A413" s="5" t="n">
         <v>45271</v>
       </c>
       <c r="B413" t="n">
@@ -4009,7 +4006,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="3" t="n">
+      <c r="A414" s="5" t="n">
         <v>45278</v>
       </c>
       <c r="B414" t="n">
@@ -4017,7 +4014,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="3" t="n">
+      <c r="A415" s="5" t="n">
         <v>45285</v>
       </c>
       <c r="B415" t="n">
@@ -4025,7 +4022,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="3" t="n">
+      <c r="A416" s="5" t="n">
         <v>45292</v>
       </c>
       <c r="B416" t="n">
@@ -4033,7 +4030,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="3" t="n">
+      <c r="A417" s="5" t="n">
         <v>45299</v>
       </c>
       <c r="B417" t="n">
@@ -4041,7 +4038,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="3" t="n">
+      <c r="A418" s="5" t="n">
         <v>45306</v>
       </c>
       <c r="B418" t="n">
@@ -4049,7 +4046,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="3" t="n">
+      <c r="A419" s="5" t="n">
         <v>45313</v>
       </c>
       <c r="B419" t="n">
@@ -4057,7 +4054,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="3" t="n">
+      <c r="A420" s="5" t="n">
         <v>45320</v>
       </c>
       <c r="B420" t="n">
@@ -4065,7 +4062,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="3" t="n">
+      <c r="A421" s="5" t="n">
         <v>45327</v>
       </c>
       <c r="B421" t="n">
@@ -4073,7 +4070,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="3" t="n">
+      <c r="A422" s="5" t="n">
         <v>45334</v>
       </c>
       <c r="B422" t="n">
@@ -4081,7 +4078,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="3" t="n">
+      <c r="A423" s="5" t="n">
         <v>45341</v>
       </c>
       <c r="B423" t="n">
@@ -4089,7 +4086,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="3" t="n">
+      <c r="A424" s="5" t="n">
         <v>45348</v>
       </c>
       <c r="B424" t="n">
@@ -4097,7 +4094,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="3" t="n">
+      <c r="A425" s="5" t="n">
         <v>45355</v>
       </c>
       <c r="B425" t="n">
@@ -4105,7 +4102,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="3" t="n">
+      <c r="A426" s="5" t="n">
         <v>45362</v>
       </c>
       <c r="B426" t="n">
@@ -4113,7 +4110,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="3" t="n">
+      <c r="A427" s="5" t="n">
         <v>45369</v>
       </c>
       <c r="B427" t="n">
@@ -4121,7 +4118,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="3" t="n">
+      <c r="A428" s="5" t="n">
         <v>45376</v>
       </c>
       <c r="B428" t="n">
@@ -4129,7 +4126,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="3" t="n">
+      <c r="A429" s="5" t="n">
         <v>45383</v>
       </c>
       <c r="B429" t="n">
@@ -4137,7 +4134,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="3" t="n">
+      <c r="A430" s="5" t="n">
         <v>45390</v>
       </c>
       <c r="B430" t="n">
@@ -4145,7 +4142,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="3" t="n">
+      <c r="A431" s="5" t="n">
         <v>45397</v>
       </c>
       <c r="B431" t="n">
@@ -4153,7 +4150,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="3" t="n">
+      <c r="A432" s="5" t="n">
         <v>45404</v>
       </c>
       <c r="B432" t="n">
@@ -4161,7 +4158,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="3" t="n">
+      <c r="A433" s="5" t="n">
         <v>45411</v>
       </c>
       <c r="B433" t="n">
@@ -4169,7 +4166,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="3" t="n">
+      <c r="A434" s="5" t="n">
         <v>45418</v>
       </c>
       <c r="B434" t="n">
@@ -4177,7 +4174,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="3" t="n">
+      <c r="A435" s="5" t="n">
         <v>45425</v>
       </c>
       <c r="B435" t="n">
@@ -4185,7 +4182,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="3" t="n">
+      <c r="A436" s="5" t="n">
         <v>45432</v>
       </c>
       <c r="B436" t="n">
@@ -4193,7 +4190,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="3" t="n">
+      <c r="A437" s="5" t="n">
         <v>45439</v>
       </c>
       <c r="B437" t="n">
@@ -4201,7 +4198,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="3" t="n">
+      <c r="A438" s="5" t="n">
         <v>45446</v>
       </c>
       <c r="B438" t="n">
@@ -4209,7 +4206,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="3" t="n">
+      <c r="A439" s="5" t="n">
         <v>45453</v>
       </c>
       <c r="B439" t="n">
@@ -4217,7 +4214,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="3" t="n">
+      <c r="A440" s="5" t="n">
         <v>45460</v>
       </c>
       <c r="B440" t="n">
@@ -4225,7 +4222,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="3" t="n">
+      <c r="A441" s="5" t="n">
         <v>45467</v>
       </c>
       <c r="B441" t="n">
@@ -4233,7 +4230,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="3" t="n">
+      <c r="A442" s="5" t="n">
         <v>45474</v>
       </c>
       <c r="B442" t="n">
@@ -4241,7 +4238,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="3" t="n">
+      <c r="A443" s="5" t="n">
         <v>45481</v>
       </c>
       <c r="B443" t="n">
@@ -4249,7 +4246,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="3" t="n">
+      <c r="A444" s="5" t="n">
         <v>45488</v>
       </c>
       <c r="B444" t="n">
@@ -4257,7 +4254,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="3" t="n">
+      <c r="A445" s="5" t="n">
         <v>45495</v>
       </c>
       <c r="B445" t="n">
@@ -4265,7 +4262,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="3" t="n">
+      <c r="A446" s="5" t="n">
         <v>45502</v>
       </c>
       <c r="B446" t="n">
@@ -4273,7 +4270,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="3" t="n">
+      <c r="A447" s="5" t="n">
         <v>45509</v>
       </c>
       <c r="B447" t="n">
@@ -4281,7 +4278,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="3" t="n">
+      <c r="A448" s="5" t="n">
         <v>45516</v>
       </c>
       <c r="B448" t="n">
@@ -4289,7 +4286,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="3" t="n">
+      <c r="A449" s="5" t="n">
         <v>45523</v>
       </c>
       <c r="B449" t="n">
@@ -4297,7 +4294,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="3" t="n">
+      <c r="A450" s="5" t="n">
         <v>45530</v>
       </c>
       <c r="B450" t="n">
@@ -4305,7 +4302,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="3" t="n">
+      <c r="A451" s="5" t="n">
         <v>45537</v>
       </c>
       <c r="B451" t="n">
@@ -4313,7 +4310,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="3" t="n">
+      <c r="A452" s="5" t="n">
         <v>45544</v>
       </c>
       <c r="B452" t="n">
@@ -4321,7 +4318,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="3" t="n">
+      <c r="A453" s="5" t="n">
         <v>45551</v>
       </c>
       <c r="B453" t="n">
@@ -4329,7 +4326,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="3" t="n">
+      <c r="A454" s="5" t="n">
         <v>45558</v>
       </c>
       <c r="B454" t="n">
@@ -4337,7 +4334,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="3" t="n">
+      <c r="A455" s="5" t="n">
         <v>45565</v>
       </c>
       <c r="B455" t="n">
@@ -4345,7 +4342,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="3" t="n">
+      <c r="A456" s="5" t="n">
         <v>45572</v>
       </c>
       <c r="B456" t="n">
@@ -4353,7 +4350,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="3" t="n">
+      <c r="A457" s="5" t="n">
         <v>45579</v>
       </c>
       <c r="B457" t="n">
@@ -4361,7 +4358,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="3" t="n">
+      <c r="A458" s="5" t="n">
         <v>45586</v>
       </c>
       <c r="B458" t="n">
@@ -4369,7 +4366,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="3" t="n">
+      <c r="A459" s="5" t="n">
         <v>45593</v>
       </c>
       <c r="B459" t="n">
@@ -4377,7 +4374,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="3" t="n">
+      <c r="A460" s="5" t="n">
         <v>45600</v>
       </c>
       <c r="B460" t="n">
@@ -4385,7 +4382,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="3" t="n">
+      <c r="A461" s="5" t="n">
         <v>45607</v>
       </c>
       <c r="B461" t="n">
@@ -4393,7 +4390,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="3" t="n">
+      <c r="A462" s="5" t="n">
         <v>45614</v>
       </c>
       <c r="B462" t="n">
@@ -4401,7 +4398,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="3" t="n">
+      <c r="A463" s="5" t="n">
         <v>45621</v>
       </c>
       <c r="B463" t="n">
@@ -4409,7 +4406,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="3" t="n">
+      <c r="A464" s="5" t="n">
         <v>45628</v>
       </c>
       <c r="B464" t="n">
@@ -4417,7 +4414,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="3" t="n">
+      <c r="A465" s="5" t="n">
         <v>45635</v>
       </c>
       <c r="B465" t="n">
@@ -4425,7 +4422,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="3" t="n">
+      <c r="A466" s="5" t="n">
         <v>45642</v>
       </c>
       <c r="B466" t="n">
@@ -4433,7 +4430,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="3" t="n">
+      <c r="A467" s="5" t="n">
         <v>45649</v>
       </c>
       <c r="B467" t="n">
@@ -4441,7 +4438,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="3" t="n">
+      <c r="A468" s="5" t="n">
         <v>45656</v>
       </c>
       <c r="B468" t="n">
@@ -4449,7 +4446,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="3" t="n">
+      <c r="A469" s="5" t="n">
         <v>45663</v>
       </c>
       <c r="B469" t="n">
@@ -4457,7 +4454,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="3" t="n">
+      <c r="A470" s="5" t="n">
         <v>45670</v>
       </c>
       <c r="B470" t="n">
@@ -4465,7 +4462,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="3" t="n">
+      <c r="A471" s="5" t="n">
         <v>45677</v>
       </c>
       <c r="B471" t="n">
@@ -4473,7 +4470,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="3" t="n">
+      <c r="A472" s="5" t="n">
         <v>45684</v>
       </c>
       <c r="B472" t="n">
@@ -4481,7 +4478,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="3" t="n">
+      <c r="A473" s="5" t="n">
         <v>45691</v>
       </c>
       <c r="B473" t="n">
@@ -4489,7 +4486,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="3" t="n">
+      <c r="A474" s="5" t="n">
         <v>45698</v>
       </c>
       <c r="B474" t="n">
@@ -4497,7 +4494,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="3" t="n">
+      <c r="A475" s="5" t="n">
         <v>45705</v>
       </c>
       <c r="B475" t="n">
@@ -4505,7 +4502,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="3" t="n">
+      <c r="A476" s="5" t="n">
         <v>45712</v>
       </c>
       <c r="B476" t="n">
@@ -4513,7 +4510,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="3" t="n">
+      <c r="A477" s="5" t="n">
         <v>45719</v>
       </c>
       <c r="B477" t="n">
@@ -4521,7 +4518,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="3" t="n">
+      <c r="A478" s="5" t="n">
         <v>45726</v>
       </c>
       <c r="B478" t="n">
@@ -4529,7 +4526,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="3" t="n">
+      <c r="A479" s="5" t="n">
         <v>45733</v>
       </c>
       <c r="B479" t="n">
@@ -4537,7 +4534,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="3" t="n">
+      <c r="A480" s="5" t="n">
         <v>45740</v>
       </c>
       <c r="B480" t="n">
@@ -4545,7 +4542,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="3" t="n">
+      <c r="A481" s="5" t="n">
         <v>45747</v>
       </c>
       <c r="B481" t="n">
@@ -4553,7 +4550,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="3" t="n">
+      <c r="A482" s="5" t="n">
         <v>45754</v>
       </c>
       <c r="B482" t="n">
@@ -4561,7 +4558,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="3" t="n">
+      <c r="A483" s="5" t="n">
         <v>45761</v>
       </c>
       <c r="B483" t="n">
@@ -4569,7 +4566,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="3" t="n">
+      <c r="A484" s="5" t="n">
         <v>45768</v>
       </c>
       <c r="B484" t="n">
@@ -4577,7 +4574,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="3" t="n">
+      <c r="A485" s="5" t="n">
         <v>45775</v>
       </c>
       <c r="B485" t="n">
@@ -4585,7 +4582,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="3" t="n">
+      <c r="A486" s="5" t="n">
         <v>45782</v>
       </c>
       <c r="B486" t="n">
@@ -4593,7 +4590,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="3" t="n">
+      <c r="A487" s="5" t="n">
         <v>45789</v>
       </c>
       <c r="B487" t="n">
@@ -4601,7 +4598,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="3" t="n">
+      <c r="A488" s="5" t="n">
         <v>45796</v>
       </c>
       <c r="B488" t="n">
@@ -4609,7 +4606,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="3" t="n">
+      <c r="A489" s="5" t="n">
         <v>45803</v>
       </c>
       <c r="B489" t="n">
@@ -4617,7 +4614,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="3" t="n">
+      <c r="A490" s="5" t="n">
         <v>45810</v>
       </c>
       <c r="B490" t="n">
@@ -4625,7 +4622,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="3" t="n">
+      <c r="A491" s="5" t="n">
         <v>45817</v>
       </c>
       <c r="B491" t="n">
@@ -4633,7 +4630,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="3" t="n">
+      <c r="A492" s="5" t="n">
         <v>45824</v>
       </c>
       <c r="B492" t="n">
@@ -4641,7 +4638,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="3" t="n">
+      <c r="A493" s="5" t="n">
         <v>45831</v>
       </c>
       <c r="B493" t="n">
@@ -4649,7 +4646,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="3" t="n">
+      <c r="A494" s="5" t="n">
         <v>45838</v>
       </c>
       <c r="B494" t="n">
@@ -4657,7 +4654,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="3" t="n">
+      <c r="A495" s="5" t="n">
         <v>45845</v>
       </c>
       <c r="B495" t="n">
@@ -4665,7 +4662,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="3" t="n">
+      <c r="A496" s="5" t="n">
         <v>45852</v>
       </c>
       <c r="B496" t="n">
@@ -4673,7 +4670,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="3" t="n">
+      <c r="A497" s="5" t="n">
         <v>45859</v>
       </c>
       <c r="B497" t="n">
@@ -4681,7 +4678,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="3" t="n">
+      <c r="A498" s="5" t="n">
         <v>45866</v>
       </c>
       <c r="B498" t="n">
@@ -4689,7 +4686,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="3" t="n">
+      <c r="A499" s="5" t="n">
         <v>45873</v>
       </c>
       <c r="B499" t="n">
@@ -4697,7 +4694,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="3" t="n">
+      <c r="A500" s="5" t="n">
         <v>45880</v>
       </c>
       <c r="B500" t="n">
@@ -4705,7 +4702,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="3" t="n">
+      <c r="A501" s="5" t="n">
         <v>45887</v>
       </c>
       <c r="B501" t="n">
@@ -4713,7 +4710,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="3" t="n">
+      <c r="A502" s="5" t="n">
         <v>45894</v>
       </c>
       <c r="B502" t="n">
@@ -4721,7 +4718,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="3" t="n">
+      <c r="A503" s="5" t="n">
         <v>45901</v>
       </c>
       <c r="B503" t="n">
@@ -4729,7 +4726,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="3" t="n">
+      <c r="A504" s="5" t="n">
         <v>45908</v>
       </c>
       <c r="B504" t="n">
@@ -4737,7 +4734,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="3" t="n">
+      <c r="A505" s="5" t="n">
         <v>45915</v>
       </c>
       <c r="B505" t="n">
@@ -4745,7 +4742,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="3" t="n">
+      <c r="A506" s="5" t="n">
         <v>45922</v>
       </c>
       <c r="B506" t="n">
@@ -4753,7 +4750,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="3" t="n">
+      <c r="A507" s="5" t="n">
         <v>45929</v>
       </c>
       <c r="B507" t="n">
@@ -4761,7 +4758,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="3" t="n">
+      <c r="A508" s="5" t="n">
         <v>45936</v>
       </c>
       <c r="B508" t="n">
@@ -4769,7 +4766,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="3" t="n">
+      <c r="A509" s="5" t="n">
         <v>45943</v>
       </c>
       <c r="B509" t="n">
@@ -4777,7 +4774,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="3" t="n">
+      <c r="A510" s="5" t="n">
         <v>45950</v>
       </c>
       <c r="B510" t="n">
@@ -4785,7 +4782,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="3" t="n">
+      <c r="A511" s="5" t="n">
         <v>45957</v>
       </c>
       <c r="B511" t="n">
@@ -4793,7 +4790,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="3" t="n">
+      <c r="A512" s="5" t="n">
         <v>45964</v>
       </c>
       <c r="B512" t="n">
@@ -4801,7 +4798,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="3" t="n">
+      <c r="A513" s="5" t="n">
         <v>45971</v>
       </c>
       <c r="B513" t="n">
@@ -4809,7 +4806,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="3" t="n">
+      <c r="A514" s="5" t="n">
         <v>45978</v>
       </c>
       <c r="B514" t="n">
@@ -4817,7 +4814,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="3" t="n">
+      <c r="A515" s="5" t="n">
         <v>45985</v>
       </c>
       <c r="B515" t="n">
@@ -4825,7 +4822,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="3" t="n">
+      <c r="A516" s="5" t="n">
         <v>45992</v>
       </c>
       <c r="B516" t="n">
@@ -4833,7 +4830,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="3" t="n">
+      <c r="A517" s="5" t="n">
         <v>45999</v>
       </c>
       <c r="B517" t="n">
@@ -4841,7 +4838,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="3" t="n">
+      <c r="A518" s="5" t="n">
         <v>46006</v>
       </c>
       <c r="B518" t="n">
@@ -4849,7 +4846,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="3" t="n">
+      <c r="A519" s="5" t="n">
         <v>46013</v>
       </c>
       <c r="B519" t="n">
@@ -4857,7 +4854,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="3" t="n">
+      <c r="A520" s="5" t="n">
         <v>46020</v>
       </c>
       <c r="B520" t="n">
@@ -4865,7 +4862,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="3" t="n">
+      <c r="A521" s="5" t="n">
         <v>46027</v>
       </c>
       <c r="B521" t="n">
@@ -4873,7 +4870,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="3" t="n">
+      <c r="A522" s="5" t="n">
         <v>46034</v>
       </c>
       <c r="B522" t="n">
@@ -4881,7 +4878,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="3" t="n">
+      <c r="A523" s="5" t="n">
         <v>46041</v>
       </c>
       <c r="B523" t="n">
@@ -4889,7 +4886,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="3" t="n">
+      <c r="A524" s="5" t="n">
         <v>46048</v>
       </c>
       <c r="B524" t="n">
@@ -4897,7 +4894,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="3" t="n">
+      <c r="A525" s="5" t="n">
         <v>46055</v>
       </c>
       <c r="B525" t="n">
@@ -4905,7 +4902,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="3" t="n">
+      <c r="A526" s="5" t="n">
         <v>46062</v>
       </c>
       <c r="B526" t="n">
@@ -4913,7 +4910,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="3" t="n">
+      <c r="A527" s="5" t="n">
         <v>46069</v>
       </c>
       <c r="B527" t="n">
@@ -4921,7 +4918,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="3" t="n">
+      <c r="A528" s="5" t="n">
         <v>46076</v>
       </c>
       <c r="B528" t="n">
@@ -4929,7 +4926,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="3" t="n">
+      <c r="A529" s="5" t="n">
         <v>46083</v>
       </c>
       <c r="B529" t="n">
@@ -4937,7 +4934,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="3" t="n">
+      <c r="A530" s="5" t="n">
         <v>46090</v>
       </c>
       <c r="B530" t="n">
@@ -4945,7 +4942,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="3" t="n">
+      <c r="A531" s="5" t="n">
         <v>46097</v>
       </c>
       <c r="B531" t="n">
@@ -4953,7 +4950,7 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="3" t="n">
+      <c r="A532" s="5" t="n">
         <v>46104</v>
       </c>
       <c r="B532" t="n">
@@ -4961,7 +4958,7 @@
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="3" t="n">
+      <c r="A533" s="5" t="n">
         <v>46111</v>
       </c>
       <c r="B533" t="n">
@@ -4969,7 +4966,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="3" t="n">
+      <c r="A534" s="5" t="n">
         <v>46118</v>
       </c>
       <c r="B534" t="n">
@@ -4977,7 +4974,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="3" t="n">
+      <c r="A535" s="5" t="n">
         <v>46125</v>
       </c>
       <c r="B535" t="n">
@@ -4985,7 +4982,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="3" t="n">
+      <c r="A536" s="5" t="n">
         <v>46132</v>
       </c>
       <c r="B536" t="n">
@@ -4993,7 +4990,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="3" t="n">
+      <c r="A537" s="5" t="n">
         <v>46139</v>
       </c>
       <c r="B537" t="n">
@@ -5001,7 +4998,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="3" t="n">
+      <c r="A538" s="5" t="n">
         <v>46146</v>
       </c>
       <c r="B538" t="n">
@@ -5009,7 +5006,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="3" t="n">
+      <c r="A539" s="5" t="n">
         <v>46153</v>
       </c>
       <c r="B539" t="n">
@@ -5017,7 +5014,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="3" t="n">
+      <c r="A540" s="5" t="n">
         <v>46160</v>
       </c>
       <c r="B540" t="n">
@@ -5025,7 +5022,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="3" t="n">
+      <c r="A541" s="5" t="n">
         <v>46167</v>
       </c>
       <c r="B541" t="n">
@@ -5033,7 +5030,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="3" t="n">
+      <c r="A542" s="5" t="n">
         <v>46174</v>
       </c>
       <c r="B542" t="n">
@@ -5041,7 +5038,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="3" t="n">
+      <c r="A543" s="5" t="n">
         <v>46181</v>
       </c>
       <c r="B543" t="n">
@@ -5049,7 +5046,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="3" t="n">
+      <c r="A544" s="5" t="n">
         <v>46188</v>
       </c>
       <c r="B544" t="n">
@@ -5057,7 +5054,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="3" t="n">
+      <c r="A545" s="5" t="n">
         <v>46195</v>
       </c>
       <c r="B545" t="n">
@@ -5065,7 +5062,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="3" t="n">
+      <c r="A546" s="5" t="n">
         <v>46202</v>
       </c>
       <c r="B546" t="n">
@@ -5073,7 +5070,7 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="3" t="n">
+      <c r="A547" s="5" t="n">
         <v>46209</v>
       </c>
       <c r="B547" t="n">
@@ -5081,7 +5078,7 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="3" t="n">
+      <c r="A548" s="5" t="n">
         <v>46216</v>
       </c>
       <c r="B548" t="n">
@@ -5089,7 +5086,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="3" t="n">
+      <c r="A549" s="5" t="n">
         <v>46223</v>
       </c>
       <c r="B549" t="n">
@@ -5097,7 +5094,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="3" t="n">
+      <c r="A550" s="5" t="n">
         <v>46230</v>
       </c>
       <c r="B550" t="n">
@@ -5105,7 +5102,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="3" t="n">
+      <c r="A551" s="5" t="n">
         <v>46237</v>
       </c>
       <c r="B551" t="n">
@@ -5113,7 +5110,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="3" t="n">
+      <c r="A552" s="5" t="n">
         <v>46244</v>
       </c>
       <c r="B552" t="n">
@@ -5121,7 +5118,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="3" t="n">
+      <c r="A553" s="5" t="n">
         <v>46251</v>
       </c>
       <c r="B553" t="n">
@@ -5129,7 +5126,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="3" t="n">
+      <c r="A554" s="5" t="n">
         <v>46258</v>
       </c>
       <c r="B554" t="n">
@@ -5137,7 +5134,7 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="3" t="n">
+      <c r="A555" s="5" t="n">
         <v>46265</v>
       </c>
       <c r="B555" t="n">
@@ -5145,7 +5142,7 @@
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="3" t="n">
+      <c r="A556" s="5" t="n">
         <v>46272</v>
       </c>
       <c r="B556" t="n">
@@ -5153,7 +5150,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="3" t="n">
+      <c r="A557" s="5" t="n">
         <v>46279</v>
       </c>
       <c r="B557" t="n">
@@ -5161,7 +5158,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="3" t="n">
+      <c r="A558" s="5" t="n">
         <v>46286</v>
       </c>
       <c r="B558" t="n">
@@ -5169,7 +5166,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="3" t="n">
+      <c r="A559" s="5" t="n">
         <v>46293</v>
       </c>
       <c r="B559" t="n">
@@ -5177,7 +5174,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="3" t="n">
+      <c r="A560" s="5" t="n">
         <v>46300</v>
       </c>
       <c r="B560" t="n">
@@ -5185,7 +5182,7 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="3" t="n">
+      <c r="A561" s="5" t="n">
         <v>46307</v>
       </c>
       <c r="B561" t="n">

--- a/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
+++ b/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
@@ -20,8 +20,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -61,13 +61,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -624,6 +623,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
@@ -638,6 +638,7 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
@@ -652,6 +653,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
@@ -666,6 +668,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
@@ -710,7 +713,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>42394</v>
       </c>
       <c r="B2" t="n">
@@ -718,7 +721,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>42401</v>
       </c>
       <c r="B3" t="n">
@@ -726,7 +729,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>42408</v>
       </c>
       <c r="B4" t="n">
@@ -734,7 +737,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>42415</v>
       </c>
       <c r="B5" t="n">
@@ -742,7 +745,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="3" t="n">
         <v>42422</v>
       </c>
       <c r="B6" t="n">
@@ -750,7 +753,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="3" t="n">
         <v>42429</v>
       </c>
       <c r="B7" t="n">
@@ -758,7 +761,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="3" t="n">
         <v>42436</v>
       </c>
       <c r="B8" t="n">
@@ -766,7 +769,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="3" t="n">
         <v>42443</v>
       </c>
       <c r="B9" t="n">
@@ -774,7 +777,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="3" t="n">
         <v>42450</v>
       </c>
       <c r="B10" t="n">
@@ -782,7 +785,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="n">
+      <c r="A11" s="3" t="n">
         <v>42457</v>
       </c>
       <c r="B11" t="n">
@@ -790,7 +793,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="n">
+      <c r="A12" s="3" t="n">
         <v>42464</v>
       </c>
       <c r="B12" t="n">
@@ -798,7 +801,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="n">
+      <c r="A13" s="3" t="n">
         <v>42471</v>
       </c>
       <c r="B13" t="n">
@@ -806,7 +809,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="n">
+      <c r="A14" s="3" t="n">
         <v>42478</v>
       </c>
       <c r="B14" t="n">
@@ -814,7 +817,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="n">
+      <c r="A15" s="3" t="n">
         <v>42485</v>
       </c>
       <c r="B15" t="n">
@@ -822,7 +825,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="n">
+      <c r="A16" s="3" t="n">
         <v>42492</v>
       </c>
       <c r="B16" t="n">
@@ -830,7 +833,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="n">
+      <c r="A17" s="3" t="n">
         <v>42499</v>
       </c>
       <c r="B17" t="n">
@@ -838,7 +841,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="n">
+      <c r="A18" s="3" t="n">
         <v>42506</v>
       </c>
       <c r="B18" t="n">
@@ -846,7 +849,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="n">
+      <c r="A19" s="3" t="n">
         <v>42513</v>
       </c>
       <c r="B19" t="n">
@@ -854,7 +857,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="n">
+      <c r="A20" s="3" t="n">
         <v>42520</v>
       </c>
       <c r="B20" t="n">
@@ -862,7 +865,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="n">
+      <c r="A21" s="3" t="n">
         <v>42527</v>
       </c>
       <c r="B21" t="n">
@@ -870,7 +873,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="n">
+      <c r="A22" s="3" t="n">
         <v>42534</v>
       </c>
       <c r="B22" t="n">
@@ -878,7 +881,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="n">
+      <c r="A23" s="3" t="n">
         <v>42541</v>
       </c>
       <c r="B23" t="n">
@@ -886,7 +889,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="n">
+      <c r="A24" s="3" t="n">
         <v>42548</v>
       </c>
       <c r="B24" t="n">
@@ -894,7 +897,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="n">
+      <c r="A25" s="3" t="n">
         <v>42555</v>
       </c>
       <c r="B25" t="n">
@@ -902,7 +905,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="n">
+      <c r="A26" s="3" t="n">
         <v>42562</v>
       </c>
       <c r="B26" t="n">
@@ -910,7 +913,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="n">
+      <c r="A27" s="3" t="n">
         <v>42569</v>
       </c>
       <c r="B27" t="n">
@@ -918,7 +921,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="n">
+      <c r="A28" s="3" t="n">
         <v>42576</v>
       </c>
       <c r="B28" t="n">
@@ -926,7 +929,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="n">
+      <c r="A29" s="3" t="n">
         <v>42583</v>
       </c>
       <c r="B29" t="n">
@@ -934,7 +937,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="n">
+      <c r="A30" s="3" t="n">
         <v>42590</v>
       </c>
       <c r="B30" t="n">
@@ -942,7 +945,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="n">
+      <c r="A31" s="3" t="n">
         <v>42597</v>
       </c>
       <c r="B31" t="n">
@@ -950,7 +953,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="n">
+      <c r="A32" s="3" t="n">
         <v>42604</v>
       </c>
       <c r="B32" t="n">
@@ -958,7 +961,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="n">
+      <c r="A33" s="3" t="n">
         <v>42611</v>
       </c>
       <c r="B33" t="n">
@@ -966,7 +969,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="n">
+      <c r="A34" s="3" t="n">
         <v>42618</v>
       </c>
       <c r="B34" t="n">
@@ -974,7 +977,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="n">
+      <c r="A35" s="3" t="n">
         <v>42625</v>
       </c>
       <c r="B35" t="n">
@@ -982,7 +985,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="n">
+      <c r="A36" s="3" t="n">
         <v>42632</v>
       </c>
       <c r="B36" t="n">
@@ -990,7 +993,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="n">
+      <c r="A37" s="3" t="n">
         <v>42639</v>
       </c>
       <c r="B37" t="n">
@@ -998,7 +1001,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="n">
+      <c r="A38" s="3" t="n">
         <v>42646</v>
       </c>
       <c r="B38" t="n">
@@ -1006,7 +1009,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="n">
+      <c r="A39" s="3" t="n">
         <v>42653</v>
       </c>
       <c r="B39" t="n">
@@ -1014,7 +1017,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="n">
+      <c r="A40" s="3" t="n">
         <v>42660</v>
       </c>
       <c r="B40" t="n">
@@ -1022,7 +1025,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="n">
+      <c r="A41" s="3" t="n">
         <v>42667</v>
       </c>
       <c r="B41" t="n">
@@ -1030,7 +1033,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="n">
+      <c r="A42" s="3" t="n">
         <v>42674</v>
       </c>
       <c r="B42" t="n">
@@ -1038,7 +1041,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="n">
+      <c r="A43" s="3" t="n">
         <v>42681</v>
       </c>
       <c r="B43" t="n">
@@ -1046,7 +1049,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="n">
+      <c r="A44" s="3" t="n">
         <v>42688</v>
       </c>
       <c r="B44" t="n">
@@ -1054,7 +1057,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="n">
+      <c r="A45" s="3" t="n">
         <v>42695</v>
       </c>
       <c r="B45" t="n">
@@ -1062,7 +1065,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="n">
+      <c r="A46" s="3" t="n">
         <v>42702</v>
       </c>
       <c r="B46" t="n">
@@ -1070,7 +1073,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="n">
+      <c r="A47" s="3" t="n">
         <v>42709</v>
       </c>
       <c r="B47" t="n">
@@ -1078,7 +1081,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="n">
+      <c r="A48" s="3" t="n">
         <v>42716</v>
       </c>
       <c r="B48" t="n">
@@ -1086,7 +1089,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="n">
+      <c r="A49" s="3" t="n">
         <v>42723</v>
       </c>
       <c r="B49" t="n">
@@ -1094,7 +1097,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="n">
+      <c r="A50" s="3" t="n">
         <v>42730</v>
       </c>
       <c r="B50" t="n">
@@ -1102,7 +1105,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="n">
+      <c r="A51" s="3" t="n">
         <v>42737</v>
       </c>
       <c r="B51" t="n">
@@ -1110,7 +1113,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="n">
+      <c r="A52" s="3" t="n">
         <v>42744</v>
       </c>
       <c r="B52" t="n">
@@ -1118,7 +1121,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="5" t="n">
+      <c r="A53" s="3" t="n">
         <v>42751</v>
       </c>
       <c r="B53" t="n">
@@ -1126,7 +1129,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="5" t="n">
+      <c r="A54" s="3" t="n">
         <v>42758</v>
       </c>
       <c r="B54" t="n">
@@ -1134,7 +1137,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="n">
+      <c r="A55" s="3" t="n">
         <v>42765</v>
       </c>
       <c r="B55" t="n">
@@ -1142,7 +1145,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="5" t="n">
+      <c r="A56" s="3" t="n">
         <v>42772</v>
       </c>
       <c r="B56" t="n">
@@ -1150,7 +1153,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="n">
+      <c r="A57" s="3" t="n">
         <v>42779</v>
       </c>
       <c r="B57" t="n">
@@ -1158,7 +1161,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="5" t="n">
+      <c r="A58" s="3" t="n">
         <v>42786</v>
       </c>
       <c r="B58" t="n">
@@ -1166,7 +1169,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="5" t="n">
+      <c r="A59" s="3" t="n">
         <v>42793</v>
       </c>
       <c r="B59" t="n">
@@ -1174,7 +1177,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="n">
+      <c r="A60" s="3" t="n">
         <v>42800</v>
       </c>
       <c r="B60" t="n">
@@ -1182,7 +1185,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="n">
+      <c r="A61" s="3" t="n">
         <v>42807</v>
       </c>
       <c r="B61" t="n">
@@ -1190,7 +1193,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="n">
+      <c r="A62" s="3" t="n">
         <v>42814</v>
       </c>
       <c r="B62" t="n">
@@ -1198,7 +1201,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="5" t="n">
+      <c r="A63" s="3" t="n">
         <v>42821</v>
       </c>
       <c r="B63" t="n">
@@ -1206,7 +1209,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="n">
+      <c r="A64" s="3" t="n">
         <v>42828</v>
       </c>
       <c r="B64" t="n">
@@ -1214,7 +1217,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="n">
+      <c r="A65" s="3" t="n">
         <v>42835</v>
       </c>
       <c r="B65" t="n">
@@ -1222,7 +1225,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="5" t="n">
+      <c r="A66" s="3" t="n">
         <v>42842</v>
       </c>
       <c r="B66" t="n">
@@ -1230,7 +1233,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="5" t="n">
+      <c r="A67" s="3" t="n">
         <v>42849</v>
       </c>
       <c r="B67" t="n">
@@ -1238,7 +1241,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="n">
+      <c r="A68" s="3" t="n">
         <v>42856</v>
       </c>
       <c r="B68" t="n">
@@ -1246,7 +1249,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="5" t="n">
+      <c r="A69" s="3" t="n">
         <v>42863</v>
       </c>
       <c r="B69" t="n">
@@ -1254,7 +1257,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="n">
+      <c r="A70" s="3" t="n">
         <v>42870</v>
       </c>
       <c r="B70" t="n">
@@ -1262,7 +1265,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="n">
+      <c r="A71" s="3" t="n">
         <v>42877</v>
       </c>
       <c r="B71" t="n">
@@ -1270,7 +1273,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="n">
+      <c r="A72" s="3" t="n">
         <v>42884</v>
       </c>
       <c r="B72" t="n">
@@ -1278,7 +1281,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="5" t="n">
+      <c r="A73" s="3" t="n">
         <v>42891</v>
       </c>
       <c r="B73" t="n">
@@ -1286,7 +1289,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="5" t="n">
+      <c r="A74" s="3" t="n">
         <v>42898</v>
       </c>
       <c r="B74" t="n">
@@ -1294,7 +1297,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="n">
+      <c r="A75" s="3" t="n">
         <v>42905</v>
       </c>
       <c r="B75" t="n">
@@ -1302,7 +1305,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="n">
+      <c r="A76" s="3" t="n">
         <v>42912</v>
       </c>
       <c r="B76" t="n">
@@ -1310,7 +1313,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="5" t="n">
+      <c r="A77" s="3" t="n">
         <v>42919</v>
       </c>
       <c r="B77" t="n">
@@ -1318,7 +1321,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="5" t="n">
+      <c r="A78" s="3" t="n">
         <v>42926</v>
       </c>
       <c r="B78" t="n">
@@ -1326,7 +1329,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="n">
+      <c r="A79" s="3" t="n">
         <v>42933</v>
       </c>
       <c r="B79" t="n">
@@ -1334,7 +1337,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="n">
+      <c r="A80" s="3" t="n">
         <v>42940</v>
       </c>
       <c r="B80" t="n">
@@ -1342,7 +1345,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="n">
+      <c r="A81" s="3" t="n">
         <v>42947</v>
       </c>
       <c r="B81" t="n">
@@ -1350,7 +1353,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="n">
+      <c r="A82" s="3" t="n">
         <v>42954</v>
       </c>
       <c r="B82" t="n">
@@ -1358,7 +1361,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="5" t="n">
+      <c r="A83" s="3" t="n">
         <v>42961</v>
       </c>
       <c r="B83" t="n">
@@ -1366,7 +1369,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="n">
+      <c r="A84" s="3" t="n">
         <v>42968</v>
       </c>
       <c r="B84" t="n">
@@ -1374,7 +1377,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="n">
+      <c r="A85" s="3" t="n">
         <v>42975</v>
       </c>
       <c r="B85" t="n">
@@ -1382,7 +1385,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="n">
+      <c r="A86" s="3" t="n">
         <v>42982</v>
       </c>
       <c r="B86" t="n">
@@ -1390,7 +1393,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="n">
+      <c r="A87" s="3" t="n">
         <v>42989</v>
       </c>
       <c r="B87" t="n">
@@ -1398,7 +1401,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="5" t="n">
+      <c r="A88" s="3" t="n">
         <v>42996</v>
       </c>
       <c r="B88" t="n">
@@ -1406,7 +1409,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="5" t="n">
+      <c r="A89" s="3" t="n">
         <v>43003</v>
       </c>
       <c r="B89" t="n">
@@ -1414,7 +1417,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="n">
+      <c r="A90" s="3" t="n">
         <v>43010</v>
       </c>
       <c r="B90" t="n">
@@ -1422,7 +1425,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="n">
+      <c r="A91" s="3" t="n">
         <v>43017</v>
       </c>
       <c r="B91" t="n">
@@ -1430,7 +1433,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="n">
+      <c r="A92" s="3" t="n">
         <v>43024</v>
       </c>
       <c r="B92" t="n">
@@ -1438,7 +1441,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="5" t="n">
+      <c r="A93" s="3" t="n">
         <v>43031</v>
       </c>
       <c r="B93" t="n">
@@ -1446,7 +1449,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="n">
+      <c r="A94" s="3" t="n">
         <v>43038</v>
       </c>
       <c r="B94" t="n">
@@ -1454,7 +1457,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="n">
+      <c r="A95" s="3" t="n">
         <v>43045</v>
       </c>
       <c r="B95" t="n">
@@ -1462,7 +1465,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="n">
+      <c r="A96" s="3" t="n">
         <v>43052</v>
       </c>
       <c r="B96" t="n">
@@ -1470,7 +1473,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="n">
+      <c r="A97" s="3" t="n">
         <v>43059</v>
       </c>
       <c r="B97" t="n">
@@ -1478,7 +1481,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="5" t="n">
+      <c r="A98" s="3" t="n">
         <v>43066</v>
       </c>
       <c r="B98" t="n">
@@ -1486,7 +1489,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="n">
+      <c r="A99" s="3" t="n">
         <v>43073</v>
       </c>
       <c r="B99" t="n">
@@ -1494,7 +1497,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="n">
+      <c r="A100" s="3" t="n">
         <v>43080</v>
       </c>
       <c r="B100" t="n">
@@ -1502,7 +1505,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="5" t="n">
+      <c r="A101" s="3" t="n">
         <v>43087</v>
       </c>
       <c r="B101" t="n">
@@ -1510,7 +1513,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="5" t="n">
+      <c r="A102" s="3" t="n">
         <v>43094</v>
       </c>
       <c r="B102" t="n">
@@ -1518,7 +1521,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="5" t="n">
+      <c r="A103" s="3" t="n">
         <v>43101</v>
       </c>
       <c r="B103" t="n">
@@ -1526,7 +1529,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n">
+      <c r="A104" s="3" t="n">
         <v>43108</v>
       </c>
       <c r="B104" t="n">
@@ -1534,7 +1537,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n">
+      <c r="A105" s="3" t="n">
         <v>43115</v>
       </c>
       <c r="B105" t="n">
@@ -1542,7 +1545,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="n">
+      <c r="A106" s="3" t="n">
         <v>43122</v>
       </c>
       <c r="B106" t="n">
@@ -1550,7 +1553,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="n">
+      <c r="A107" s="3" t="n">
         <v>43129</v>
       </c>
       <c r="B107" t="n">
@@ -1558,7 +1561,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="n">
+      <c r="A108" s="3" t="n">
         <v>43136</v>
       </c>
       <c r="B108" t="n">
@@ -1566,7 +1569,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="5" t="n">
+      <c r="A109" s="3" t="n">
         <v>43143</v>
       </c>
       <c r="B109" t="n">
@@ -1574,7 +1577,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="n">
+      <c r="A110" s="3" t="n">
         <v>43150</v>
       </c>
       <c r="B110" t="n">
@@ -1582,7 +1585,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="n">
+      <c r="A111" s="3" t="n">
         <v>43157</v>
       </c>
       <c r="B111" t="n">
@@ -1590,7 +1593,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="n">
+      <c r="A112" s="3" t="n">
         <v>43164</v>
       </c>
       <c r="B112" t="n">
@@ -1598,7 +1601,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="5" t="n">
+      <c r="A113" s="3" t="n">
         <v>43171</v>
       </c>
       <c r="B113" t="n">
@@ -1606,7 +1609,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="n">
+      <c r="A114" s="3" t="n">
         <v>43178</v>
       </c>
       <c r="B114" t="n">
@@ -1614,7 +1617,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="n">
+      <c r="A115" s="3" t="n">
         <v>43185</v>
       </c>
       <c r="B115" t="n">
@@ -1622,7 +1625,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="n">
+      <c r="A116" s="3" t="n">
         <v>43192</v>
       </c>
       <c r="B116" t="n">
@@ -1630,7 +1633,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="n">
+      <c r="A117" s="3" t="n">
         <v>43199</v>
       </c>
       <c r="B117" t="n">
@@ -1638,7 +1641,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="n">
+      <c r="A118" s="3" t="n">
         <v>43206</v>
       </c>
       <c r="B118" t="n">
@@ -1646,7 +1649,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="5" t="n">
+      <c r="A119" s="3" t="n">
         <v>43213</v>
       </c>
       <c r="B119" t="n">
@@ -1654,7 +1657,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="n">
+      <c r="A120" s="3" t="n">
         <v>43220</v>
       </c>
       <c r="B120" t="n">
@@ -1662,7 +1665,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="5" t="n">
+      <c r="A121" s="3" t="n">
         <v>43227</v>
       </c>
       <c r="B121" t="n">
@@ -1670,7 +1673,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="n">
+      <c r="A122" s="3" t="n">
         <v>43234</v>
       </c>
       <c r="B122" t="n">
@@ -1678,7 +1681,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="5" t="n">
+      <c r="A123" s="3" t="n">
         <v>43241</v>
       </c>
       <c r="B123" t="n">
@@ -1686,7 +1689,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="5" t="n">
+      <c r="A124" s="3" t="n">
         <v>43248</v>
       </c>
       <c r="B124" t="n">
@@ -1694,7 +1697,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="n">
+      <c r="A125" s="3" t="n">
         <v>43255</v>
       </c>
       <c r="B125" t="n">
@@ -1702,7 +1705,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="n">
+      <c r="A126" s="3" t="n">
         <v>43262</v>
       </c>
       <c r="B126" t="n">
@@ -1710,7 +1713,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="5" t="n">
+      <c r="A127" s="3" t="n">
         <v>43269</v>
       </c>
       <c r="B127" t="n">
@@ -1718,7 +1721,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="5" t="n">
+      <c r="A128" s="3" t="n">
         <v>43276</v>
       </c>
       <c r="B128" t="n">
@@ -1726,7 +1729,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="n">
+      <c r="A129" s="3" t="n">
         <v>43283</v>
       </c>
       <c r="B129" t="n">
@@ -1734,7 +1737,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="n">
+      <c r="A130" s="3" t="n">
         <v>43290</v>
       </c>
       <c r="B130" t="n">
@@ -1742,7 +1745,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="n">
+      <c r="A131" s="3" t="n">
         <v>43297</v>
       </c>
       <c r="B131" t="n">
@@ -1750,7 +1753,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="n">
+      <c r="A132" s="3" t="n">
         <v>43304</v>
       </c>
       <c r="B132" t="n">
@@ -1758,7 +1761,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="n">
+      <c r="A133" s="3" t="n">
         <v>43311</v>
       </c>
       <c r="B133" t="n">
@@ -1766,7 +1769,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="5" t="n">
+      <c r="A134" s="3" t="n">
         <v>43318</v>
       </c>
       <c r="B134" t="n">
@@ -1774,7 +1777,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="5" t="n">
+      <c r="A135" s="3" t="n">
         <v>43325</v>
       </c>
       <c r="B135" t="n">
@@ -1782,7 +1785,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="n">
+      <c r="A136" s="3" t="n">
         <v>43332</v>
       </c>
       <c r="B136" t="n">
@@ -1790,7 +1793,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="n">
+      <c r="A137" s="3" t="n">
         <v>43339</v>
       </c>
       <c r="B137" t="n">
@@ -1798,7 +1801,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="5" t="n">
+      <c r="A138" s="3" t="n">
         <v>43346</v>
       </c>
       <c r="B138" t="n">
@@ -1806,7 +1809,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="5" t="n">
+      <c r="A139" s="3" t="n">
         <v>43353</v>
       </c>
       <c r="B139" t="n">
@@ -1814,7 +1817,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="n">
+      <c r="A140" s="3" t="n">
         <v>43360</v>
       </c>
       <c r="B140" t="n">
@@ -1822,7 +1825,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="5" t="n">
+      <c r="A141" s="3" t="n">
         <v>43367</v>
       </c>
       <c r="B141" t="n">
@@ -1830,7 +1833,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="5" t="n">
+      <c r="A142" s="3" t="n">
         <v>43374</v>
       </c>
       <c r="B142" t="n">
@@ -1838,7 +1841,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="n">
+      <c r="A143" s="3" t="n">
         <v>43381</v>
       </c>
       <c r="B143" t="n">
@@ -1846,7 +1849,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="n">
+      <c r="A144" s="3" t="n">
         <v>43388</v>
       </c>
       <c r="B144" t="n">
@@ -1854,7 +1857,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="n">
+      <c r="A145" s="3" t="n">
         <v>43395</v>
       </c>
       <c r="B145" t="n">
@@ -1862,7 +1865,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="5" t="n">
+      <c r="A146" s="3" t="n">
         <v>43402</v>
       </c>
       <c r="B146" t="n">
@@ -1870,7 +1873,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="5" t="n">
+      <c r="A147" s="3" t="n">
         <v>43409</v>
       </c>
       <c r="B147" t="n">
@@ -1878,7 +1881,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="n">
+      <c r="A148" s="3" t="n">
         <v>43416</v>
       </c>
       <c r="B148" t="n">
@@ -1886,7 +1889,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="n">
+      <c r="A149" s="3" t="n">
         <v>43423</v>
       </c>
       <c r="B149" t="n">
@@ -1894,7 +1897,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="5" t="n">
+      <c r="A150" s="3" t="n">
         <v>43430</v>
       </c>
       <c r="B150" t="n">
@@ -1902,7 +1905,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="5" t="n">
+      <c r="A151" s="3" t="n">
         <v>43437</v>
       </c>
       <c r="B151" t="n">
@@ -1910,7 +1913,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="n">
+      <c r="A152" s="3" t="n">
         <v>43444</v>
       </c>
       <c r="B152" t="n">
@@ -1918,7 +1921,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="n">
+      <c r="A153" s="3" t="n">
         <v>43451</v>
       </c>
       <c r="B153" t="n">
@@ -1926,7 +1929,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="n">
+      <c r="A154" s="3" t="n">
         <v>43458</v>
       </c>
       <c r="B154" t="n">
@@ -1934,7 +1937,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="n">
+      <c r="A155" s="3" t="n">
         <v>43465</v>
       </c>
       <c r="B155" t="n">
@@ -1942,7 +1945,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="n">
+      <c r="A156" s="3" t="n">
         <v>43472</v>
       </c>
       <c r="B156" t="n">
@@ -1950,7 +1953,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="n">
+      <c r="A157" s="3" t="n">
         <v>43479</v>
       </c>
       <c r="B157" t="n">
@@ -1958,7 +1961,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="n">
+      <c r="A158" s="3" t="n">
         <v>43486</v>
       </c>
       <c r="B158" t="n">
@@ -1966,7 +1969,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="n">
+      <c r="A159" s="3" t="n">
         <v>43493</v>
       </c>
       <c r="B159" t="n">
@@ -1974,7 +1977,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="n">
+      <c r="A160" s="3" t="n">
         <v>43500</v>
       </c>
       <c r="B160" t="n">
@@ -1982,7 +1985,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="n">
+      <c r="A161" s="3" t="n">
         <v>43507</v>
       </c>
       <c r="B161" t="n">
@@ -1990,7 +1993,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="n">
+      <c r="A162" s="3" t="n">
         <v>43514</v>
       </c>
       <c r="B162" t="n">
@@ -1998,7 +2001,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="n">
+      <c r="A163" s="3" t="n">
         <v>43521</v>
       </c>
       <c r="B163" t="n">
@@ -2006,7 +2009,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="n">
+      <c r="A164" s="3" t="n">
         <v>43528</v>
       </c>
       <c r="B164" t="n">
@@ -2014,7 +2017,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="n">
+      <c r="A165" s="3" t="n">
         <v>43535</v>
       </c>
       <c r="B165" t="n">
@@ -2022,7 +2025,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="n">
+      <c r="A166" s="3" t="n">
         <v>43542</v>
       </c>
       <c r="B166" t="n">
@@ -2030,7 +2033,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="n">
+      <c r="A167" s="3" t="n">
         <v>43549</v>
       </c>
       <c r="B167" t="n">
@@ -2038,7 +2041,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="n">
+      <c r="A168" s="3" t="n">
         <v>43556</v>
       </c>
       <c r="B168" t="n">
@@ -2046,7 +2049,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="n">
+      <c r="A169" s="3" t="n">
         <v>43563</v>
       </c>
       <c r="B169" t="n">
@@ -2054,7 +2057,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="n">
+      <c r="A170" s="3" t="n">
         <v>43570</v>
       </c>
       <c r="B170" t="n">
@@ -2062,7 +2065,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="n">
+      <c r="A171" s="3" t="n">
         <v>43577</v>
       </c>
       <c r="B171" t="n">
@@ -2070,7 +2073,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="n">
+      <c r="A172" s="3" t="n">
         <v>43584</v>
       </c>
       <c r="B172" t="n">
@@ -2078,7 +2081,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="n">
+      <c r="A173" s="3" t="n">
         <v>43591</v>
       </c>
       <c r="B173" t="n">
@@ -2086,7 +2089,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="n">
+      <c r="A174" s="3" t="n">
         <v>43598</v>
       </c>
       <c r="B174" t="n">
@@ -2094,7 +2097,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="n">
+      <c r="A175" s="3" t="n">
         <v>43605</v>
       </c>
       <c r="B175" t="n">
@@ -2102,7 +2105,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="n">
+      <c r="A176" s="3" t="n">
         <v>43612</v>
       </c>
       <c r="B176" t="n">
@@ -2110,7 +2113,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="n">
+      <c r="A177" s="3" t="n">
         <v>43619</v>
       </c>
       <c r="B177" t="n">
@@ -2118,7 +2121,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="n">
+      <c r="A178" s="3" t="n">
         <v>43626</v>
       </c>
       <c r="B178" t="n">
@@ -2126,7 +2129,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="n">
+      <c r="A179" s="3" t="n">
         <v>43633</v>
       </c>
       <c r="B179" t="n">
@@ -2134,7 +2137,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="n">
+      <c r="A180" s="3" t="n">
         <v>43640</v>
       </c>
       <c r="B180" t="n">
@@ -2142,7 +2145,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="n">
+      <c r="A181" s="3" t="n">
         <v>43647</v>
       </c>
       <c r="B181" t="n">
@@ -2150,7 +2153,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="n">
+      <c r="A182" s="3" t="n">
         <v>43654</v>
       </c>
       <c r="B182" t="n">
@@ -2158,7 +2161,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="n">
+      <c r="A183" s="3" t="n">
         <v>43661</v>
       </c>
       <c r="B183" t="n">
@@ -2166,7 +2169,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="n">
+      <c r="A184" s="3" t="n">
         <v>43668</v>
       </c>
       <c r="B184" t="n">
@@ -2174,7 +2177,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="n">
+      <c r="A185" s="3" t="n">
         <v>43675</v>
       </c>
       <c r="B185" t="n">
@@ -2182,7 +2185,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="n">
+      <c r="A186" s="3" t="n">
         <v>43682</v>
       </c>
       <c r="B186" t="n">
@@ -2190,7 +2193,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="n">
+      <c r="A187" s="3" t="n">
         <v>43689</v>
       </c>
       <c r="B187" t="n">
@@ -2198,7 +2201,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="n">
+      <c r="A188" s="3" t="n">
         <v>43696</v>
       </c>
       <c r="B188" t="n">
@@ -2206,7 +2209,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="n">
+      <c r="A189" s="3" t="n">
         <v>43703</v>
       </c>
       <c r="B189" t="n">
@@ -2214,7 +2217,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="n">
+      <c r="A190" s="3" t="n">
         <v>43710</v>
       </c>
       <c r="B190" t="n">
@@ -2222,7 +2225,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="n">
+      <c r="A191" s="3" t="n">
         <v>43717</v>
       </c>
       <c r="B191" t="n">
@@ -2230,7 +2233,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="n">
+      <c r="A192" s="3" t="n">
         <v>43724</v>
       </c>
       <c r="B192" t="n">
@@ -2238,7 +2241,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="n">
+      <c r="A193" s="3" t="n">
         <v>43731</v>
       </c>
       <c r="B193" t="n">
@@ -2246,7 +2249,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="5" t="n">
+      <c r="A194" s="3" t="n">
         <v>43738</v>
       </c>
       <c r="B194" t="n">
@@ -2254,7 +2257,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="5" t="n">
+      <c r="A195" s="3" t="n">
         <v>43745</v>
       </c>
       <c r="B195" t="n">
@@ -2262,7 +2265,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="n">
+      <c r="A196" s="3" t="n">
         <v>43752</v>
       </c>
       <c r="B196" t="n">
@@ -2270,7 +2273,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="n">
+      <c r="A197" s="3" t="n">
         <v>43759</v>
       </c>
       <c r="B197" t="n">
@@ -2278,7 +2281,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="n">
+      <c r="A198" s="3" t="n">
         <v>43766</v>
       </c>
       <c r="B198" t="n">
@@ -2286,7 +2289,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="n">
+      <c r="A199" s="3" t="n">
         <v>43773</v>
       </c>
       <c r="B199" t="n">
@@ -2294,7 +2297,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="5" t="n">
+      <c r="A200" s="3" t="n">
         <v>43780</v>
       </c>
       <c r="B200" t="n">
@@ -2302,7 +2305,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="n">
+      <c r="A201" s="3" t="n">
         <v>43787</v>
       </c>
       <c r="B201" t="n">
@@ -2310,7 +2313,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="n">
+      <c r="A202" s="3" t="n">
         <v>43794</v>
       </c>
       <c r="B202" t="n">
@@ -2318,7 +2321,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="5" t="n">
+      <c r="A203" s="3" t="n">
         <v>43801</v>
       </c>
       <c r="B203" t="n">
@@ -2326,7 +2329,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="n">
+      <c r="A204" s="3" t="n">
         <v>43808</v>
       </c>
       <c r="B204" t="n">
@@ -2334,7 +2337,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="n">
+      <c r="A205" s="3" t="n">
         <v>43815</v>
       </c>
       <c r="B205" t="n">
@@ -2342,7 +2345,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="5" t="n">
+      <c r="A206" s="3" t="n">
         <v>43822</v>
       </c>
       <c r="B206" t="n">
@@ -2350,7 +2353,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="n">
+      <c r="A207" s="3" t="n">
         <v>43829</v>
       </c>
       <c r="B207" t="n">
@@ -2358,7 +2361,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="5" t="n">
+      <c r="A208" s="3" t="n">
         <v>43836</v>
       </c>
       <c r="B208" t="n">
@@ -2366,7 +2369,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="5" t="n">
+      <c r="A209" s="3" t="n">
         <v>43843</v>
       </c>
       <c r="B209" t="n">
@@ -2374,7 +2377,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="n">
+      <c r="A210" s="3" t="n">
         <v>43850</v>
       </c>
       <c r="B210" t="n">
@@ -2382,7 +2385,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="n">
+      <c r="A211" s="3" t="n">
         <v>43857</v>
       </c>
       <c r="B211" t="n">
@@ -2390,7 +2393,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="n">
+      <c r="A212" s="3" t="n">
         <v>43864</v>
       </c>
       <c r="B212" t="n">
@@ -2398,7 +2401,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="n">
+      <c r="A213" s="3" t="n">
         <v>43871</v>
       </c>
       <c r="B213" t="n">
@@ -2406,7 +2409,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="n">
+      <c r="A214" s="3" t="n">
         <v>43878</v>
       </c>
       <c r="B214" t="n">
@@ -2414,7 +2417,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="n">
+      <c r="A215" s="3" t="n">
         <v>43885</v>
       </c>
       <c r="B215" t="n">
@@ -2422,7 +2425,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="n">
+      <c r="A216" s="3" t="n">
         <v>43892</v>
       </c>
       <c r="B216" t="n">
@@ -2430,7 +2433,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="n">
+      <c r="A217" s="3" t="n">
         <v>43899</v>
       </c>
       <c r="B217" t="n">
@@ -2438,7 +2441,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="5" t="n">
+      <c r="A218" s="3" t="n">
         <v>43906</v>
       </c>
       <c r="B218" t="n">
@@ -2446,7 +2449,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="5" t="n">
+      <c r="A219" s="3" t="n">
         <v>43913</v>
       </c>
       <c r="B219" t="n">
@@ -2454,7 +2457,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="5" t="n">
+      <c r="A220" s="3" t="n">
         <v>43920</v>
       </c>
       <c r="B220" t="n">
@@ -2462,7 +2465,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="5" t="n">
+      <c r="A221" s="3" t="n">
         <v>43927</v>
       </c>
       <c r="B221" t="n">
@@ -2470,7 +2473,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="5" t="n">
+      <c r="A222" s="3" t="n">
         <v>43934</v>
       </c>
       <c r="B222" t="n">
@@ -2478,7 +2481,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="n">
+      <c r="A223" s="3" t="n">
         <v>43941</v>
       </c>
       <c r="B223" t="n">
@@ -2486,7 +2489,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="5" t="n">
+      <c r="A224" s="3" t="n">
         <v>43948</v>
       </c>
       <c r="B224" t="n">
@@ -2494,7 +2497,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="5" t="n">
+      <c r="A225" s="3" t="n">
         <v>43955</v>
       </c>
       <c r="B225" t="n">
@@ -2502,7 +2505,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="n">
+      <c r="A226" s="3" t="n">
         <v>43962</v>
       </c>
       <c r="B226" t="n">
@@ -2510,7 +2513,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="5" t="n">
+      <c r="A227" s="3" t="n">
         <v>43969</v>
       </c>
       <c r="B227" t="n">
@@ -2518,7 +2521,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="5" t="n">
+      <c r="A228" s="3" t="n">
         <v>43976</v>
       </c>
       <c r="B228" t="n">
@@ -2526,7 +2529,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="5" t="n">
+      <c r="A229" s="3" t="n">
         <v>43983</v>
       </c>
       <c r="B229" t="n">
@@ -2534,7 +2537,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="n">
+      <c r="A230" s="3" t="n">
         <v>43990</v>
       </c>
       <c r="B230" t="n">
@@ -2542,7 +2545,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="n">
+      <c r="A231" s="3" t="n">
         <v>43997</v>
       </c>
       <c r="B231" t="n">
@@ -2550,7 +2553,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="n">
+      <c r="A232" s="3" t="n">
         <v>44004</v>
       </c>
       <c r="B232" t="n">
@@ -2558,7 +2561,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="n">
+      <c r="A233" s="3" t="n">
         <v>44011</v>
       </c>
       <c r="B233" t="n">
@@ -2566,7 +2569,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="5" t="n">
+      <c r="A234" s="3" t="n">
         <v>44018</v>
       </c>
       <c r="B234" t="n">
@@ -2574,7 +2577,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="5" t="n">
+      <c r="A235" s="3" t="n">
         <v>44025</v>
       </c>
       <c r="B235" t="n">
@@ -2582,7 +2585,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="n">
+      <c r="A236" s="3" t="n">
         <v>44032</v>
       </c>
       <c r="B236" t="n">
@@ -2590,7 +2593,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="n">
+      <c r="A237" s="3" t="n">
         <v>44039</v>
       </c>
       <c r="B237" t="n">
@@ -2598,7 +2601,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="n">
+      <c r="A238" s="3" t="n">
         <v>44046</v>
       </c>
       <c r="B238" t="n">
@@ -2606,7 +2609,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="n">
+      <c r="A239" s="3" t="n">
         <v>44053</v>
       </c>
       <c r="B239" t="n">
@@ -2614,7 +2617,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="n">
+      <c r="A240" s="3" t="n">
         <v>44060</v>
       </c>
       <c r="B240" t="n">
@@ -2622,7 +2625,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="n">
+      <c r="A241" s="3" t="n">
         <v>44067</v>
       </c>
       <c r="B241" t="n">
@@ -2630,7 +2633,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="n">
+      <c r="A242" s="3" t="n">
         <v>44074</v>
       </c>
       <c r="B242" t="n">
@@ -2638,7 +2641,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="n">
+      <c r="A243" s="3" t="n">
         <v>44081</v>
       </c>
       <c r="B243" t="n">
@@ -2646,7 +2649,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="n">
+      <c r="A244" s="3" t="n">
         <v>44088</v>
       </c>
       <c r="B244" t="n">
@@ -2654,7 +2657,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="n">
+      <c r="A245" s="3" t="n">
         <v>44095</v>
       </c>
       <c r="B245" t="n">
@@ -2662,7 +2665,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="5" t="n">
+      <c r="A246" s="3" t="n">
         <v>44102</v>
       </c>
       <c r="B246" t="n">
@@ -2670,7 +2673,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="5" t="n">
+      <c r="A247" s="3" t="n">
         <v>44109</v>
       </c>
       <c r="B247" t="n">
@@ -2678,7 +2681,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="5" t="n">
+      <c r="A248" s="3" t="n">
         <v>44116</v>
       </c>
       <c r="B248" t="n">
@@ -2686,7 +2689,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="5" t="n">
+      <c r="A249" s="3" t="n">
         <v>44123</v>
       </c>
       <c r="B249" t="n">
@@ -2694,7 +2697,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="n">
+      <c r="A250" s="3" t="n">
         <v>44130</v>
       </c>
       <c r="B250" t="n">
@@ -2702,7 +2705,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="5" t="n">
+      <c r="A251" s="3" t="n">
         <v>44137</v>
       </c>
       <c r="B251" t="n">
@@ -2710,7 +2713,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="5" t="n">
+      <c r="A252" s="3" t="n">
         <v>44144</v>
       </c>
       <c r="B252" t="n">
@@ -2718,7 +2721,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="n">
+      <c r="A253" s="3" t="n">
         <v>44151</v>
       </c>
       <c r="B253" t="n">
@@ -2726,7 +2729,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="5" t="n">
+      <c r="A254" s="3" t="n">
         <v>44158</v>
       </c>
       <c r="B254" t="n">
@@ -2734,7 +2737,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="n">
+      <c r="A255" s="3" t="n">
         <v>44165</v>
       </c>
       <c r="B255" t="n">
@@ -2742,7 +2745,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="5" t="n">
+      <c r="A256" s="3" t="n">
         <v>44172</v>
       </c>
       <c r="B256" t="n">
@@ -2750,7 +2753,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="5" t="n">
+      <c r="A257" s="3" t="n">
         <v>44179</v>
       </c>
       <c r="B257" t="n">
@@ -2758,7 +2761,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="5" t="n">
+      <c r="A258" s="3" t="n">
         <v>44186</v>
       </c>
       <c r="B258" t="n">
@@ -2766,7 +2769,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="5" t="n">
+      <c r="A259" s="3" t="n">
         <v>44193</v>
       </c>
       <c r="B259" t="n">
@@ -2774,7 +2777,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="n">
+      <c r="A260" s="3" t="n">
         <v>44200</v>
       </c>
       <c r="B260" t="n">
@@ -2782,7 +2785,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="5" t="n">
+      <c r="A261" s="3" t="n">
         <v>44207</v>
       </c>
       <c r="B261" t="n">
@@ -2790,7 +2793,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="5" t="n">
+      <c r="A262" s="3" t="n">
         <v>44214</v>
       </c>
       <c r="B262" t="n">
@@ -2798,7 +2801,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="5" t="n">
+      <c r="A263" s="3" t="n">
         <v>44221</v>
       </c>
       <c r="B263" t="n">
@@ -2806,7 +2809,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="5" t="n">
+      <c r="A264" s="3" t="n">
         <v>44228</v>
       </c>
       <c r="B264" t="n">
@@ -2814,7 +2817,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="n">
+      <c r="A265" s="3" t="n">
         <v>44235</v>
       </c>
       <c r="B265" t="n">
@@ -2822,7 +2825,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="n">
+      <c r="A266" s="3" t="n">
         <v>44242</v>
       </c>
       <c r="B266" t="n">
@@ -2830,7 +2833,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="n">
+      <c r="A267" s="3" t="n">
         <v>44249</v>
       </c>
       <c r="B267" t="n">
@@ -2838,7 +2841,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="n">
+      <c r="A268" s="3" t="n">
         <v>44256</v>
       </c>
       <c r="B268" t="n">
@@ -2846,7 +2849,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="n">
+      <c r="A269" s="3" t="n">
         <v>44263</v>
       </c>
       <c r="B269" t="n">
@@ -2854,7 +2857,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="n">
+      <c r="A270" s="3" t="n">
         <v>44270</v>
       </c>
       <c r="B270" t="n">
@@ -2862,7 +2865,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="n">
+      <c r="A271" s="3" t="n">
         <v>44277</v>
       </c>
       <c r="B271" t="n">
@@ -2870,7 +2873,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="5" t="n">
+      <c r="A272" s="3" t="n">
         <v>44284</v>
       </c>
       <c r="B272" t="n">
@@ -2878,7 +2881,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="5" t="n">
+      <c r="A273" s="3" t="n">
         <v>44291</v>
       </c>
       <c r="B273" t="n">
@@ -2886,7 +2889,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="5" t="n">
+      <c r="A274" s="3" t="n">
         <v>44298</v>
       </c>
       <c r="B274" t="n">
@@ -2894,7 +2897,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="5" t="n">
+      <c r="A275" s="3" t="n">
         <v>44305</v>
       </c>
       <c r="B275" t="n">
@@ -2902,7 +2905,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="5" t="n">
+      <c r="A276" s="3" t="n">
         <v>44312</v>
       </c>
       <c r="B276" t="n">
@@ -2910,7 +2913,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="5" t="n">
+      <c r="A277" s="3" t="n">
         <v>44319</v>
       </c>
       <c r="B277" t="n">
@@ -2918,7 +2921,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="5" t="n">
+      <c r="A278" s="3" t="n">
         <v>44326</v>
       </c>
       <c r="B278" t="n">
@@ -2926,7 +2929,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="5" t="n">
+      <c r="A279" s="3" t="n">
         <v>44333</v>
       </c>
       <c r="B279" t="n">
@@ -2934,7 +2937,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="5" t="n">
+      <c r="A280" s="3" t="n">
         <v>44340</v>
       </c>
       <c r="B280" t="n">
@@ -2942,7 +2945,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="5" t="n">
+      <c r="A281" s="3" t="n">
         <v>44347</v>
       </c>
       <c r="B281" t="n">
@@ -2950,7 +2953,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="5" t="n">
+      <c r="A282" s="3" t="n">
         <v>44354</v>
       </c>
       <c r="B282" t="n">
@@ -2958,7 +2961,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="5" t="n">
+      <c r="A283" s="3" t="n">
         <v>44361</v>
       </c>
       <c r="B283" t="n">
@@ -2966,7 +2969,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="5" t="n">
+      <c r="A284" s="3" t="n">
         <v>44368</v>
       </c>
       <c r="B284" t="n">
@@ -2974,7 +2977,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="5" t="n">
+      <c r="A285" s="3" t="n">
         <v>44375</v>
       </c>
       <c r="B285" t="n">
@@ -2982,7 +2985,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="5" t="n">
+      <c r="A286" s="3" t="n">
         <v>44382</v>
       </c>
       <c r="B286" t="n">
@@ -2990,7 +2993,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="5" t="n">
+      <c r="A287" s="3" t="n">
         <v>44389</v>
       </c>
       <c r="B287" t="n">
@@ -2998,7 +3001,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="5" t="n">
+      <c r="A288" s="3" t="n">
         <v>44396</v>
       </c>
       <c r="B288" t="n">
@@ -3006,7 +3009,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="5" t="n">
+      <c r="A289" s="3" t="n">
         <v>44403</v>
       </c>
       <c r="B289" t="n">
@@ -3014,7 +3017,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="5" t="n">
+      <c r="A290" s="3" t="n">
         <v>44410</v>
       </c>
       <c r="B290" t="n">
@@ -3022,7 +3025,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="5" t="n">
+      <c r="A291" s="3" t="n">
         <v>44417</v>
       </c>
       <c r="B291" t="n">
@@ -3030,7 +3033,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="5" t="n">
+      <c r="A292" s="3" t="n">
         <v>44424</v>
       </c>
       <c r="B292" t="n">
@@ -3038,7 +3041,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="n">
+      <c r="A293" s="3" t="n">
         <v>44431</v>
       </c>
       <c r="B293" t="n">
@@ -3046,7 +3049,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="n">
+      <c r="A294" s="3" t="n">
         <v>44438</v>
       </c>
       <c r="B294" t="n">
@@ -3054,7 +3057,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="n">
+      <c r="A295" s="3" t="n">
         <v>44445</v>
       </c>
       <c r="B295" t="n">
@@ -3062,7 +3065,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="5" t="n">
+      <c r="A296" s="3" t="n">
         <v>44452</v>
       </c>
       <c r="B296" t="n">
@@ -3070,7 +3073,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="5" t="n">
+      <c r="A297" s="3" t="n">
         <v>44459</v>
       </c>
       <c r="B297" t="n">
@@ -3078,7 +3081,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="5" t="n">
+      <c r="A298" s="3" t="n">
         <v>44466</v>
       </c>
       <c r="B298" t="n">
@@ -3086,7 +3089,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="5" t="n">
+      <c r="A299" s="3" t="n">
         <v>44473</v>
       </c>
       <c r="B299" t="n">
@@ -3094,7 +3097,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="5" t="n">
+      <c r="A300" s="3" t="n">
         <v>44480</v>
       </c>
       <c r="B300" t="n">
@@ -3102,7 +3105,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="5" t="n">
+      <c r="A301" s="3" t="n">
         <v>44487</v>
       </c>
       <c r="B301" t="n">
@@ -3110,7 +3113,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="5" t="n">
+      <c r="A302" s="3" t="n">
         <v>44494</v>
       </c>
       <c r="B302" t="n">
@@ -3118,7 +3121,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="5" t="n">
+      <c r="A303" s="3" t="n">
         <v>44501</v>
       </c>
       <c r="B303" t="n">
@@ -3126,7 +3129,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="5" t="n">
+      <c r="A304" s="3" t="n">
         <v>44508</v>
       </c>
       <c r="B304" t="n">
@@ -3134,7 +3137,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="5" t="n">
+      <c r="A305" s="3" t="n">
         <v>44515</v>
       </c>
       <c r="B305" t="n">
@@ -3142,7 +3145,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="5" t="n">
+      <c r="A306" s="3" t="n">
         <v>44522</v>
       </c>
       <c r="B306" t="n">
@@ -3150,7 +3153,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="5" t="n">
+      <c r="A307" s="3" t="n">
         <v>44529</v>
       </c>
       <c r="B307" t="n">
@@ -3158,7 +3161,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="5" t="n">
+      <c r="A308" s="3" t="n">
         <v>44536</v>
       </c>
       <c r="B308" t="n">
@@ -3166,7 +3169,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="5" t="n">
+      <c r="A309" s="3" t="n">
         <v>44543</v>
       </c>
       <c r="B309" t="n">
@@ -3174,7 +3177,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="5" t="n">
+      <c r="A310" s="3" t="n">
         <v>44550</v>
       </c>
       <c r="B310" t="n">
@@ -3182,7 +3185,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="5" t="n">
+      <c r="A311" s="3" t="n">
         <v>44557</v>
       </c>
       <c r="B311" t="n">
@@ -3190,7 +3193,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="5" t="n">
+      <c r="A312" s="3" t="n">
         <v>44564</v>
       </c>
       <c r="B312" t="n">
@@ -3198,7 +3201,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="5" t="n">
+      <c r="A313" s="3" t="n">
         <v>44571</v>
       </c>
       <c r="B313" t="n">
@@ -3206,7 +3209,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="5" t="n">
+      <c r="A314" s="3" t="n">
         <v>44578</v>
       </c>
       <c r="B314" t="n">
@@ -3214,7 +3217,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="5" t="n">
+      <c r="A315" s="3" t="n">
         <v>44585</v>
       </c>
       <c r="B315" t="n">
@@ -3222,7 +3225,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="5" t="n">
+      <c r="A316" s="3" t="n">
         <v>44592</v>
       </c>
       <c r="B316" t="n">
@@ -3230,7 +3233,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="5" t="n">
+      <c r="A317" s="3" t="n">
         <v>44599</v>
       </c>
       <c r="B317" t="n">
@@ -3238,7 +3241,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="5" t="n">
+      <c r="A318" s="3" t="n">
         <v>44606</v>
       </c>
       <c r="B318" t="n">
@@ -3246,7 +3249,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="5" t="n">
+      <c r="A319" s="3" t="n">
         <v>44613</v>
       </c>
       <c r="B319" t="n">
@@ -3254,7 +3257,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="5" t="n">
+      <c r="A320" s="3" t="n">
         <v>44620</v>
       </c>
       <c r="B320" t="n">
@@ -3262,7 +3265,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="5" t="n">
+      <c r="A321" s="3" t="n">
         <v>44627</v>
       </c>
       <c r="B321" t="n">
@@ -3270,7 +3273,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="5" t="n">
+      <c r="A322" s="3" t="n">
         <v>44634</v>
       </c>
       <c r="B322" t="n">
@@ -3278,7 +3281,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="5" t="n">
+      <c r="A323" s="3" t="n">
         <v>44641</v>
       </c>
       <c r="B323" t="n">
@@ -3286,7 +3289,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="5" t="n">
+      <c r="A324" s="3" t="n">
         <v>44648</v>
       </c>
       <c r="B324" t="n">
@@ -3294,7 +3297,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="5" t="n">
+      <c r="A325" s="3" t="n">
         <v>44655</v>
       </c>
       <c r="B325" t="n">
@@ -3302,7 +3305,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="5" t="n">
+      <c r="A326" s="3" t="n">
         <v>44662</v>
       </c>
       <c r="B326" t="n">
@@ -3310,7 +3313,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="5" t="n">
+      <c r="A327" s="3" t="n">
         <v>44669</v>
       </c>
       <c r="B327" t="n">
@@ -3318,7 +3321,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="5" t="n">
+      <c r="A328" s="3" t="n">
         <v>44676</v>
       </c>
       <c r="B328" t="n">
@@ -3326,7 +3329,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="5" t="n">
+      <c r="A329" s="3" t="n">
         <v>44683</v>
       </c>
       <c r="B329" t="n">
@@ -3334,7 +3337,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="5" t="n">
+      <c r="A330" s="3" t="n">
         <v>44690</v>
       </c>
       <c r="B330" t="n">
@@ -3342,7 +3345,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="5" t="n">
+      <c r="A331" s="3" t="n">
         <v>44697</v>
       </c>
       <c r="B331" t="n">
@@ -3350,7 +3353,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="5" t="n">
+      <c r="A332" s="3" t="n">
         <v>44704</v>
       </c>
       <c r="B332" t="n">
@@ -3358,7 +3361,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="5" t="n">
+      <c r="A333" s="3" t="n">
         <v>44711</v>
       </c>
       <c r="B333" t="n">
@@ -3366,7 +3369,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="5" t="n">
+      <c r="A334" s="3" t="n">
         <v>44718</v>
       </c>
       <c r="B334" t="n">
@@ -3374,7 +3377,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="5" t="n">
+      <c r="A335" s="3" t="n">
         <v>44725</v>
       </c>
       <c r="B335" t="n">
@@ -3382,7 +3385,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="5" t="n">
+      <c r="A336" s="3" t="n">
         <v>44732</v>
       </c>
       <c r="B336" t="n">
@@ -3390,7 +3393,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="5" t="n">
+      <c r="A337" s="3" t="n">
         <v>44739</v>
       </c>
       <c r="B337" t="n">
@@ -3398,7 +3401,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="5" t="n">
+      <c r="A338" s="3" t="n">
         <v>44746</v>
       </c>
       <c r="B338" t="n">
@@ -3406,7 +3409,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="5" t="n">
+      <c r="A339" s="3" t="n">
         <v>44753</v>
       </c>
       <c r="B339" t="n">
@@ -3414,7 +3417,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="5" t="n">
+      <c r="A340" s="3" t="n">
         <v>44760</v>
       </c>
       <c r="B340" t="n">
@@ -3422,7 +3425,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="5" t="n">
+      <c r="A341" s="3" t="n">
         <v>44767</v>
       </c>
       <c r="B341" t="n">
@@ -3430,7 +3433,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="5" t="n">
+      <c r="A342" s="3" t="n">
         <v>44774</v>
       </c>
       <c r="B342" t="n">
@@ -3438,7 +3441,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="5" t="n">
+      <c r="A343" s="3" t="n">
         <v>44781</v>
       </c>
       <c r="B343" t="n">
@@ -3446,7 +3449,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="5" t="n">
+      <c r="A344" s="3" t="n">
         <v>44788</v>
       </c>
       <c r="B344" t="n">
@@ -3454,7 +3457,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="5" t="n">
+      <c r="A345" s="3" t="n">
         <v>44795</v>
       </c>
       <c r="B345" t="n">
@@ -3462,7 +3465,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="5" t="n">
+      <c r="A346" s="3" t="n">
         <v>44802</v>
       </c>
       <c r="B346" t="n">
@@ -3470,7 +3473,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="5" t="n">
+      <c r="A347" s="3" t="n">
         <v>44809</v>
       </c>
       <c r="B347" t="n">
@@ -3478,7 +3481,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="5" t="n">
+      <c r="A348" s="3" t="n">
         <v>44816</v>
       </c>
       <c r="B348" t="n">
@@ -3486,7 +3489,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="5" t="n">
+      <c r="A349" s="3" t="n">
         <v>44823</v>
       </c>
       <c r="B349" t="n">
@@ -3494,7 +3497,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="5" t="n">
+      <c r="A350" s="3" t="n">
         <v>44830</v>
       </c>
       <c r="B350" t="n">
@@ -3502,7 +3505,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="5" t="n">
+      <c r="A351" s="3" t="n">
         <v>44837</v>
       </c>
       <c r="B351" t="n">
@@ -3510,7 +3513,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="5" t="n">
+      <c r="A352" s="3" t="n">
         <v>44844</v>
       </c>
       <c r="B352" t="n">
@@ -3518,7 +3521,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="5" t="n">
+      <c r="A353" s="3" t="n">
         <v>44851</v>
       </c>
       <c r="B353" t="n">
@@ -3526,7 +3529,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="5" t="n">
+      <c r="A354" s="3" t="n">
         <v>44858</v>
       </c>
       <c r="B354" t="n">
@@ -3534,7 +3537,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="5" t="n">
+      <c r="A355" s="3" t="n">
         <v>44865</v>
       </c>
       <c r="B355" t="n">
@@ -3542,7 +3545,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="5" t="n">
+      <c r="A356" s="3" t="n">
         <v>44872</v>
       </c>
       <c r="B356" t="n">
@@ -3550,7 +3553,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="5" t="n">
+      <c r="A357" s="3" t="n">
         <v>44879</v>
       </c>
       <c r="B357" t="n">
@@ -3558,7 +3561,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="5" t="n">
+      <c r="A358" s="3" t="n">
         <v>44886</v>
       </c>
       <c r="B358" t="n">
@@ -3566,7 +3569,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="5" t="n">
+      <c r="A359" s="3" t="n">
         <v>44893</v>
       </c>
       <c r="B359" t="n">
@@ -3574,7 +3577,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="5" t="n">
+      <c r="A360" s="3" t="n">
         <v>44900</v>
       </c>
       <c r="B360" t="n">
@@ -3582,7 +3585,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="5" t="n">
+      <c r="A361" s="3" t="n">
         <v>44907</v>
       </c>
       <c r="B361" t="n">
@@ -3590,7 +3593,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="5" t="n">
+      <c r="A362" s="3" t="n">
         <v>44914</v>
       </c>
       <c r="B362" t="n">
@@ -3598,7 +3601,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="5" t="n">
+      <c r="A363" s="3" t="n">
         <v>44921</v>
       </c>
       <c r="B363" t="n">
@@ -3606,7 +3609,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="5" t="n">
+      <c r="A364" s="3" t="n">
         <v>44928</v>
       </c>
       <c r="B364" t="n">
@@ -3614,7 +3617,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="5" t="n">
+      <c r="A365" s="3" t="n">
         <v>44935</v>
       </c>
       <c r="B365" t="n">
@@ -3622,7 +3625,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="5" t="n">
+      <c r="A366" s="3" t="n">
         <v>44942</v>
       </c>
       <c r="B366" t="n">
@@ -3630,7 +3633,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="5" t="n">
+      <c r="A367" s="3" t="n">
         <v>44949</v>
       </c>
       <c r="B367" t="n">
@@ -3638,7 +3641,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="5" t="n">
+      <c r="A368" s="3" t="n">
         <v>44956</v>
       </c>
       <c r="B368" t="n">
@@ -3646,7 +3649,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="5" t="n">
+      <c r="A369" s="3" t="n">
         <v>44963</v>
       </c>
       <c r="B369" t="n">
@@ -3654,7 +3657,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="5" t="n">
+      <c r="A370" s="3" t="n">
         <v>44970</v>
       </c>
       <c r="B370" t="n">
@@ -3662,7 +3665,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="5" t="n">
+      <c r="A371" s="3" t="n">
         <v>44977</v>
       </c>
       <c r="B371" t="n">
@@ -3670,7 +3673,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="5" t="n">
+      <c r="A372" s="3" t="n">
         <v>44984</v>
       </c>
       <c r="B372" t="n">
@@ -3678,7 +3681,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="5" t="n">
+      <c r="A373" s="3" t="n">
         <v>44991</v>
       </c>
       <c r="B373" t="n">
@@ -3686,7 +3689,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="5" t="n">
+      <c r="A374" s="3" t="n">
         <v>44998</v>
       </c>
       <c r="B374" t="n">
@@ -3694,7 +3697,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="5" t="n">
+      <c r="A375" s="3" t="n">
         <v>45005</v>
       </c>
       <c r="B375" t="n">
@@ -3702,7 +3705,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="5" t="n">
+      <c r="A376" s="3" t="n">
         <v>45012</v>
       </c>
       <c r="B376" t="n">
@@ -3710,7 +3713,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="5" t="n">
+      <c r="A377" s="3" t="n">
         <v>45019</v>
       </c>
       <c r="B377" t="n">
@@ -3718,7 +3721,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="5" t="n">
+      <c r="A378" s="3" t="n">
         <v>45026</v>
       </c>
       <c r="B378" t="n">
@@ -3726,7 +3729,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="5" t="n">
+      <c r="A379" s="3" t="n">
         <v>45033</v>
       </c>
       <c r="B379" t="n">
@@ -3734,7 +3737,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="5" t="n">
+      <c r="A380" s="3" t="n">
         <v>45040</v>
       </c>
       <c r="B380" t="n">
@@ -3742,7 +3745,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="5" t="n">
+      <c r="A381" s="3" t="n">
         <v>45047</v>
       </c>
       <c r="B381" t="n">
@@ -3750,7 +3753,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="5" t="n">
+      <c r="A382" s="3" t="n">
         <v>45054</v>
       </c>
       <c r="B382" t="n">
@@ -3758,7 +3761,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="5" t="n">
+      <c r="A383" s="3" t="n">
         <v>45061</v>
       </c>
       <c r="B383" t="n">
@@ -3766,7 +3769,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="5" t="n">
+      <c r="A384" s="3" t="n">
         <v>45068</v>
       </c>
       <c r="B384" t="n">
@@ -3774,7 +3777,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="5" t="n">
+      <c r="A385" s="3" t="n">
         <v>45075</v>
       </c>
       <c r="B385" t="n">
@@ -3782,7 +3785,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="5" t="n">
+      <c r="A386" s="3" t="n">
         <v>45082</v>
       </c>
       <c r="B386" t="n">
@@ -3790,7 +3793,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="5" t="n">
+      <c r="A387" s="3" t="n">
         <v>45089</v>
       </c>
       <c r="B387" t="n">
@@ -3798,7 +3801,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="5" t="n">
+      <c r="A388" s="3" t="n">
         <v>45096</v>
       </c>
       <c r="B388" t="n">
@@ -3806,7 +3809,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="5" t="n">
+      <c r="A389" s="3" t="n">
         <v>45103</v>
       </c>
       <c r="B389" t="n">
@@ -3814,7 +3817,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="5" t="n">
+      <c r="A390" s="3" t="n">
         <v>45110</v>
       </c>
       <c r="B390" t="n">
@@ -3822,7 +3825,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="5" t="n">
+      <c r="A391" s="3" t="n">
         <v>45117</v>
       </c>
       <c r="B391" t="n">
@@ -3830,7 +3833,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="5" t="n">
+      <c r="A392" s="3" t="n">
         <v>45124</v>
       </c>
       <c r="B392" t="n">
@@ -3838,7 +3841,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="5" t="n">
+      <c r="A393" s="3" t="n">
         <v>45131</v>
       </c>
       <c r="B393" t="n">
@@ -3846,7 +3849,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="5" t="n">
+      <c r="A394" s="3" t="n">
         <v>45138</v>
       </c>
       <c r="B394" t="n">
@@ -3854,7 +3857,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="5" t="n">
+      <c r="A395" s="3" t="n">
         <v>45145</v>
       </c>
       <c r="B395" t="n">
@@ -3862,7 +3865,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="5" t="n">
+      <c r="A396" s="3" t="n">
         <v>45152</v>
       </c>
       <c r="B396" t="n">
@@ -3870,7 +3873,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="5" t="n">
+      <c r="A397" s="3" t="n">
         <v>45159</v>
       </c>
       <c r="B397" t="n">
@@ -3878,7 +3881,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="5" t="n">
+      <c r="A398" s="3" t="n">
         <v>45166</v>
       </c>
       <c r="B398" t="n">
@@ -3886,7 +3889,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="5" t="n">
+      <c r="A399" s="3" t="n">
         <v>45173</v>
       </c>
       <c r="B399" t="n">
@@ -3894,7 +3897,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="5" t="n">
+      <c r="A400" s="3" t="n">
         <v>45180</v>
       </c>
       <c r="B400" t="n">
@@ -3902,7 +3905,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="5" t="n">
+      <c r="A401" s="3" t="n">
         <v>45187</v>
       </c>
       <c r="B401" t="n">
@@ -3910,7 +3913,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="5" t="n">
+      <c r="A402" s="3" t="n">
         <v>45194</v>
       </c>
       <c r="B402" t="n">
@@ -3918,7 +3921,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="5" t="n">
+      <c r="A403" s="3" t="n">
         <v>45201</v>
       </c>
       <c r="B403" t="n">
@@ -3926,7 +3929,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="5" t="n">
+      <c r="A404" s="3" t="n">
         <v>45208</v>
       </c>
       <c r="B404" t="n">
@@ -3934,7 +3937,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="5" t="n">
+      <c r="A405" s="3" t="n">
         <v>45215</v>
       </c>
       <c r="B405" t="n">
@@ -3942,7 +3945,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="5" t="n">
+      <c r="A406" s="3" t="n">
         <v>45222</v>
       </c>
       <c r="B406" t="n">
@@ -3950,7 +3953,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="5" t="n">
+      <c r="A407" s="3" t="n">
         <v>45229</v>
       </c>
       <c r="B407" t="n">
@@ -3958,7 +3961,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="5" t="n">
+      <c r="A408" s="3" t="n">
         <v>45236</v>
       </c>
       <c r="B408" t="n">
@@ -3966,7 +3969,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="5" t="n">
+      <c r="A409" s="3" t="n">
         <v>45243</v>
       </c>
       <c r="B409" t="n">
@@ -3974,7 +3977,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="5" t="n">
+      <c r="A410" s="3" t="n">
         <v>45250</v>
       </c>
       <c r="B410" t="n">
@@ -3982,7 +3985,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="5" t="n">
+      <c r="A411" s="3" t="n">
         <v>45257</v>
       </c>
       <c r="B411" t="n">
@@ -3990,7 +3993,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="5" t="n">
+      <c r="A412" s="3" t="n">
         <v>45264</v>
       </c>
       <c r="B412" t="n">
@@ -3998,7 +4001,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="5" t="n">
+      <c r="A413" s="3" t="n">
         <v>45271</v>
       </c>
       <c r="B413" t="n">
@@ -4006,7 +4009,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="5" t="n">
+      <c r="A414" s="3" t="n">
         <v>45278</v>
       </c>
       <c r="B414" t="n">
@@ -4014,7 +4017,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="5" t="n">
+      <c r="A415" s="3" t="n">
         <v>45285</v>
       </c>
       <c r="B415" t="n">
@@ -4022,7 +4025,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="5" t="n">
+      <c r="A416" s="3" t="n">
         <v>45292</v>
       </c>
       <c r="B416" t="n">
@@ -4030,7 +4033,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="5" t="n">
+      <c r="A417" s="3" t="n">
         <v>45299</v>
       </c>
       <c r="B417" t="n">
@@ -4038,7 +4041,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="5" t="n">
+      <c r="A418" s="3" t="n">
         <v>45306</v>
       </c>
       <c r="B418" t="n">
@@ -4046,7 +4049,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="5" t="n">
+      <c r="A419" s="3" t="n">
         <v>45313</v>
       </c>
       <c r="B419" t="n">
@@ -4054,7 +4057,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="5" t="n">
+      <c r="A420" s="3" t="n">
         <v>45320</v>
       </c>
       <c r="B420" t="n">
@@ -4062,7 +4065,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="5" t="n">
+      <c r="A421" s="3" t="n">
         <v>45327</v>
       </c>
       <c r="B421" t="n">
@@ -4070,7 +4073,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="5" t="n">
+      <c r="A422" s="3" t="n">
         <v>45334</v>
       </c>
       <c r="B422" t="n">
@@ -4078,7 +4081,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="5" t="n">
+      <c r="A423" s="3" t="n">
         <v>45341</v>
       </c>
       <c r="B423" t="n">
@@ -4086,7 +4089,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="5" t="n">
+      <c r="A424" s="3" t="n">
         <v>45348</v>
       </c>
       <c r="B424" t="n">
@@ -4094,7 +4097,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="5" t="n">
+      <c r="A425" s="3" t="n">
         <v>45355</v>
       </c>
       <c r="B425" t="n">
@@ -4102,7 +4105,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="5" t="n">
+      <c r="A426" s="3" t="n">
         <v>45362</v>
       </c>
       <c r="B426" t="n">
@@ -4110,7 +4113,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="5" t="n">
+      <c r="A427" s="3" t="n">
         <v>45369</v>
       </c>
       <c r="B427" t="n">
@@ -4118,7 +4121,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="5" t="n">
+      <c r="A428" s="3" t="n">
         <v>45376</v>
       </c>
       <c r="B428" t="n">
@@ -4126,7 +4129,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="5" t="n">
+      <c r="A429" s="3" t="n">
         <v>45383</v>
       </c>
       <c r="B429" t="n">
@@ -4134,7 +4137,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="5" t="n">
+      <c r="A430" s="3" t="n">
         <v>45390</v>
       </c>
       <c r="B430" t="n">
@@ -4142,7 +4145,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="5" t="n">
+      <c r="A431" s="3" t="n">
         <v>45397</v>
       </c>
       <c r="B431" t="n">
@@ -4150,7 +4153,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="5" t="n">
+      <c r="A432" s="3" t="n">
         <v>45404</v>
       </c>
       <c r="B432" t="n">
@@ -4158,7 +4161,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="5" t="n">
+      <c r="A433" s="3" t="n">
         <v>45411</v>
       </c>
       <c r="B433" t="n">
@@ -4166,7 +4169,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="5" t="n">
+      <c r="A434" s="3" t="n">
         <v>45418</v>
       </c>
       <c r="B434" t="n">
@@ -4174,7 +4177,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="5" t="n">
+      <c r="A435" s="3" t="n">
         <v>45425</v>
       </c>
       <c r="B435" t="n">
@@ -4182,7 +4185,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="5" t="n">
+      <c r="A436" s="3" t="n">
         <v>45432</v>
       </c>
       <c r="B436" t="n">
@@ -4190,7 +4193,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="5" t="n">
+      <c r="A437" s="3" t="n">
         <v>45439</v>
       </c>
       <c r="B437" t="n">
@@ -4198,7 +4201,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="5" t="n">
+      <c r="A438" s="3" t="n">
         <v>45446</v>
       </c>
       <c r="B438" t="n">
@@ -4206,7 +4209,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="5" t="n">
+      <c r="A439" s="3" t="n">
         <v>45453</v>
       </c>
       <c r="B439" t="n">
@@ -4214,7 +4217,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="5" t="n">
+      <c r="A440" s="3" t="n">
         <v>45460</v>
       </c>
       <c r="B440" t="n">
@@ -4222,7 +4225,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="5" t="n">
+      <c r="A441" s="3" t="n">
         <v>45467</v>
       </c>
       <c r="B441" t="n">
@@ -4230,7 +4233,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="5" t="n">
+      <c r="A442" s="3" t="n">
         <v>45474</v>
       </c>
       <c r="B442" t="n">
@@ -4238,7 +4241,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="5" t="n">
+      <c r="A443" s="3" t="n">
         <v>45481</v>
       </c>
       <c r="B443" t="n">
@@ -4246,7 +4249,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="5" t="n">
+      <c r="A444" s="3" t="n">
         <v>45488</v>
       </c>
       <c r="B444" t="n">
@@ -4254,7 +4257,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="5" t="n">
+      <c r="A445" s="3" t="n">
         <v>45495</v>
       </c>
       <c r="B445" t="n">
@@ -4262,7 +4265,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="5" t="n">
+      <c r="A446" s="3" t="n">
         <v>45502</v>
       </c>
       <c r="B446" t="n">
@@ -4270,7 +4273,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="5" t="n">
+      <c r="A447" s="3" t="n">
         <v>45509</v>
       </c>
       <c r="B447" t="n">
@@ -4278,7 +4281,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="5" t="n">
+      <c r="A448" s="3" t="n">
         <v>45516</v>
       </c>
       <c r="B448" t="n">
@@ -4286,7 +4289,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="5" t="n">
+      <c r="A449" s="3" t="n">
         <v>45523</v>
       </c>
       <c r="B449" t="n">
@@ -4294,7 +4297,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="5" t="n">
+      <c r="A450" s="3" t="n">
         <v>45530</v>
       </c>
       <c r="B450" t="n">
@@ -4302,7 +4305,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="5" t="n">
+      <c r="A451" s="3" t="n">
         <v>45537</v>
       </c>
       <c r="B451" t="n">
@@ -4310,7 +4313,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="5" t="n">
+      <c r="A452" s="3" t="n">
         <v>45544</v>
       </c>
       <c r="B452" t="n">
@@ -4318,7 +4321,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="5" t="n">
+      <c r="A453" s="3" t="n">
         <v>45551</v>
       </c>
       <c r="B453" t="n">
@@ -4326,7 +4329,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="5" t="n">
+      <c r="A454" s="3" t="n">
         <v>45558</v>
       </c>
       <c r="B454" t="n">
@@ -4334,7 +4337,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="5" t="n">
+      <c r="A455" s="3" t="n">
         <v>45565</v>
       </c>
       <c r="B455" t="n">
@@ -4342,7 +4345,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="5" t="n">
+      <c r="A456" s="3" t="n">
         <v>45572</v>
       </c>
       <c r="B456" t="n">
@@ -4350,7 +4353,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="5" t="n">
+      <c r="A457" s="3" t="n">
         <v>45579</v>
       </c>
       <c r="B457" t="n">
@@ -4358,7 +4361,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="5" t="n">
+      <c r="A458" s="3" t="n">
         <v>45586</v>
       </c>
       <c r="B458" t="n">
@@ -4366,7 +4369,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="5" t="n">
+      <c r="A459" s="3" t="n">
         <v>45593</v>
       </c>
       <c r="B459" t="n">
@@ -4374,7 +4377,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="5" t="n">
+      <c r="A460" s="3" t="n">
         <v>45600</v>
       </c>
       <c r="B460" t="n">
@@ -4382,7 +4385,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="5" t="n">
+      <c r="A461" s="3" t="n">
         <v>45607</v>
       </c>
       <c r="B461" t="n">
@@ -4390,7 +4393,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="5" t="n">
+      <c r="A462" s="3" t="n">
         <v>45614</v>
       </c>
       <c r="B462" t="n">
@@ -4398,7 +4401,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="5" t="n">
+      <c r="A463" s="3" t="n">
         <v>45621</v>
       </c>
       <c r="B463" t="n">
@@ -4406,7 +4409,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="5" t="n">
+      <c r="A464" s="3" t="n">
         <v>45628</v>
       </c>
       <c r="B464" t="n">
@@ -4414,7 +4417,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="5" t="n">
+      <c r="A465" s="3" t="n">
         <v>45635</v>
       </c>
       <c r="B465" t="n">
@@ -4422,7 +4425,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="5" t="n">
+      <c r="A466" s="3" t="n">
         <v>45642</v>
       </c>
       <c r="B466" t="n">
@@ -4430,7 +4433,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="5" t="n">
+      <c r="A467" s="3" t="n">
         <v>45649</v>
       </c>
       <c r="B467" t="n">
@@ -4438,7 +4441,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="5" t="n">
+      <c r="A468" s="3" t="n">
         <v>45656</v>
       </c>
       <c r="B468" t="n">
@@ -4446,7 +4449,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="5" t="n">
+      <c r="A469" s="3" t="n">
         <v>45663</v>
       </c>
       <c r="B469" t="n">
@@ -4454,7 +4457,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="5" t="n">
+      <c r="A470" s="3" t="n">
         <v>45670</v>
       </c>
       <c r="B470" t="n">
@@ -4462,7 +4465,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="5" t="n">
+      <c r="A471" s="3" t="n">
         <v>45677</v>
       </c>
       <c r="B471" t="n">
@@ -4470,7 +4473,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="5" t="n">
+      <c r="A472" s="3" t="n">
         <v>45684</v>
       </c>
       <c r="B472" t="n">
@@ -4478,7 +4481,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="5" t="n">
+      <c r="A473" s="3" t="n">
         <v>45691</v>
       </c>
       <c r="B473" t="n">
@@ -4486,7 +4489,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="5" t="n">
+      <c r="A474" s="3" t="n">
         <v>45698</v>
       </c>
       <c r="B474" t="n">
@@ -4494,7 +4497,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="5" t="n">
+      <c r="A475" s="3" t="n">
         <v>45705</v>
       </c>
       <c r="B475" t="n">
@@ -4502,7 +4505,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="5" t="n">
+      <c r="A476" s="3" t="n">
         <v>45712</v>
       </c>
       <c r="B476" t="n">
@@ -4510,7 +4513,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="5" t="n">
+      <c r="A477" s="3" t="n">
         <v>45719</v>
       </c>
       <c r="B477" t="n">
@@ -4518,7 +4521,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="5" t="n">
+      <c r="A478" s="3" t="n">
         <v>45726</v>
       </c>
       <c r="B478" t="n">
@@ -4526,7 +4529,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="5" t="n">
+      <c r="A479" s="3" t="n">
         <v>45733</v>
       </c>
       <c r="B479" t="n">
@@ -4534,7 +4537,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="5" t="n">
+      <c r="A480" s="3" t="n">
         <v>45740</v>
       </c>
       <c r="B480" t="n">
@@ -4542,7 +4545,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="5" t="n">
+      <c r="A481" s="3" t="n">
         <v>45747</v>
       </c>
       <c r="B481" t="n">
@@ -4550,7 +4553,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="5" t="n">
+      <c r="A482" s="3" t="n">
         <v>45754</v>
       </c>
       <c r="B482" t="n">
@@ -4558,7 +4561,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="5" t="n">
+      <c r="A483" s="3" t="n">
         <v>45761</v>
       </c>
       <c r="B483" t="n">
@@ -4566,7 +4569,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="5" t="n">
+      <c r="A484" s="3" t="n">
         <v>45768</v>
       </c>
       <c r="B484" t="n">
@@ -4574,7 +4577,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="5" t="n">
+      <c r="A485" s="3" t="n">
         <v>45775</v>
       </c>
       <c r="B485" t="n">
@@ -4582,7 +4585,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="5" t="n">
+      <c r="A486" s="3" t="n">
         <v>45782</v>
       </c>
       <c r="B486" t="n">
@@ -4590,7 +4593,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="5" t="n">
+      <c r="A487" s="3" t="n">
         <v>45789</v>
       </c>
       <c r="B487" t="n">
@@ -4598,7 +4601,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="5" t="n">
+      <c r="A488" s="3" t="n">
         <v>45796</v>
       </c>
       <c r="B488" t="n">
@@ -4606,7 +4609,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="5" t="n">
+      <c r="A489" s="3" t="n">
         <v>45803</v>
       </c>
       <c r="B489" t="n">
@@ -4614,7 +4617,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="5" t="n">
+      <c r="A490" s="3" t="n">
         <v>45810</v>
       </c>
       <c r="B490" t="n">
@@ -4622,7 +4625,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="5" t="n">
+      <c r="A491" s="3" t="n">
         <v>45817</v>
       </c>
       <c r="B491" t="n">
@@ -4630,7 +4633,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="5" t="n">
+      <c r="A492" s="3" t="n">
         <v>45824</v>
       </c>
       <c r="B492" t="n">
@@ -4638,7 +4641,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="5" t="n">
+      <c r="A493" s="3" t="n">
         <v>45831</v>
       </c>
       <c r="B493" t="n">
@@ -4646,7 +4649,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="5" t="n">
+      <c r="A494" s="3" t="n">
         <v>45838</v>
       </c>
       <c r="B494" t="n">
@@ -4654,7 +4657,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="5" t="n">
+      <c r="A495" s="3" t="n">
         <v>45845</v>
       </c>
       <c r="B495" t="n">
@@ -4662,7 +4665,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="5" t="n">
+      <c r="A496" s="3" t="n">
         <v>45852</v>
       </c>
       <c r="B496" t="n">
@@ -4670,7 +4673,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="5" t="n">
+      <c r="A497" s="3" t="n">
         <v>45859</v>
       </c>
       <c r="B497" t="n">
@@ -4678,7 +4681,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="5" t="n">
+      <c r="A498" s="3" t="n">
         <v>45866</v>
       </c>
       <c r="B498" t="n">
@@ -4686,7 +4689,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="5" t="n">
+      <c r="A499" s="3" t="n">
         <v>45873</v>
       </c>
       <c r="B499" t="n">
@@ -4694,7 +4697,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="5" t="n">
+      <c r="A500" s="3" t="n">
         <v>45880</v>
       </c>
       <c r="B500" t="n">
@@ -4702,7 +4705,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="5" t="n">
+      <c r="A501" s="3" t="n">
         <v>45887</v>
       </c>
       <c r="B501" t="n">
@@ -4710,7 +4713,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="5" t="n">
+      <c r="A502" s="3" t="n">
         <v>45894</v>
       </c>
       <c r="B502" t="n">
@@ -4718,7 +4721,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="5" t="n">
+      <c r="A503" s="3" t="n">
         <v>45901</v>
       </c>
       <c r="B503" t="n">
@@ -4726,7 +4729,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="5" t="n">
+      <c r="A504" s="3" t="n">
         <v>45908</v>
       </c>
       <c r="B504" t="n">
@@ -4734,7 +4737,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="5" t="n">
+      <c r="A505" s="3" t="n">
         <v>45915</v>
       </c>
       <c r="B505" t="n">
@@ -4742,7 +4745,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="5" t="n">
+      <c r="A506" s="3" t="n">
         <v>45922</v>
       </c>
       <c r="B506" t="n">
@@ -4750,7 +4753,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="5" t="n">
+      <c r="A507" s="3" t="n">
         <v>45929</v>
       </c>
       <c r="B507" t="n">
@@ -4758,7 +4761,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="5" t="n">
+      <c r="A508" s="3" t="n">
         <v>45936</v>
       </c>
       <c r="B508" t="n">
@@ -4766,7 +4769,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="5" t="n">
+      <c r="A509" s="3" t="n">
         <v>45943</v>
       </c>
       <c r="B509" t="n">
@@ -4774,7 +4777,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="5" t="n">
+      <c r="A510" s="3" t="n">
         <v>45950</v>
       </c>
       <c r="B510" t="n">
@@ -4782,7 +4785,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="5" t="n">
+      <c r="A511" s="3" t="n">
         <v>45957</v>
       </c>
       <c r="B511" t="n">
@@ -4790,7 +4793,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="5" t="n">
+      <c r="A512" s="3" t="n">
         <v>45964</v>
       </c>
       <c r="B512" t="n">
@@ -4798,7 +4801,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="5" t="n">
+      <c r="A513" s="3" t="n">
         <v>45971</v>
       </c>
       <c r="B513" t="n">
@@ -4806,7 +4809,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="5" t="n">
+      <c r="A514" s="3" t="n">
         <v>45978</v>
       </c>
       <c r="B514" t="n">
@@ -4814,7 +4817,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="5" t="n">
+      <c r="A515" s="3" t="n">
         <v>45985</v>
       </c>
       <c r="B515" t="n">
@@ -4822,7 +4825,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="5" t="n">
+      <c r="A516" s="3" t="n">
         <v>45992</v>
       </c>
       <c r="B516" t="n">
@@ -4830,7 +4833,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="5" t="n">
+      <c r="A517" s="3" t="n">
         <v>45999</v>
       </c>
       <c r="B517" t="n">
@@ -4838,7 +4841,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="5" t="n">
+      <c r="A518" s="3" t="n">
         <v>46006</v>
       </c>
       <c r="B518" t="n">
@@ -4846,7 +4849,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="5" t="n">
+      <c r="A519" s="3" t="n">
         <v>46013</v>
       </c>
       <c r="B519" t="n">
@@ -4854,7 +4857,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="5" t="n">
+      <c r="A520" s="3" t="n">
         <v>46020</v>
       </c>
       <c r="B520" t="n">
@@ -4862,7 +4865,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="5" t="n">
+      <c r="A521" s="3" t="n">
         <v>46027</v>
       </c>
       <c r="B521" t="n">
@@ -4870,7 +4873,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="5" t="n">
+      <c r="A522" s="3" t="n">
         <v>46034</v>
       </c>
       <c r="B522" t="n">
@@ -4878,7 +4881,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="5" t="n">
+      <c r="A523" s="3" t="n">
         <v>46041</v>
       </c>
       <c r="B523" t="n">
@@ -4886,7 +4889,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="5" t="n">
+      <c r="A524" s="3" t="n">
         <v>46048</v>
       </c>
       <c r="B524" t="n">
@@ -4894,7 +4897,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="5" t="n">
+      <c r="A525" s="3" t="n">
         <v>46055</v>
       </c>
       <c r="B525" t="n">
@@ -4902,7 +4905,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="5" t="n">
+      <c r="A526" s="3" t="n">
         <v>46062</v>
       </c>
       <c r="B526" t="n">
@@ -4910,7 +4913,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="5" t="n">
+      <c r="A527" s="3" t="n">
         <v>46069</v>
       </c>
       <c r="B527" t="n">
@@ -4918,7 +4921,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="5" t="n">
+      <c r="A528" s="3" t="n">
         <v>46076</v>
       </c>
       <c r="B528" t="n">
@@ -4926,7 +4929,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="5" t="n">
+      <c r="A529" s="3" t="n">
         <v>46083</v>
       </c>
       <c r="B529" t="n">
@@ -4934,7 +4937,7 @@
       </c>
     </row>
     <row r="530">
-      <c r="A530" s="5" t="n">
+      <c r="A530" s="3" t="n">
         <v>46090</v>
       </c>
       <c r="B530" t="n">
@@ -4942,7 +4945,7 @@
       </c>
     </row>
     <row r="531">
-      <c r="A531" s="5" t="n">
+      <c r="A531" s="3" t="n">
         <v>46097</v>
       </c>
       <c r="B531" t="n">
@@ -4950,15 +4953,15 @@
       </c>
     </row>
     <row r="532">
-      <c r="A532" s="5" t="n">
+      <c r="A532" s="3" t="n">
         <v>46104</v>
       </c>
       <c r="B532" t="n">
-        <v>953600.3285714285</v>
+        <v>953600.4857142856</v>
       </c>
     </row>
     <row r="533">
-      <c r="A533" s="5" t="n">
+      <c r="A533" s="3" t="n">
         <v>46111</v>
       </c>
       <c r="B533" t="n">
@@ -4966,7 +4969,7 @@
       </c>
     </row>
     <row r="534">
-      <c r="A534" s="5" t="n">
+      <c r="A534" s="3" t="n">
         <v>46118</v>
       </c>
       <c r="B534" t="n">
@@ -4974,7 +4977,7 @@
       </c>
     </row>
     <row r="535">
-      <c r="A535" s="5" t="n">
+      <c r="A535" s="3" t="n">
         <v>46125</v>
       </c>
       <c r="B535" t="n">
@@ -4982,7 +4985,7 @@
       </c>
     </row>
     <row r="536">
-      <c r="A536" s="5" t="n">
+      <c r="A536" s="3" t="n">
         <v>46132</v>
       </c>
       <c r="B536" t="n">
@@ -4990,7 +4993,7 @@
       </c>
     </row>
     <row r="537">
-      <c r="A537" s="5" t="n">
+      <c r="A537" s="3" t="n">
         <v>46139</v>
       </c>
       <c r="B537" t="n">
@@ -4998,7 +5001,7 @@
       </c>
     </row>
     <row r="538">
-      <c r="A538" s="5" t="n">
+      <c r="A538" s="3" t="n">
         <v>46146</v>
       </c>
       <c r="B538" t="n">
@@ -5006,7 +5009,7 @@
       </c>
     </row>
     <row r="539">
-      <c r="A539" s="5" t="n">
+      <c r="A539" s="3" t="n">
         <v>46153</v>
       </c>
       <c r="B539" t="n">
@@ -5014,7 +5017,7 @@
       </c>
     </row>
     <row r="540">
-      <c r="A540" s="5" t="n">
+      <c r="A540" s="3" t="n">
         <v>46160</v>
       </c>
       <c r="B540" t="n">
@@ -5022,7 +5025,7 @@
       </c>
     </row>
     <row r="541">
-      <c r="A541" s="5" t="n">
+      <c r="A541" s="3" t="n">
         <v>46167</v>
       </c>
       <c r="B541" t="n">
@@ -5030,7 +5033,7 @@
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="5" t="n">
+      <c r="A542" s="3" t="n">
         <v>46174</v>
       </c>
       <c r="B542" t="n">
@@ -5038,7 +5041,7 @@
       </c>
     </row>
     <row r="543">
-      <c r="A543" s="5" t="n">
+      <c r="A543" s="3" t="n">
         <v>46181</v>
       </c>
       <c r="B543" t="n">
@@ -5046,7 +5049,7 @@
       </c>
     </row>
     <row r="544">
-      <c r="A544" s="5" t="n">
+      <c r="A544" s="3" t="n">
         <v>46188</v>
       </c>
       <c r="B544" t="n">
@@ -5054,7 +5057,7 @@
       </c>
     </row>
     <row r="545">
-      <c r="A545" s="5" t="n">
+      <c r="A545" s="3" t="n">
         <v>46195</v>
       </c>
       <c r="B545" t="n">
@@ -5062,7 +5065,7 @@
       </c>
     </row>
     <row r="546">
-      <c r="A546" s="5" t="n">
+      <c r="A546" s="3" t="n">
         <v>46202</v>
       </c>
       <c r="B546" t="n">
@@ -5070,15 +5073,15 @@
       </c>
     </row>
     <row r="547">
-      <c r="A547" s="5" t="n">
+      <c r="A547" s="3" t="n">
         <v>46209</v>
       </c>
       <c r="B547" t="n">
-        <v>1095172.785714286</v>
+        <v>1095111.157142857</v>
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="5" t="n">
+      <c r="A548" s="3" t="n">
         <v>46216</v>
       </c>
       <c r="B548" t="n">
@@ -5086,7 +5089,7 @@
       </c>
     </row>
     <row r="549">
-      <c r="A549" s="5" t="n">
+      <c r="A549" s="3" t="n">
         <v>46223</v>
       </c>
       <c r="B549" t="n">
@@ -5094,7 +5097,7 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="5" t="n">
+      <c r="A550" s="3" t="n">
         <v>46230</v>
       </c>
       <c r="B550" t="n">
@@ -5102,7 +5105,7 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="5" t="n">
+      <c r="A551" s="3" t="n">
         <v>46237</v>
       </c>
       <c r="B551" t="n">
@@ -5110,7 +5113,7 @@
       </c>
     </row>
     <row r="552">
-      <c r="A552" s="5" t="n">
+      <c r="A552" s="3" t="n">
         <v>46244</v>
       </c>
       <c r="B552" t="n">
@@ -5118,7 +5121,7 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="5" t="n">
+      <c r="A553" s="3" t="n">
         <v>46251</v>
       </c>
       <c r="B553" t="n">
@@ -5126,7 +5129,7 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="5" t="n">
+      <c r="A554" s="3" t="n">
         <v>46258</v>
       </c>
       <c r="B554" t="n">
@@ -5134,15 +5137,15 @@
       </c>
     </row>
     <row r="555">
-      <c r="A555" s="5" t="n">
+      <c r="A555" s="3" t="n">
         <v>46265</v>
       </c>
       <c r="B555" t="n">
-        <v>1131045.314285714</v>
+        <v>1130727.757142857</v>
       </c>
     </row>
     <row r="556">
-      <c r="A556" s="5" t="n">
+      <c r="A556" s="3" t="n">
         <v>46272</v>
       </c>
       <c r="B556" t="n">
@@ -5150,7 +5153,7 @@
       </c>
     </row>
     <row r="557">
-      <c r="A557" s="5" t="n">
+      <c r="A557" s="3" t="n">
         <v>46279</v>
       </c>
       <c r="B557" t="n">
@@ -5158,7 +5161,7 @@
       </c>
     </row>
     <row r="558">
-      <c r="A558" s="5" t="n">
+      <c r="A558" s="3" t="n">
         <v>46286</v>
       </c>
       <c r="B558" t="n">
@@ -5166,7 +5169,7 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="5" t="n">
+      <c r="A559" s="3" t="n">
         <v>46293</v>
       </c>
       <c r="B559" t="n">
@@ -5174,7 +5177,7 @@
       </c>
     </row>
     <row r="560">
-      <c r="A560" s="5" t="n">
+      <c r="A560" s="3" t="n">
         <v>46300</v>
       </c>
       <c r="B560" t="n">
@@ -5182,11 +5185,11 @@
       </c>
     </row>
     <row r="561">
-      <c r="A561" s="5" t="n">
+      <c r="A561" s="3" t="n">
         <v>46307</v>
       </c>
       <c r="B561" t="n">
-        <v>1034647.85</v>
+        <v>1040153</v>
       </c>
     </row>
   </sheetData>
@@ -5201,7 +5204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3912"/>
+  <dimension ref="A1:F3914"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79239,19 +79242,19 @@
         <v>46106</v>
       </c>
       <c r="B3710" t="n">
-        <v>990847.8</v>
+        <v>990847.1</v>
       </c>
       <c r="C3710" t="n">
-        <v>928840.2</v>
+        <v>928844.7</v>
       </c>
       <c r="D3710" t="n">
-        <v>52492.7</v>
+        <v>52487.4</v>
       </c>
       <c r="E3710" t="n">
         <v>9515</v>
       </c>
       <c r="F3710" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3711">
@@ -79259,19 +79262,19 @@
         <v>46107</v>
       </c>
       <c r="B3711" t="n">
-        <v>994917.9</v>
+        <v>994919.7</v>
       </c>
       <c r="C3711" t="n">
-        <v>933777.1</v>
+        <v>933781</v>
       </c>
       <c r="D3711" t="n">
-        <v>51581</v>
+        <v>51579</v>
       </c>
       <c r="E3711" t="n">
         <v>9559.799999999999</v>
       </c>
       <c r="F3711" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3712">
@@ -81339,19 +81342,19 @@
         <v>46211</v>
       </c>
       <c r="B3815" t="n">
-        <v>1127652.9</v>
+        <v>1127305.5</v>
       </c>
       <c r="C3815" t="n">
-        <v>1047508.4</v>
+        <v>1047186.9</v>
       </c>
       <c r="D3815" t="n">
-        <v>66413.10000000001</v>
+        <v>66386.39999999999</v>
       </c>
       <c r="E3815" t="n">
-        <v>13731.3</v>
+        <v>13732.1</v>
       </c>
       <c r="F3815" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3816">
@@ -81359,19 +81362,19 @@
         <v>46212</v>
       </c>
       <c r="B3816" t="n">
-        <v>1120482.7</v>
+        <v>1120398.7</v>
       </c>
       <c r="C3816" t="n">
-        <v>1040256.1</v>
+        <v>1040198.7</v>
       </c>
       <c r="D3816" t="n">
-        <v>66830</v>
+        <v>66802.5</v>
       </c>
       <c r="E3816" t="n">
-        <v>13396.6</v>
+        <v>13397.5</v>
       </c>
       <c r="F3816" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3817">
@@ -82459,19 +82462,19 @@
         <v>46267</v>
       </c>
       <c r="B3871" t="n">
-        <v>1172954.3</v>
+        <v>1173359</v>
       </c>
       <c r="C3871" t="n">
-        <v>1096985.6</v>
+        <v>1097407.7</v>
       </c>
       <c r="D3871" t="n">
-        <v>63981</v>
+        <v>63862.2</v>
       </c>
       <c r="E3871" t="n">
-        <v>11987.6</v>
+        <v>12089.1</v>
       </c>
       <c r="F3871" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3872">
@@ -82479,19 +82482,19 @@
         <v>46268</v>
       </c>
       <c r="B3872" t="n">
-        <v>1169257</v>
+        <v>1166629.4</v>
       </c>
       <c r="C3872" t="n">
-        <v>1097867.3</v>
+        <v>1095270.9</v>
       </c>
       <c r="D3872" t="n">
-        <v>60016.2</v>
+        <v>59892.3</v>
       </c>
       <c r="E3872" t="n">
-        <v>11373.5</v>
+        <v>11466.2</v>
       </c>
       <c r="F3872" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3873">
@@ -83291,6 +83294,46 @@
         <v>12322.8</v>
       </c>
       <c r="F3912" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3913">
+      <c r="A3913" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B3913" t="n">
+        <v>1057411.4</v>
+      </c>
+      <c r="C3913" t="n">
+        <v>1003154.8</v>
+      </c>
+      <c r="D3913" t="n">
+        <v>41960.7</v>
+      </c>
+      <c r="E3913" t="n">
+        <v>12295.9</v>
+      </c>
+      <c r="F3913" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3914">
+      <c r="A3914" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B3914" t="n">
+        <v>1033904.9</v>
+      </c>
+      <c r="C3914" t="n">
+        <v>978793.4</v>
+      </c>
+      <c r="D3914" t="n">
+        <v>42737.4</v>
+      </c>
+      <c r="E3914" t="n">
+        <v>12374.1</v>
+      </c>
+      <c r="F3914" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
+++ b/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
@@ -4957,7 +4957,7 @@
         <v>46104</v>
       </c>
       <c r="B532" t="n">
-        <v>953600.4857142856</v>
+        <v>953600.4</v>
       </c>
     </row>
     <row r="533">
@@ -5077,7 +5077,7 @@
         <v>46209</v>
       </c>
       <c r="B547" t="n">
-        <v>1095111.157142857</v>
+        <v>1095082.842857143</v>
       </c>
     </row>
     <row r="548">
@@ -5141,7 +5141,7 @@
         <v>46265</v>
       </c>
       <c r="B555" t="n">
-        <v>1130727.757142857</v>
+        <v>1130406.385714286</v>
       </c>
     </row>
     <row r="556">
@@ -5189,7 +5189,7 @@
         <v>46307</v>
       </c>
       <c r="B561" t="n">
-        <v>1040153</v>
+        <v>1029106.16</v>
       </c>
     </row>
   </sheetData>
@@ -5204,7 +5204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3914"/>
+  <dimension ref="A1:F3915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79282,19 +79282,19 @@
         <v>46108</v>
       </c>
       <c r="B3712" t="n">
-        <v>991958.5</v>
+        <v>991957.9</v>
       </c>
       <c r="C3712" t="n">
-        <v>930973</v>
+        <v>930977</v>
       </c>
       <c r="D3712" t="n">
-        <v>51580.3</v>
+        <v>51575.7</v>
       </c>
       <c r="E3712" t="n">
         <v>9405.200000000001</v>
       </c>
       <c r="F3712" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3713">
@@ -81382,19 +81382,19 @@
         <v>46213</v>
       </c>
       <c r="B3817" t="n">
-        <v>1116673.7</v>
+        <v>1116475.5</v>
       </c>
       <c r="C3817" t="n">
-        <v>1038492.1</v>
+        <v>1038320.4</v>
       </c>
       <c r="D3817" t="n">
-        <v>65078.9</v>
+        <v>65051.7</v>
       </c>
       <c r="E3817" t="n">
-        <v>13102.7</v>
+        <v>13103.4</v>
       </c>
       <c r="F3817" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3818">
@@ -82502,19 +82502,19 @@
         <v>46269</v>
       </c>
       <c r="B3873" t="n">
-        <v>1163367</v>
+        <v>1161117.4</v>
       </c>
       <c r="C3873" t="n">
-        <v>1090782.9</v>
+        <v>1088559.4</v>
       </c>
       <c r="D3873" t="n">
-        <v>60003.1</v>
+        <v>59879.5</v>
       </c>
       <c r="E3873" t="n">
-        <v>12581</v>
+        <v>12678.5</v>
       </c>
       <c r="F3873" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3874">
@@ -83334,6 +83334,26 @@
         <v>12374.1</v>
       </c>
       <c r="F3914" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3915">
+      <c r="A3915" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B3915" t="n">
+        <v>984918.8</v>
+      </c>
+      <c r="C3915" t="n">
+        <v>927405.9</v>
+      </c>
+      <c r="D3915" t="n">
+        <v>45313.5</v>
+      </c>
+      <c r="E3915" t="n">
+        <v>12199.4</v>
+      </c>
+      <c r="F3915" t="n">
         <v>0</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
+++ b/output/Data and Chart Outputs/mexico_demanda_nacional_daily.xlsx
@@ -4957,7 +4957,7 @@
         <v>46104</v>
       </c>
       <c r="B532" t="n">
-        <v>953600.4</v>
+        <v>953599.5857142856</v>
       </c>
     </row>
     <row r="533">
@@ -5077,7 +5077,7 @@
         <v>46209</v>
       </c>
       <c r="B547" t="n">
-        <v>1095082.842857143</v>
+        <v>1095048.528571428</v>
       </c>
     </row>
     <row r="548">
@@ -5141,7 +5141,7 @@
         <v>46265</v>
       </c>
       <c r="B555" t="n">
-        <v>1130406.385714286</v>
+        <v>1130359.914285714</v>
       </c>
     </row>
     <row r="556">
@@ -5189,7 +5189,7 @@
         <v>46307</v>
       </c>
       <c r="B561" t="n">
-        <v>1029106.16</v>
+        <v>1006183.616666667</v>
       </c>
     </row>
   </sheetData>
@@ -5204,7 +5204,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3915"/>
+  <dimension ref="A1:F3916"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79302,19 +79302,19 @@
         <v>46109</v>
       </c>
       <c r="B3713" t="n">
-        <v>926099.2</v>
+        <v>926093.5</v>
       </c>
       <c r="C3713" t="n">
-        <v>865922.1</v>
+        <v>865925.5</v>
       </c>
       <c r="D3713" t="n">
-        <v>50893</v>
+        <v>50883.8</v>
       </c>
       <c r="E3713" t="n">
         <v>9284.200000000001</v>
       </c>
       <c r="F3713" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3714">
@@ -81402,19 +81402,19 @@
         <v>46214</v>
       </c>
       <c r="B3818" t="n">
-        <v>1059958.6</v>
+        <v>1059718.4</v>
       </c>
       <c r="C3818" t="n">
-        <v>986517.7</v>
+        <v>986302.6</v>
       </c>
       <c r="D3818" t="n">
-        <v>60497.4</v>
+        <v>60469.8</v>
       </c>
       <c r="E3818" t="n">
-        <v>12943.5</v>
+        <v>12946</v>
       </c>
       <c r="F3818" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3819">
@@ -82522,19 +82522,19 @@
         <v>46270</v>
       </c>
       <c r="B3874" t="n">
-        <v>1097248.5</v>
+        <v>1096923.2</v>
       </c>
       <c r="C3874" t="n">
-        <v>1028035.5</v>
+        <v>1027794.6</v>
       </c>
       <c r="D3874" t="n">
-        <v>56579.5</v>
+        <v>56387.4</v>
       </c>
       <c r="E3874" t="n">
-        <v>12633.5</v>
+        <v>12741.2</v>
       </c>
       <c r="F3874" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3875">
@@ -83354,6 +83354,26 @@
         <v>12199.4</v>
       </c>
       <c r="F3915" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3916">
+      <c r="A3916" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B3916" t="n">
+        <v>891570.9</v>
+      </c>
+      <c r="C3916" t="n">
+        <v>836823.7</v>
+      </c>
+      <c r="D3916" t="n">
+        <v>42438</v>
+      </c>
+      <c r="E3916" t="n">
+        <v>12309.2</v>
+      </c>
+      <c r="F3916" t="n">
         <v>0</v>
       </c>
     </row>
